--- a/docs/design/pokemon_romhack_tracker.xlsx
+++ b/docs/design/pokemon_romhack_tracker.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10322" uniqueCount="3566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10332" uniqueCount="3576">
   <si>
     <t>Dex #</t>
   </si>
@@ -10740,6 +10740,36 @@
   </si>
   <si>
     <t>This Pokémon’s Sp. Atk is doubled. Its moves always gain same-type attack bonus.</t>
+  </si>
+  <si>
+    <t>The first Grass move after switch-in also uses Smack Down.</t>
+  </si>
+  <si>
+    <t>Poison moves hit twice. The second hit deals 40% damage.</t>
+  </si>
+  <si>
+    <t>Pulse moves lower the target's Sp. Def by 1.</t>
+  </si>
+  <si>
+    <t>If hit for 25% HP or less by a move, set Stealth Rock.</t>
+  </si>
+  <si>
+    <t>Sound moves used by this Pokemon also use Charge.</t>
+  </si>
+  <si>
+    <t>Below half HP, Flying moves restore 1/4 of the damage dealt.</t>
+  </si>
+  <si>
+    <t>If all party Pokemon share a type, set Misty Terrain.</t>
+  </si>
+  <si>
+    <t>If all party Pokemon share a type, set Psychic Terrain.</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Regular Mega ability is Delta Stream; no unique ability is currently mapped.</t>
   </si>
 </sst>
 </file>
@@ -76679,9 +76709,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V191"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
@@ -76720,7 +76750,7 @@
     <col min="48" max="51" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="28" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -76788,7 +76818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ns3:dyDescent="0.2">
       <c r="A2" s="8">
         <v>3</v>
       </c>
@@ -76835,17 +76865,19 @@
         <v>6</v>
       </c>
       <c r="Q2" s="70" t="s">
-        <v>27</v>
+        <v>3002</v>
       </c>
       <c r="R2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="11"/>
+        <v>3566</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T2" s="10"/>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ns3:dyDescent="0.2">
       <c r="A3" s="8">
         <v>6</v>
       </c>
@@ -76897,12 +76929,14 @@
       <c r="R3" t="s">
         <v>37</v>
       </c>
-      <c r="S3" s="11"/>
+      <c r="S3" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T3" s="10"/>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ns3:dyDescent="0.2">
       <c r="A4" s="8">
         <v>6</v>
       </c>
@@ -76954,12 +76988,14 @@
       <c r="R4" t="s">
         <v>37</v>
       </c>
-      <c r="S4" s="11"/>
+      <c r="S4" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T4" s="10"/>
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ns3:dyDescent="0.2">
       <c r="A5" s="8">
         <v>9</v>
       </c>
@@ -77009,12 +77045,14 @@
       <c r="R5" t="s">
         <v>46</v>
       </c>
-      <c r="S5" s="11"/>
+      <c r="S5" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T5" s="10"/>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
     </row>
-    <row r="6" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A6" s="8">
         <v>15</v>
       </c>
@@ -77061,17 +77099,19 @@
         <v>6</v>
       </c>
       <c r="Q6" s="70" t="s">
-        <v>61</v>
+        <v>3081</v>
       </c>
       <c r="R6" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="S6" s="11"/>
+        <v>3567</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T6" s="10"/>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ns3:dyDescent="0.2">
       <c r="A7" s="8">
         <v>18</v>
       </c>
@@ -77123,12 +77163,14 @@
       <c r="R7" t="s">
         <v>73</v>
       </c>
-      <c r="S7" s="11"/>
+      <c r="S7" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T7" s="10"/>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
     </row>
-    <row r="8" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="8">
         <v>19</v>
       </c>
@@ -77189,7 +77231,7 @@
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
     </row>
-    <row r="9" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="8">
         <v>20</v>
       </c>
@@ -77250,7 +77292,7 @@
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ns3:dyDescent="0.2">
       <c r="A10" s="8">
         <v>25</v>
       </c>
@@ -77307,7 +77349,7 @@
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ns3:dyDescent="0.2">
       <c r="A11" s="8">
         <v>26</v>
       </c>
@@ -77364,7 +77406,7 @@
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ns3:dyDescent="0.2">
       <c r="A12" s="8">
         <v>27</v>
       </c>
@@ -77423,7 +77465,7 @@
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ns3:dyDescent="0.2">
       <c r="A13" s="8">
         <v>28</v>
       </c>
@@ -77482,7 +77524,7 @@
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
     </row>
-    <row r="14" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="18" customHeight="1" ns3:dyDescent="0.2">
       <c r="A14" s="8">
         <v>37</v>
       </c>
@@ -77539,7 +77581,7 @@
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
     </row>
-    <row r="15" spans="1:22" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="19" customHeight="1" ns3:dyDescent="0.2">
       <c r="A15" s="8">
         <v>38</v>
       </c>
@@ -77598,7 +77640,7 @@
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ns3:dyDescent="0.2">
       <c r="A16" s="8">
         <v>50</v>
       </c>
@@ -77659,7 +77701,7 @@
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ns3:dyDescent="0.2">
       <c r="A17" s="8">
         <v>51</v>
       </c>
@@ -77720,7 +77762,7 @@
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ns3:dyDescent="0.2">
       <c r="A18" s="8">
         <v>52</v>
       </c>
@@ -77779,7 +77821,7 @@
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ns3:dyDescent="0.2">
       <c r="A19" s="8">
         <v>52</v>
       </c>
@@ -77838,7 +77880,7 @@
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ns3:dyDescent="0.2">
       <c r="A20" s="8">
         <v>53</v>
       </c>
@@ -77897,7 +77939,7 @@
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ns3:dyDescent="0.2">
       <c r="A21" s="8">
         <v>58</v>
       </c>
@@ -77958,7 +78000,7 @@
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ns3:dyDescent="0.2">
       <c r="A22" s="8">
         <v>59</v>
       </c>
@@ -78019,7 +78061,7 @@
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ns3:dyDescent="0.2">
       <c r="A23" s="8">
         <v>65</v>
       </c>
@@ -78069,12 +78111,14 @@
       <c r="R23" t="s">
         <v>202</v>
       </c>
-      <c r="S23" s="11"/>
+      <c r="S23" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T23" s="10"/>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ns3:dyDescent="0.2">
       <c r="A24" s="8">
         <v>74</v>
       </c>
@@ -78135,7 +78179,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ns3:dyDescent="0.2">
       <c r="A25" s="8">
         <v>75</v>
       </c>
@@ -78196,7 +78240,7 @@
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ns3:dyDescent="0.2">
       <c r="A26" s="8">
         <v>76</v>
       </c>
@@ -78257,7 +78301,7 @@
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ns3:dyDescent="0.2">
       <c r="A27" s="8">
         <v>77</v>
       </c>
@@ -78316,7 +78360,7 @@
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ns3:dyDescent="0.2">
       <c r="A28" s="8">
         <v>78</v>
       </c>
@@ -78377,7 +78421,7 @@
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ns3:dyDescent="0.2">
       <c r="A29" s="8">
         <v>79</v>
       </c>
@@ -78436,7 +78480,7 @@
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ns3:dyDescent="0.2">
       <c r="A30" s="8">
         <v>80</v>
       </c>
@@ -78497,7 +78541,7 @@
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ns3:dyDescent="0.2">
       <c r="A31" s="8">
         <v>80</v>
       </c>
@@ -78549,12 +78593,14 @@
       <c r="R31" t="s">
         <v>240</v>
       </c>
-      <c r="S31" s="11"/>
+      <c r="S31" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T31" s="10"/>
       <c r="U31" s="11"/>
       <c r="V31" s="11"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ns3:dyDescent="0.2">
       <c r="A32" s="8">
         <v>83</v>
       </c>
@@ -78611,7 +78657,7 @@
       <c r="U32" s="11"/>
       <c r="V32" s="11"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ns3:dyDescent="0.2">
       <c r="A33" s="8">
         <v>88</v>
       </c>
@@ -78672,7 +78718,7 @@
       <c r="U33" s="11"/>
       <c r="V33" s="11"/>
     </row>
-    <row r="34" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A34" s="8">
         <v>89</v>
       </c>
@@ -78733,7 +78779,7 @@
       <c r="U34" s="11"/>
       <c r="V34" s="11"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ns3:dyDescent="0.2">
       <c r="A35" s="8">
         <v>94</v>
       </c>
@@ -78785,12 +78831,14 @@
       <c r="R35" t="s">
         <v>281</v>
       </c>
-      <c r="S35" s="11"/>
+      <c r="S35" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T35" s="10"/>
       <c r="U35" s="11"/>
       <c r="V35" s="11"/>
     </row>
-    <row r="36" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A36" s="8">
         <v>100</v>
       </c>
@@ -78851,7 +78899,7 @@
       <c r="U36" s="11"/>
       <c r="V36" s="11"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ns3:dyDescent="0.2">
       <c r="A37" s="8">
         <v>101</v>
       </c>
@@ -78912,7 +78960,7 @@
       <c r="U37" s="11"/>
       <c r="V37" s="11"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" ns3:dyDescent="0.2">
       <c r="A38" s="8">
         <v>103</v>
       </c>
@@ -78971,7 +79019,7 @@
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ns3:dyDescent="0.2">
       <c r="A39" s="8">
         <v>105</v>
       </c>
@@ -79032,7 +79080,7 @@
       <c r="U39" s="11"/>
       <c r="V39" s="11"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" ns3:dyDescent="0.2">
       <c r="A40" s="8">
         <v>110</v>
       </c>
@@ -79093,7 +79141,7 @@
       <c r="U40" s="11"/>
       <c r="V40" s="11"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" ns3:dyDescent="0.2">
       <c r="A41" s="8">
         <v>115</v>
       </c>
@@ -79143,12 +79191,14 @@
       <c r="R41" t="s">
         <v>345</v>
       </c>
-      <c r="S41" s="11"/>
+      <c r="S41" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T41" s="10"/>
       <c r="U41" s="11"/>
       <c r="V41" s="11"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" ns3:dyDescent="0.2">
       <c r="A42" s="8">
         <v>122</v>
       </c>
@@ -79209,7 +79259,7 @@
       <c r="U42" s="11"/>
       <c r="V42" s="11"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" ns3:dyDescent="0.2">
       <c r="A43" s="8">
         <v>127</v>
       </c>
@@ -79261,12 +79311,14 @@
       <c r="R43" t="s">
         <v>380</v>
       </c>
-      <c r="S43" s="11"/>
+      <c r="S43" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T43" s="10"/>
       <c r="U43" s="11"/>
       <c r="V43" s="11"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" ns3:dyDescent="0.2">
       <c r="A44" s="8">
         <v>128</v>
       </c>
@@ -79327,7 +79379,7 @@
       <c r="U44" s="11"/>
       <c r="V44" s="11"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ns3:dyDescent="0.2">
       <c r="A45" s="8">
         <v>128</v>
       </c>
@@ -79388,7 +79440,7 @@
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ns3:dyDescent="0.2">
       <c r="A46" s="8">
         <v>128</v>
       </c>
@@ -79447,7 +79499,7 @@
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
     </row>
-    <row r="47" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A47" s="8">
         <v>130</v>
       </c>
@@ -79499,12 +79551,14 @@
       <c r="R47" s="72" t="s">
         <v>387</v>
       </c>
-      <c r="S47" s="11"/>
+      <c r="S47" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T47" s="10"/>
       <c r="U47" s="11"/>
       <c r="V47" s="11"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ns3:dyDescent="0.2">
       <c r="A48" s="8">
         <v>133</v>
       </c>
@@ -79563,7 +79617,7 @@
       <c r="U48" s="11"/>
       <c r="V48" s="11"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22" ns3:dyDescent="0.2">
       <c r="A49" s="8">
         <v>142</v>
       </c>
@@ -79615,12 +79669,14 @@
       <c r="R49" t="s">
         <v>426</v>
       </c>
-      <c r="S49" s="11"/>
+      <c r="S49" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T49" s="10"/>
       <c r="U49" s="11"/>
       <c r="V49" s="11"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" ns3:dyDescent="0.2">
       <c r="A50" s="8">
         <v>144</v>
       </c>
@@ -79677,7 +79733,7 @@
       <c r="U50" s="11"/>
       <c r="V50" s="11"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22" ns3:dyDescent="0.2">
       <c r="A51" s="8">
         <v>145</v>
       </c>
@@ -79734,7 +79790,7 @@
       <c r="U51" s="11"/>
       <c r="V51" s="11"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" ns3:dyDescent="0.2">
       <c r="A52" s="8">
         <v>146</v>
       </c>
@@ -79791,7 +79847,7 @@
       <c r="U52" s="11"/>
       <c r="V52" s="11"/>
     </row>
-    <row r="53" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A53" s="8">
         <v>150</v>
       </c>
@@ -79843,12 +79899,14 @@
       <c r="R53" s="72" t="s">
         <v>450</v>
       </c>
-      <c r="S53" s="11"/>
+      <c r="S53" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T53" s="10"/>
       <c r="U53" s="11"/>
       <c r="V53" s="11"/>
     </row>
-    <row r="54" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A54" s="8">
         <v>150</v>
       </c>
@@ -79898,12 +79956,14 @@
       <c r="R54" s="72" t="s">
         <v>450</v>
       </c>
-      <c r="S54" s="11"/>
+      <c r="S54" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T54" s="10"/>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" ns3:dyDescent="0.2">
       <c r="A55" s="8">
         <v>157</v>
       </c>
@@ -79962,7 +80022,7 @@
       <c r="U55" s="11"/>
       <c r="V55" s="11"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:22" ns3:dyDescent="0.2">
       <c r="A56" s="8">
         <v>181</v>
       </c>
@@ -80009,17 +80069,19 @@
         <v>6</v>
       </c>
       <c r="Q56" t="s">
-        <v>499</v>
+        <v>3005</v>
       </c>
       <c r="R56" t="s">
-        <v>500</v>
-      </c>
-      <c r="S56" s="11"/>
+        <v>3568</v>
+      </c>
+      <c r="S56" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T56" s="10"/>
       <c r="U56" s="11"/>
       <c r="V56" s="11"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:22" ns3:dyDescent="0.2">
       <c r="A57" s="8">
         <v>194</v>
       </c>
@@ -80078,7 +80140,7 @@
       <c r="U57" s="11"/>
       <c r="V57" s="11"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" ns3:dyDescent="0.2">
       <c r="A58" s="8">
         <v>199</v>
       </c>
@@ -80139,7 +80201,7 @@
       <c r="U58" s="11"/>
       <c r="V58" s="11"/>
     </row>
-    <row r="59" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A59" s="8">
         <v>208</v>
       </c>
@@ -80198,7 +80260,7 @@
       <c r="U59" s="11"/>
       <c r="V59" s="11"/>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:22" ns3:dyDescent="0.2">
       <c r="A60" s="8">
         <v>211</v>
       </c>
@@ -80259,7 +80321,7 @@
       <c r="U60" s="11"/>
       <c r="V60" s="11"/>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:22" ns3:dyDescent="0.2">
       <c r="A61" s="8">
         <v>212</v>
       </c>
@@ -80311,12 +80373,14 @@
       <c r="R61" t="s">
         <v>580</v>
       </c>
-      <c r="S61" s="11"/>
+      <c r="S61" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T61" s="10"/>
       <c r="U61" s="11"/>
       <c r="V61" s="11"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:22" ns3:dyDescent="0.2">
       <c r="A62" s="8">
         <v>214</v>
       </c>
@@ -80368,12 +80432,14 @@
       <c r="R62" t="s">
         <v>587</v>
       </c>
-      <c r="S62" s="11"/>
+      <c r="S62" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T62" s="10"/>
       <c r="U62" s="11"/>
       <c r="V62" s="11"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:22" ns3:dyDescent="0.2">
       <c r="A63" s="8">
         <v>215</v>
       </c>
@@ -80434,7 +80500,7 @@
       <c r="U63" s="11"/>
       <c r="V63" s="11"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:22" ns3:dyDescent="0.2">
       <c r="A64" s="8">
         <v>222</v>
       </c>
@@ -80491,7 +80557,7 @@
       <c r="U64" s="11"/>
       <c r="V64" s="11"/>
     </row>
-    <row r="65" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A65" s="8">
         <v>229</v>
       </c>
@@ -80543,12 +80609,14 @@
       <c r="R65" s="72" t="s">
         <v>624</v>
       </c>
-      <c r="S65" s="11"/>
+      <c r="S65" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T65" s="10"/>
       <c r="U65" s="11"/>
       <c r="V65" s="11"/>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:22" ns3:dyDescent="0.2">
       <c r="A66" s="8">
         <v>248</v>
       </c>
@@ -80600,12 +80668,14 @@
       <c r="R66" t="s">
         <v>659</v>
       </c>
-      <c r="S66" s="11"/>
+      <c r="S66" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T66" s="10"/>
       <c r="U66" s="11"/>
       <c r="V66" s="11"/>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:22" ns3:dyDescent="0.2">
       <c r="A67" s="8">
         <v>254</v>
       </c>
@@ -80657,12 +80727,14 @@
       <c r="R67" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="S67" s="11"/>
+      <c r="S67" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T67" s="10"/>
       <c r="U67" s="11"/>
       <c r="V67" s="11"/>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:22" ns3:dyDescent="0.2">
       <c r="A68" s="8">
         <v>257</v>
       </c>
@@ -80714,12 +80786,14 @@
       <c r="R68" t="s">
         <v>678</v>
       </c>
-      <c r="S68" s="11"/>
+      <c r="S68" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T68" s="10"/>
       <c r="U68" s="11"/>
       <c r="V68" s="11"/>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:22" ns3:dyDescent="0.2">
       <c r="A69" s="8">
         <v>260</v>
       </c>
@@ -80771,12 +80845,14 @@
       <c r="R69" t="s">
         <v>683</v>
       </c>
-      <c r="S69" s="11"/>
+      <c r="S69" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T69" s="10"/>
       <c r="U69" s="11"/>
       <c r="V69" s="11"/>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:22" ns3:dyDescent="0.2">
       <c r="A70" s="8">
         <v>263</v>
       </c>
@@ -80837,7 +80913,7 @@
       <c r="U70" s="11"/>
       <c r="V70" s="11"/>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:22" ns3:dyDescent="0.2">
       <c r="A71" s="8">
         <v>264</v>
       </c>
@@ -80898,7 +80974,7 @@
       <c r="U71" s="11"/>
       <c r="V71" s="11"/>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:22" ns3:dyDescent="0.2">
       <c r="A72" s="8">
         <v>282</v>
       </c>
@@ -80950,12 +81026,14 @@
       <c r="R72" t="s">
         <v>2919</v>
       </c>
-      <c r="S72" s="11"/>
+      <c r="S72" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T72" s="10"/>
       <c r="U72" s="11"/>
       <c r="V72" s="11"/>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:22" ns3:dyDescent="0.2">
       <c r="A73" s="8">
         <v>302</v>
       </c>
@@ -81007,12 +81085,14 @@
       <c r="R73" t="s">
         <v>765</v>
       </c>
-      <c r="S73" s="11"/>
+      <c r="S73" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T73" s="10"/>
       <c r="U73" s="11"/>
       <c r="V73" s="11"/>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:22" ns3:dyDescent="0.2">
       <c r="A74" s="8">
         <v>303</v>
       </c>
@@ -81064,12 +81144,14 @@
       <c r="R74" t="s">
         <v>768</v>
       </c>
-      <c r="S74" s="11"/>
+      <c r="S74" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T74" s="10"/>
       <c r="U74" s="11"/>
       <c r="V74" s="11"/>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:22" ns3:dyDescent="0.2">
       <c r="A75" s="8">
         <v>306</v>
       </c>
@@ -81114,17 +81196,19 @@
         <v>6</v>
       </c>
       <c r="Q75" s="70" t="s">
-        <v>770</v>
+        <v>3010</v>
       </c>
       <c r="R75" t="s">
-        <v>771</v>
-      </c>
-      <c r="S75" s="11"/>
+        <v>3569</v>
+      </c>
+      <c r="S75" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T75" s="10"/>
       <c r="U75" s="11"/>
       <c r="V75" s="11"/>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:22" ns3:dyDescent="0.2">
       <c r="A76" s="8">
         <v>308</v>
       </c>
@@ -81176,12 +81260,14 @@
       <c r="R76" t="s">
         <v>777</v>
       </c>
-      <c r="S76" s="11"/>
+      <c r="S76" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T76" s="10"/>
       <c r="U76" s="11"/>
       <c r="V76" s="11"/>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:22" ns3:dyDescent="0.2">
       <c r="A77" s="8">
         <v>310</v>
       </c>
@@ -81226,17 +81312,19 @@
         <v>6</v>
       </c>
       <c r="Q77" t="s">
-        <v>781</v>
+        <v>3121</v>
       </c>
       <c r="R77" t="s">
-        <v>782</v>
-      </c>
-      <c r="S77" s="11"/>
+        <v>3570</v>
+      </c>
+      <c r="S77" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T77" s="10"/>
       <c r="U77" s="11"/>
       <c r="V77" s="11"/>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:22" ns3:dyDescent="0.2">
       <c r="A78" s="8">
         <v>319</v>
       </c>
@@ -81288,12 +81376,14 @@
       <c r="R78" t="s">
         <v>802</v>
       </c>
-      <c r="S78" s="11"/>
+      <c r="S78" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T78" s="10"/>
       <c r="U78" s="11"/>
       <c r="V78" s="11"/>
     </row>
-    <row r="79" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A79" s="8">
         <v>323</v>
       </c>
@@ -81344,12 +81434,14 @@
       <c r="R79" s="72" t="s">
         <v>811</v>
       </c>
-      <c r="S79" s="11"/>
+      <c r="S79" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T79" s="10"/>
       <c r="U79" s="11"/>
       <c r="V79" s="11"/>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:22" ns3:dyDescent="0.2">
       <c r="A80" s="8">
         <v>334</v>
       </c>
@@ -81401,12 +81493,14 @@
       <c r="R80" t="s">
         <v>835</v>
       </c>
-      <c r="S80" s="11"/>
+      <c r="S80" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T80" s="10"/>
       <c r="U80" s="11"/>
       <c r="V80" s="11"/>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:22" ns3:dyDescent="0.2">
       <c r="A81" s="8">
         <v>351</v>
       </c>
@@ -81461,7 +81555,7 @@
       <c r="U81" s="11"/>
       <c r="V81" s="11"/>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:22" ns3:dyDescent="0.2">
       <c r="A82" s="8">
         <v>351</v>
       </c>
@@ -81516,7 +81610,7 @@
       <c r="U82" s="11"/>
       <c r="V82" s="11"/>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:22" ns3:dyDescent="0.2">
       <c r="A83" s="8">
         <v>351</v>
       </c>
@@ -81571,7 +81665,7 @@
       <c r="U83" s="11"/>
       <c r="V83" s="11"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:22" ns3:dyDescent="0.2">
       <c r="A84" s="8">
         <v>354</v>
       </c>
@@ -81621,12 +81715,14 @@
       <c r="R84" t="s">
         <v>884</v>
       </c>
-      <c r="S84" s="11"/>
+      <c r="S84" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T84" s="10"/>
       <c r="U84" s="11"/>
       <c r="V84" s="11"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:22" ns3:dyDescent="0.2">
       <c r="A85" s="8">
         <v>359</v>
       </c>
@@ -81676,12 +81772,14 @@
       <c r="R85" t="s">
         <v>896</v>
       </c>
-      <c r="S85" s="11"/>
+      <c r="S85" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T85" s="10"/>
       <c r="U85" s="11"/>
       <c r="V85" s="11"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:22" ns3:dyDescent="0.2">
       <c r="A86" s="8">
         <v>362</v>
       </c>
@@ -81731,12 +81829,14 @@
       <c r="R86" t="s">
         <v>900</v>
       </c>
-      <c r="S86" s="11"/>
+      <c r="S86" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T86" s="10"/>
       <c r="U86" s="11"/>
       <c r="V86" s="11"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:22" ns3:dyDescent="0.2">
       <c r="A87" s="8">
         <v>373</v>
       </c>
@@ -81783,17 +81883,19 @@
         <v>6</v>
       </c>
       <c r="Q87" s="70" t="s">
-        <v>916</v>
+        <v>3044</v>
       </c>
       <c r="R87" t="s">
-        <v>917</v>
-      </c>
-      <c r="S87" s="11"/>
+        <v>3571</v>
+      </c>
+      <c r="S87" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T87" s="10"/>
       <c r="U87" s="11"/>
       <c r="V87" s="11"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:22" ns3:dyDescent="0.2">
       <c r="A88" s="8">
         <v>376</v>
       </c>
@@ -81845,12 +81947,14 @@
       <c r="R88" t="s">
         <v>922</v>
       </c>
-      <c r="S88" s="11"/>
+      <c r="S88" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T88" s="10"/>
       <c r="U88" s="11"/>
       <c r="V88" s="11"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:22" ns3:dyDescent="0.2">
       <c r="A89" s="8">
         <v>380</v>
       </c>
@@ -81897,17 +82001,19 @@
         <v>6</v>
       </c>
       <c r="Q89" s="70" t="s">
-        <v>934</v>
+        <v>3048</v>
       </c>
       <c r="R89" t="s">
-        <v>935</v>
-      </c>
-      <c r="S89" s="11"/>
+        <v>3572</v>
+      </c>
+      <c r="S89" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T89" s="10"/>
       <c r="U89" s="11"/>
       <c r="V89" s="11"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:22" ns3:dyDescent="0.2">
       <c r="A90" s="8">
         <v>381</v>
       </c>
@@ -81954,17 +82060,19 @@
         <v>6</v>
       </c>
       <c r="Q90" s="70" t="s">
-        <v>937</v>
+        <v>3049</v>
       </c>
       <c r="R90" t="s">
-        <v>938</v>
-      </c>
-      <c r="S90" s="11"/>
+        <v>3573</v>
+      </c>
+      <c r="S90" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T90" s="10"/>
       <c r="U90" s="11"/>
       <c r="V90" s="11"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:22" ns3:dyDescent="0.2">
       <c r="A91" s="8">
         <v>382</v>
       </c>
@@ -82019,7 +82127,7 @@
       <c r="U91" s="11"/>
       <c r="V91" s="11"/>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:22" ns3:dyDescent="0.2">
       <c r="A92" s="8">
         <v>383</v>
       </c>
@@ -82076,7 +82184,7 @@
       <c r="U92" s="11"/>
       <c r="V92" s="11"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:22" ns3:dyDescent="0.2">
       <c r="A93" s="8">
         <v>384</v>
       </c>
@@ -82123,17 +82231,17 @@
         <v>6</v>
       </c>
       <c r="Q93" t="s">
-        <v>948</v>
+        <v>3574</v>
       </c>
       <c r="R93" t="s">
-        <v>949</v>
+        <v>3575</v>
       </c>
       <c r="S93" s="11"/>
       <c r="T93" s="10"/>
       <c r="U93" s="11"/>
       <c r="V93" s="11"/>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:22" ns3:dyDescent="0.2">
       <c r="A94" s="8">
         <v>386</v>
       </c>
@@ -82188,7 +82296,7 @@
       <c r="U94" s="11"/>
       <c r="V94" s="11"/>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:22" ns3:dyDescent="0.2">
       <c r="A95" s="8">
         <v>386</v>
       </c>
@@ -82243,7 +82351,7 @@
       <c r="U95" s="11"/>
       <c r="V95" s="11"/>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:22" ns3:dyDescent="0.2">
       <c r="A96" s="8">
         <v>386</v>
       </c>
@@ -82298,7 +82406,7 @@
       <c r="U96" s="11"/>
       <c r="V96" s="11"/>
     </row>
-    <row r="97" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A97" s="8">
         <v>412</v>
       </c>
@@ -82355,7 +82463,7 @@
       <c r="U97" s="11"/>
       <c r="V97" s="11"/>
     </row>
-    <row r="98" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A98" s="8">
         <v>412</v>
       </c>
@@ -82412,7 +82520,7 @@
       <c r="U98" s="11"/>
       <c r="V98" s="11"/>
     </row>
-    <row r="99" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A99" s="8">
         <v>413</v>
       </c>
@@ -82471,7 +82579,7 @@
       <c r="U99" s="11"/>
       <c r="V99" s="11"/>
     </row>
-    <row r="100" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A100" s="8">
         <v>413</v>
       </c>
@@ -82530,7 +82638,7 @@
       <c r="U100" s="11"/>
       <c r="V100" s="11"/>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:22" ns3:dyDescent="0.2">
       <c r="A101" s="8">
         <v>428</v>
       </c>
@@ -82582,12 +82690,14 @@
       <c r="R101" t="s">
         <v>1029</v>
       </c>
-      <c r="S101" s="11"/>
+      <c r="S101" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T101" s="10"/>
       <c r="U101" s="11"/>
       <c r="V101" s="11"/>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:22" ns3:dyDescent="0.2">
       <c r="A102" s="8">
         <v>445</v>
       </c>
@@ -82639,12 +82749,14 @@
       <c r="R102" t="s">
         <v>1056</v>
       </c>
-      <c r="S102" s="11"/>
+      <c r="S102" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T102" s="10"/>
       <c r="U102" s="11"/>
       <c r="V102" s="11"/>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:22" ns3:dyDescent="0.2">
       <c r="A103" s="8">
         <v>448</v>
       </c>
@@ -82696,12 +82808,14 @@
       <c r="R103" t="s">
         <v>1062</v>
       </c>
-      <c r="S103" s="11"/>
+      <c r="S103" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T103" s="10"/>
       <c r="U103" s="11"/>
       <c r="V103" s="11"/>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:22" ns3:dyDescent="0.2">
       <c r="A104" s="8">
         <v>460</v>
       </c>
@@ -82753,12 +82867,14 @@
       <c r="R104" t="s">
         <v>1087</v>
       </c>
-      <c r="S104" s="11"/>
+      <c r="S104" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T104" s="10"/>
       <c r="U104" s="11"/>
       <c r="V104" s="11"/>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:22" ns3:dyDescent="0.2">
       <c r="A105" s="8">
         <v>475</v>
       </c>
@@ -82810,12 +82926,14 @@
       <c r="R105" t="s">
         <v>1110</v>
       </c>
-      <c r="S105" s="11"/>
+      <c r="S105" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T105" s="10"/>
       <c r="U105" s="11"/>
       <c r="V105" s="11"/>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:22" ns3:dyDescent="0.2">
       <c r="A106" s="12">
         <v>479</v>
       </c>
@@ -82873,7 +82991,7 @@
       <c r="U106" s="11"/>
       <c r="V106" s="11"/>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:22" ns3:dyDescent="0.2">
       <c r="A107" s="12">
         <v>479</v>
       </c>
@@ -82932,7 +83050,7 @@
       <c r="U107" s="11"/>
       <c r="V107" s="11"/>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:22" ns3:dyDescent="0.2">
       <c r="A108" s="12">
         <v>479</v>
       </c>
@@ -82991,7 +83109,7 @@
       <c r="U108" s="11"/>
       <c r="V108" s="11"/>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:22" ns3:dyDescent="0.2">
       <c r="A109" s="12">
         <v>479</v>
       </c>
@@ -83050,7 +83168,7 @@
       <c r="U109" s="11"/>
       <c r="V109" s="11"/>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:22" ns3:dyDescent="0.2">
       <c r="A110" s="12">
         <v>479</v>
       </c>
@@ -83109,7 +83227,7 @@
       <c r="U110" s="11"/>
       <c r="V110" s="11"/>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:22" ns3:dyDescent="0.2">
       <c r="A111" s="8">
         <v>483</v>
       </c>
@@ -83168,7 +83286,7 @@
       <c r="U111" s="11"/>
       <c r="V111" s="11"/>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:22" ns3:dyDescent="0.2">
       <c r="A112" s="8">
         <v>484</v>
       </c>
@@ -83227,7 +83345,7 @@
       <c r="U112" s="11"/>
       <c r="V112" s="11"/>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:22" ns3:dyDescent="0.2">
       <c r="A113" s="8">
         <v>487</v>
       </c>
@@ -83284,7 +83402,7 @@
       <c r="U113" s="11"/>
       <c r="V113" s="11"/>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:22" ns3:dyDescent="0.2">
       <c r="A114" s="8">
         <v>492</v>
       </c>
@@ -83341,7 +83459,7 @@
       <c r="U114" s="11"/>
       <c r="V114" s="11"/>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:22" ns3:dyDescent="0.2">
       <c r="A115" s="8">
         <v>503</v>
       </c>
@@ -83400,7 +83518,7 @@
       <c r="U115" s="11"/>
       <c r="V115" s="11"/>
     </row>
-    <row r="116" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A116" s="8">
         <v>531</v>
       </c>
@@ -83452,12 +83570,14 @@
       <c r="R116" s="72" t="s">
         <v>2973</v>
       </c>
-      <c r="S116" s="11"/>
+      <c r="S116" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T116" s="10"/>
       <c r="U116" s="11"/>
       <c r="V116" s="11"/>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:22" ns3:dyDescent="0.2">
       <c r="A117" s="8">
         <v>549</v>
       </c>
@@ -83518,7 +83638,7 @@
       <c r="U117" s="11"/>
       <c r="V117" s="11"/>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:22" ns3:dyDescent="0.2">
       <c r="A118" s="8">
         <v>550</v>
       </c>
@@ -83577,7 +83697,7 @@
       <c r="U118" s="11"/>
       <c r="V118" s="11"/>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:22" ns3:dyDescent="0.2">
       <c r="A119" s="8">
         <v>550</v>
       </c>
@@ -83636,7 +83756,7 @@
       <c r="U119" s="11"/>
       <c r="V119" s="11"/>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:22" ns3:dyDescent="0.2">
       <c r="A120" s="8">
         <v>554</v>
       </c>
@@ -83693,7 +83813,7 @@
       <c r="U120" s="11"/>
       <c r="V120" s="11"/>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:22" ns3:dyDescent="0.2">
       <c r="A121" s="8">
         <v>555</v>
       </c>
@@ -83750,7 +83870,7 @@
       <c r="U121" s="11"/>
       <c r="V121" s="11"/>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:22" ns3:dyDescent="0.2">
       <c r="A122" s="8">
         <v>555</v>
       </c>
@@ -83809,7 +83929,7 @@
       <c r="U122" s="11"/>
       <c r="V122" s="11"/>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:22" ns3:dyDescent="0.2">
       <c r="A123" s="8">
         <v>555</v>
       </c>
@@ -83866,7 +83986,7 @@
       <c r="U123" s="11"/>
       <c r="V123" s="11"/>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:22" ns3:dyDescent="0.2">
       <c r="A124" s="8">
         <v>562</v>
       </c>
@@ -83923,7 +84043,7 @@
       <c r="U124" s="11"/>
       <c r="V124" s="11"/>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:22" ns3:dyDescent="0.2">
       <c r="A125" s="8">
         <v>570</v>
       </c>
@@ -83980,7 +84100,7 @@
       <c r="U125" s="11"/>
       <c r="V125" s="11"/>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:22" ns3:dyDescent="0.2">
       <c r="A126" s="8">
         <v>571</v>
       </c>
@@ -84037,7 +84157,7 @@
       <c r="U126" s="11"/>
       <c r="V126" s="11"/>
     </row>
-    <row r="127" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A127" s="8">
         <v>618</v>
       </c>
@@ -84094,7 +84214,7 @@
       <c r="U127" s="11"/>
       <c r="V127" s="11"/>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:22" ns3:dyDescent="0.2">
       <c r="A128" s="8">
         <v>628</v>
       </c>
@@ -84155,7 +84275,7 @@
       <c r="U128" s="11"/>
       <c r="V128" s="11"/>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:22" ns3:dyDescent="0.2">
       <c r="A129" s="8">
         <v>641</v>
       </c>
@@ -84210,7 +84330,7 @@
       <c r="U129" s="11"/>
       <c r="V129" s="11"/>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:22" ns3:dyDescent="0.2">
       <c r="A130" s="8">
         <v>642</v>
       </c>
@@ -84267,7 +84387,7 @@
       <c r="U130" s="11"/>
       <c r="V130" s="11"/>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:22" ns3:dyDescent="0.2">
       <c r="A131" s="8">
         <v>645</v>
       </c>
@@ -84324,7 +84444,7 @@
       <c r="U131" s="11"/>
       <c r="V131" s="11"/>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:22" ns3:dyDescent="0.2">
       <c r="A132" s="8">
         <v>646</v>
       </c>
@@ -84381,7 +84501,7 @@
       <c r="U132" s="11"/>
       <c r="V132" s="11"/>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:22" ns3:dyDescent="0.2">
       <c r="A133" s="8">
         <v>646</v>
       </c>
@@ -84438,7 +84558,7 @@
       <c r="U133" s="11"/>
       <c r="V133" s="11"/>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:22" ns3:dyDescent="0.2">
       <c r="A134" s="8">
         <v>647</v>
       </c>
@@ -84497,7 +84617,7 @@
       <c r="U134" s="11"/>
       <c r="V134" s="11"/>
     </row>
-    <row r="135" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A135" s="8">
         <v>648</v>
       </c>
@@ -84556,7 +84676,7 @@
       <c r="U135" s="11"/>
       <c r="V135" s="11"/>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:22" ns3:dyDescent="0.2">
       <c r="A136" s="8">
         <v>658</v>
       </c>
@@ -84613,7 +84733,7 @@
       <c r="U136" s="11"/>
       <c r="V136" s="11"/>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:22" ns3:dyDescent="0.2">
       <c r="A137" s="8">
         <v>678</v>
       </c>
@@ -84672,7 +84792,7 @@
       <c r="U137" s="11"/>
       <c r="V137" s="11"/>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:22" ns3:dyDescent="0.2">
       <c r="A138" s="8">
         <v>681</v>
       </c>
@@ -84729,7 +84849,7 @@
       <c r="U138" s="11"/>
       <c r="V138" s="11"/>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:22" ns3:dyDescent="0.2">
       <c r="A139" s="8">
         <v>705</v>
       </c>
@@ -84790,7 +84910,7 @@
       <c r="U139" s="11"/>
       <c r="V139" s="11"/>
     </row>
-    <row r="140" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A140" s="8">
         <v>706</v>
       </c>
@@ -84851,7 +84971,7 @@
       <c r="U140" s="11"/>
       <c r="V140" s="11"/>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:22" ns3:dyDescent="0.2">
       <c r="A141" s="8">
         <v>710</v>
       </c>
@@ -84912,7 +85032,7 @@
       <c r="U141" s="11"/>
       <c r="V141" s="11"/>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:22" ns3:dyDescent="0.2">
       <c r="A142" s="8">
         <v>710</v>
       </c>
@@ -84973,7 +85093,7 @@
       <c r="U142" s="11"/>
       <c r="V142" s="11"/>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:22" ns3:dyDescent="0.2">
       <c r="A143" s="8">
         <v>710</v>
       </c>
@@ -85034,7 +85154,7 @@
       <c r="U143" s="11"/>
       <c r="V143" s="11"/>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:22" ns3:dyDescent="0.2">
       <c r="A144" s="8">
         <v>711</v>
       </c>
@@ -85095,7 +85215,7 @@
       <c r="U144" s="11"/>
       <c r="V144" s="11"/>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:22" ns3:dyDescent="0.2">
       <c r="A145" s="8">
         <v>711</v>
       </c>
@@ -85156,7 +85276,7 @@
       <c r="U145" s="11"/>
       <c r="V145" s="11"/>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:22" ns3:dyDescent="0.2">
       <c r="A146" s="8">
         <v>711</v>
       </c>
@@ -85217,7 +85337,7 @@
       <c r="U146" s="11"/>
       <c r="V146" s="11"/>
     </row>
-    <row r="147" spans="1:22" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:22" ht="19" customHeight="1" ns3:dyDescent="0.2">
       <c r="A147" s="12">
         <v>713</v>
       </c>
@@ -85278,7 +85398,7 @@
       <c r="U147" s="11"/>
       <c r="V147" s="11"/>
     </row>
-    <row r="148" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A148" s="8">
         <v>718</v>
       </c>
@@ -85335,7 +85455,7 @@
       <c r="U148" s="11"/>
       <c r="V148" s="11"/>
     </row>
-    <row r="149" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A149" s="8">
         <v>718</v>
       </c>
@@ -85392,7 +85512,7 @@
       <c r="U149" s="11"/>
       <c r="V149" s="11"/>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:22" ns3:dyDescent="0.2">
       <c r="A150" s="8">
         <v>719</v>
       </c>
@@ -85444,12 +85564,14 @@
       <c r="R150" t="s">
         <v>1595</v>
       </c>
-      <c r="S150" s="11"/>
+      <c r="S150" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="T150" s="10"/>
       <c r="U150" s="11"/>
       <c r="V150" s="11"/>
     </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:22" ns3:dyDescent="0.2">
       <c r="A151" s="8">
         <v>720</v>
       </c>
@@ -85506,7 +85628,7 @@
       <c r="U151" s="11"/>
       <c r="V151" s="11"/>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:22" ns3:dyDescent="0.2">
       <c r="A152" s="8">
         <v>724</v>
       </c>
@@ -85565,7 +85687,7 @@
       <c r="U152" s="11"/>
       <c r="V152" s="11"/>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:22" ns3:dyDescent="0.2">
       <c r="A153" s="8">
         <v>741</v>
       </c>
@@ -85622,7 +85744,7 @@
       <c r="U153" s="11"/>
       <c r="V153" s="11"/>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:22" ns3:dyDescent="0.2">
       <c r="A154" s="8">
         <v>741</v>
       </c>
@@ -85679,7 +85801,7 @@
       <c r="U154" s="11"/>
       <c r="V154" s="11"/>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:22" ns3:dyDescent="0.2">
       <c r="A155" s="8">
         <v>741</v>
       </c>
@@ -85736,7 +85858,7 @@
       <c r="U155" s="11"/>
       <c r="V155" s="11"/>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:22" ns3:dyDescent="0.2">
       <c r="A156" s="8">
         <v>744</v>
       </c>
@@ -85791,7 +85913,7 @@
       <c r="U156" s="11"/>
       <c r="V156" s="11"/>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:22" ns3:dyDescent="0.2">
       <c r="A157" s="8">
         <v>745</v>
       </c>
@@ -85846,7 +85968,7 @@
       <c r="U157" s="11"/>
       <c r="V157" s="11"/>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:22" ns3:dyDescent="0.2">
       <c r="A158" s="8">
         <v>745</v>
       </c>
@@ -85905,7 +86027,7 @@
       <c r="U158" s="11"/>
       <c r="V158" s="11"/>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:22" ns3:dyDescent="0.2">
       <c r="A159" s="8">
         <v>746</v>
       </c>
@@ -85960,7 +86082,7 @@
       <c r="U159" s="11"/>
       <c r="V159" s="11"/>
     </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:22" ns3:dyDescent="0.2">
       <c r="A160" s="8">
         <v>774</v>
       </c>
@@ -86017,7 +86139,7 @@
       <c r="U160" s="11"/>
       <c r="V160" s="11"/>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:22" ns3:dyDescent="0.2">
       <c r="A161" s="8">
         <v>800</v>
       </c>
@@ -86074,7 +86196,7 @@
       <c r="U161" s="11"/>
       <c r="V161" s="11"/>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:22" ns3:dyDescent="0.2">
       <c r="A162" s="8">
         <v>800</v>
       </c>
@@ -86131,7 +86253,7 @@
       <c r="U162" s="11"/>
       <c r="V162" s="11"/>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:22" ns3:dyDescent="0.2">
       <c r="A163" s="8">
         <v>800</v>
       </c>
@@ -86188,7 +86310,7 @@
       <c r="U163" s="11"/>
       <c r="V163" s="11"/>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:22" ns3:dyDescent="0.2">
       <c r="A164" s="8">
         <v>849</v>
       </c>
@@ -86249,7 +86371,7 @@
       <c r="U164" s="11"/>
       <c r="V164" s="11"/>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:22" ns3:dyDescent="0.2">
       <c r="A165" s="8">
         <v>875</v>
       </c>
@@ -86304,7 +86426,7 @@
       <c r="U165" s="11"/>
       <c r="V165" s="11"/>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:22" ns3:dyDescent="0.2">
       <c r="A166" s="8">
         <v>876</v>
       </c>
@@ -86365,7 +86487,7 @@
       <c r="U166" s="11"/>
       <c r="V166" s="11"/>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:22" ns3:dyDescent="0.2">
       <c r="A167" s="8">
         <v>877</v>
       </c>
@@ -86422,7 +86544,7 @@
       <c r="U167" s="11"/>
       <c r="V167" s="11"/>
     </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:22" ns3:dyDescent="0.2">
       <c r="A168" s="8">
         <v>888</v>
       </c>
@@ -86479,7 +86601,7 @@
       <c r="U168" s="11"/>
       <c r="V168" s="11"/>
     </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:22" ns3:dyDescent="0.2">
       <c r="A169" s="8">
         <v>889</v>
       </c>
@@ -86536,7 +86658,7 @@
       <c r="U169" s="11"/>
       <c r="V169" s="11"/>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:22" ns3:dyDescent="0.2">
       <c r="A170" s="8">
         <v>890</v>
       </c>
@@ -86593,7 +86715,7 @@
       <c r="U170" s="11"/>
       <c r="V170" s="11"/>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:22" ns3:dyDescent="0.2">
       <c r="A171" s="8">
         <v>892</v>
       </c>
@@ -86650,7 +86772,7 @@
       <c r="U171" s="11"/>
       <c r="V171" s="11"/>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:22" ns3:dyDescent="0.2">
       <c r="A172" s="8">
         <v>898</v>
       </c>
@@ -86707,7 +86829,7 @@
       <c r="U172" s="11"/>
       <c r="V172" s="11"/>
     </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:22" ns3:dyDescent="0.2">
       <c r="A173" s="8">
         <v>898</v>
       </c>
@@ -86764,7 +86886,7 @@
       <c r="U173" s="11"/>
       <c r="V173" s="11"/>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:22" ns3:dyDescent="0.2">
       <c r="A174" s="8">
         <v>901</v>
       </c>
@@ -86818,7 +86940,7 @@
       <c r="U174" s="11"/>
       <c r="V174" s="11"/>
     </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:22" ns3:dyDescent="0.2">
       <c r="A175" s="8">
         <v>902</v>
       </c>
@@ -86879,7 +87001,7 @@
       <c r="U175" s="11"/>
       <c r="V175" s="11"/>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:22" ns3:dyDescent="0.2">
       <c r="A176" s="8">
         <v>905</v>
       </c>
@@ -86936,7 +87058,7 @@
       <c r="U176" s="11"/>
       <c r="V176" s="11"/>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:22" ns3:dyDescent="0.2">
       <c r="A177" s="8">
         <v>916</v>
       </c>
@@ -86995,7 +87117,7 @@
       <c r="U177" s="11"/>
       <c r="V177" s="11"/>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:22" ns3:dyDescent="0.2">
       <c r="A178" s="8">
         <v>925</v>
       </c>
@@ -87054,7 +87176,7 @@
       <c r="U178" s="11"/>
       <c r="V178" s="11"/>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:22" ns3:dyDescent="0.2">
       <c r="A179" s="8">
         <v>931</v>
       </c>
@@ -87115,7 +87237,7 @@
       <c r="U179" s="11"/>
       <c r="V179" s="11"/>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:22" ns3:dyDescent="0.2">
       <c r="A180" s="8">
         <v>931</v>
       </c>
@@ -87176,7 +87298,7 @@
       <c r="U180" s="11"/>
       <c r="V180" s="11"/>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:22" ns3:dyDescent="0.2">
       <c r="A181" s="8">
         <v>931</v>
       </c>
@@ -87237,7 +87359,7 @@
       <c r="U181" s="11"/>
       <c r="V181" s="11"/>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:22" ns3:dyDescent="0.2">
       <c r="A182" s="8">
         <v>964</v>
       </c>
@@ -87292,7 +87414,7 @@
       <c r="U182" s="11"/>
       <c r="V182" s="11"/>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:22" ns3:dyDescent="0.2">
       <c r="A183" s="8">
         <v>978</v>
       </c>
@@ -87351,7 +87473,7 @@
       <c r="U183" s="11"/>
       <c r="V183" s="11"/>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:22" ns3:dyDescent="0.2">
       <c r="A184" s="8">
         <v>978</v>
       </c>
@@ -87410,7 +87532,7 @@
       <c r="U184" s="11"/>
       <c r="V184" s="11"/>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:22" ns3:dyDescent="0.2">
       <c r="A185" s="8">
         <v>982</v>
       </c>
@@ -87469,7 +87591,7 @@
       <c r="U185" s="11"/>
       <c r="V185" s="11"/>
     </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" ns3:dyDescent="0.2">
       <c r="A186" s="8">
         <v>999</v>
       </c>
@@ -87524,7 +87646,7 @@
       <c r="U186" s="11"/>
       <c r="V186" s="11"/>
     </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:22" ns3:dyDescent="0.2">
       <c r="A187" s="8">
         <v>1017</v>
       </c>
@@ -87581,7 +87703,7 @@
       <c r="U187" s="11"/>
       <c r="V187" s="11"/>
     </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:22" ns3:dyDescent="0.2">
       <c r="A188" s="8">
         <v>1017</v>
       </c>
@@ -87638,7 +87760,7 @@
       <c r="U188" s="11"/>
       <c r="V188" s="11"/>
     </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:22" ns3:dyDescent="0.2">
       <c r="A189" s="8">
         <v>1017</v>
       </c>
@@ -87695,7 +87817,7 @@
       <c r="U189" s="11"/>
       <c r="V189" s="11"/>
     </row>
-    <row r="190" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A190" s="8">
         <v>1024</v>
       </c>
@@ -87750,7 +87872,7 @@
       <c r="U190" s="11"/>
       <c r="V190" s="11"/>
     </row>
-    <row r="191" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A191" s="8">
         <v>1024</v>
       </c>

--- a/docs/design/pokemon_romhack_tracker.xlsx
+++ b/docs/design/pokemon_romhack_tracker.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10332" uniqueCount="3576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10333" uniqueCount="3577">
   <si>
     <t>Dex #</t>
   </si>
@@ -3341,7 +3341,7 @@
     <t>Yanmega</t>
   </si>
   <si>
-    <t>AERODYNAMICS</t>
+    <t>AERODYNAMIC</t>
   </si>
   <si>
     <t>Leafeon</t>
@@ -10770,6 +10770,9 @@
   </si>
   <si>
     <t>Regular Mega ability is Delta Stream; no unique ability is currently mapped.</t>
+  </si>
+  <si>
+    <t>If any Pokemon fainted last turn, this Pokemon's Water- and Ghost-type moves trap the target.</t>
   </si>
 </sst>
 </file>
@@ -11728,9 +11731,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X1027"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
@@ -11753,7 +11756,7 @@
     <col min="22" max="22" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="28" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -11819,7 +11822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ns3:dyDescent="0.2">
       <c r="A2" s="58">
         <v>1</v>
       </c>
@@ -11877,7 +11880,7 @@
       <c r="U2" s="11"/>
       <c r="V2" s="10"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ns3:dyDescent="0.2">
       <c r="A3" s="58">
         <v>2</v>
       </c>
@@ -11935,7 +11938,7 @@
       <c r="U3" s="11"/>
       <c r="V3" s="10"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ns3:dyDescent="0.2">
       <c r="A4" s="58">
         <v>3</v>
       </c>
@@ -11993,7 +11996,7 @@
       <c r="U4" s="11"/>
       <c r="V4" s="10"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ns3:dyDescent="0.2">
       <c r="A5" s="58">
         <v>4</v>
       </c>
@@ -12049,7 +12052,7 @@
       <c r="U5" s="11"/>
       <c r="V5" s="10"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ns3:dyDescent="0.2">
       <c r="A6" s="58">
         <v>5</v>
       </c>
@@ -12105,7 +12108,7 @@
       <c r="U6" s="11"/>
       <c r="V6" s="10"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ns3:dyDescent="0.2">
       <c r="A7" s="58">
         <v>6</v>
       </c>
@@ -12163,7 +12166,7 @@
       <c r="U7" s="11"/>
       <c r="V7" s="10"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ns3:dyDescent="0.2">
       <c r="A8" s="58">
         <v>7</v>
       </c>
@@ -12219,7 +12222,7 @@
       <c r="U8" s="11"/>
       <c r="V8" s="10"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ns3:dyDescent="0.2">
       <c r="A9" s="58">
         <v>8</v>
       </c>
@@ -12275,7 +12278,7 @@
       <c r="U9" s="11"/>
       <c r="V9" s="10"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ns3:dyDescent="0.2">
       <c r="A10" s="58">
         <v>9</v>
       </c>
@@ -12331,7 +12334,7 @@
       <c r="U10" s="11"/>
       <c r="V10" s="10"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ns3:dyDescent="0.2">
       <c r="A11" s="58">
         <v>10</v>
       </c>
@@ -12387,7 +12390,7 @@
       <c r="U11" s="11"/>
       <c r="V11" s="10"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ns3:dyDescent="0.2">
       <c r="A12" s="58">
         <v>11</v>
       </c>
@@ -12441,7 +12444,7 @@
       <c r="U12" s="11"/>
       <c r="V12" s="10"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ns3:dyDescent="0.2">
       <c r="A13" s="58">
         <v>12</v>
       </c>
@@ -12499,7 +12502,7 @@
       <c r="U13" s="11"/>
       <c r="V13" s="10"/>
     </row>
-    <row r="14" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A14" s="58">
         <v>13</v>
       </c>
@@ -12557,7 +12560,7 @@
       <c r="U14" s="11"/>
       <c r="V14" s="10"/>
     </row>
-    <row r="15" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A15" s="58">
         <v>14</v>
       </c>
@@ -12613,7 +12616,7 @@
       <c r="U15" s="11"/>
       <c r="V15" s="10"/>
     </row>
-    <row r="16" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A16" s="58">
         <v>15</v>
       </c>
@@ -12670,7 +12673,7 @@
       <c r="U16" s="11"/>
       <c r="V16" s="10"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ns3:dyDescent="0.2">
       <c r="A17" s="58">
         <v>16</v>
       </c>
@@ -12730,7 +12733,7 @@
       <c r="U17" s="11"/>
       <c r="V17" s="10"/>
     </row>
-    <row r="18" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A18" s="58">
         <v>17</v>
       </c>
@@ -12790,7 +12793,7 @@
       <c r="U18" s="11"/>
       <c r="V18" s="10"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ns3:dyDescent="0.2">
       <c r="A19" s="58">
         <v>18</v>
       </c>
@@ -12850,7 +12853,7 @@
       <c r="U19" s="11"/>
       <c r="V19" s="10"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ns3:dyDescent="0.2">
       <c r="A20" s="58">
         <v>19</v>
       </c>
@@ -12908,7 +12911,7 @@
       <c r="U20" s="11"/>
       <c r="V20" s="10"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ns3:dyDescent="0.2">
       <c r="A21" s="58">
         <v>20</v>
       </c>
@@ -12966,7 +12969,7 @@
       <c r="U21" s="11"/>
       <c r="V21" s="10"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ns3:dyDescent="0.2">
       <c r="A22" s="58">
         <v>21</v>
       </c>
@@ -13026,7 +13029,7 @@
       <c r="U22" s="11"/>
       <c r="V22" s="10"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ns3:dyDescent="0.2">
       <c r="A23" s="58">
         <v>22</v>
       </c>
@@ -13086,7 +13089,7 @@
       <c r="U23" s="11"/>
       <c r="V23" s="10"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ns3:dyDescent="0.2">
       <c r="A24" s="58">
         <v>23</v>
       </c>
@@ -13144,7 +13147,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="10"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ns3:dyDescent="0.2">
       <c r="A25" s="58">
         <v>24</v>
       </c>
@@ -13204,7 +13207,7 @@
       <c r="U25" s="11"/>
       <c r="V25" s="10"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ns3:dyDescent="0.2">
       <c r="A26" s="58">
         <v>25</v>
       </c>
@@ -13260,7 +13263,7 @@
       <c r="U26" s="11"/>
       <c r="V26" s="10"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ns3:dyDescent="0.2">
       <c r="A27" s="58">
         <v>26</v>
       </c>
@@ -13316,7 +13319,7 @@
       <c r="U27" s="11"/>
       <c r="V27" s="10"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ns3:dyDescent="0.2">
       <c r="A28" s="58">
         <v>27</v>
       </c>
@@ -13372,7 +13375,7 @@
       <c r="U28" s="11"/>
       <c r="V28" s="10"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ns3:dyDescent="0.2">
       <c r="A29" s="58">
         <v>28</v>
       </c>
@@ -13428,7 +13431,7 @@
       <c r="U29" s="11"/>
       <c r="V29" s="10"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ns3:dyDescent="0.2">
       <c r="A30" s="58">
         <v>29</v>
       </c>
@@ -13488,7 +13491,7 @@
       <c r="U30" s="11"/>
       <c r="V30" s="10"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ns3:dyDescent="0.2">
       <c r="A31" s="58">
         <v>30</v>
       </c>
@@ -13546,7 +13549,7 @@
       <c r="U31" s="11"/>
       <c r="V31" s="10"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ns3:dyDescent="0.2">
       <c r="A32" s="58">
         <v>31</v>
       </c>
@@ -13606,7 +13609,7 @@
       <c r="U32" s="11"/>
       <c r="V32" s="10"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ns3:dyDescent="0.2">
       <c r="A33" s="58">
         <v>32</v>
       </c>
@@ -13666,7 +13669,7 @@
       <c r="U33" s="11"/>
       <c r="V33" s="10"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ns3:dyDescent="0.2">
       <c r="A34" s="58">
         <v>33</v>
       </c>
@@ -13724,7 +13727,7 @@
       <c r="U34" s="11"/>
       <c r="V34" s="10"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ns3:dyDescent="0.2">
       <c r="A35" s="58">
         <v>34</v>
       </c>
@@ -13784,7 +13787,7 @@
       <c r="U35" s="11"/>
       <c r="V35" s="10"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ns3:dyDescent="0.2">
       <c r="A36" s="58">
         <v>35</v>
       </c>
@@ -13842,7 +13845,7 @@
       <c r="U36" s="11"/>
       <c r="V36" s="10"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ns3:dyDescent="0.2">
       <c r="A37" s="58">
         <v>36</v>
       </c>
@@ -13900,7 +13903,7 @@
       <c r="U37" s="11"/>
       <c r="V37" s="10"/>
     </row>
-    <row r="38" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A38" s="58">
         <v>37</v>
       </c>
@@ -13956,7 +13959,7 @@
       <c r="U38" s="11"/>
       <c r="V38" s="10"/>
     </row>
-    <row r="39" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A39" s="58">
         <v>38</v>
       </c>
@@ -14012,7 +14015,7 @@
       <c r="U39" s="11"/>
       <c r="V39" s="10"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" ns3:dyDescent="0.2">
       <c r="A40" s="58">
         <v>39</v>
       </c>
@@ -14072,7 +14075,7 @@
       <c r="U40" s="11"/>
       <c r="V40" s="10"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" ns3:dyDescent="0.2">
       <c r="A41" s="58">
         <v>40</v>
       </c>
@@ -14132,7 +14135,7 @@
       <c r="U41" s="11"/>
       <c r="V41" s="10"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" ns3:dyDescent="0.2">
       <c r="A42" s="58">
         <v>41</v>
       </c>
@@ -14190,7 +14193,7 @@
       <c r="U42" s="11"/>
       <c r="V42" s="10"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" ns3:dyDescent="0.2">
       <c r="A43" s="58">
         <v>42</v>
       </c>
@@ -14248,7 +14251,7 @@
       <c r="U43" s="11"/>
       <c r="V43" s="10"/>
     </row>
-    <row r="44" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A44" s="58">
         <v>43</v>
       </c>
@@ -14306,7 +14309,7 @@
       <c r="U44" s="11"/>
       <c r="V44" s="10"/>
     </row>
-    <row r="45" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A45" s="58">
         <v>44</v>
       </c>
@@ -14364,7 +14367,7 @@
       <c r="U45" s="11"/>
       <c r="V45" s="10"/>
     </row>
-    <row r="46" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A46" s="58">
         <v>45</v>
       </c>
@@ -14422,7 +14425,7 @@
       <c r="U46" s="11"/>
       <c r="V46" s="10"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ns3:dyDescent="0.2">
       <c r="A47" s="58">
         <v>46</v>
       </c>
@@ -14482,7 +14485,7 @@
       <c r="U47" s="11"/>
       <c r="V47" s="10"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ns3:dyDescent="0.2">
       <c r="A48" s="58">
         <v>47</v>
       </c>
@@ -14542,7 +14545,7 @@
       <c r="U48" s="11"/>
       <c r="V48" s="10"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22" ns3:dyDescent="0.2">
       <c r="A49" s="58">
         <v>48</v>
       </c>
@@ -14602,7 +14605,7 @@
       <c r="U49" s="11"/>
       <c r="V49" s="10"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" ns3:dyDescent="0.2">
       <c r="A50" s="58">
         <v>49</v>
       </c>
@@ -14662,7 +14665,7 @@
       <c r="U50" s="11"/>
       <c r="V50" s="10"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22" ns3:dyDescent="0.2">
       <c r="A51" s="58">
         <v>50</v>
       </c>
@@ -14720,7 +14723,7 @@
       <c r="U51" s="11"/>
       <c r="V51" s="10"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" ns3:dyDescent="0.2">
       <c r="A52" s="58">
         <v>51</v>
       </c>
@@ -14778,7 +14781,7 @@
       <c r="U52" s="11"/>
       <c r="V52" s="10"/>
     </row>
-    <row r="53" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A53" s="58">
         <v>52</v>
       </c>
@@ -14838,7 +14841,7 @@
       <c r="U53" s="11"/>
       <c r="V53" s="10"/>
     </row>
-    <row r="54" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A54" s="58">
         <v>53</v>
       </c>
@@ -14898,7 +14901,7 @@
       <c r="U54" s="11"/>
       <c r="V54" s="10"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" ns3:dyDescent="0.2">
       <c r="A55" s="58">
         <v>54</v>
       </c>
@@ -14958,7 +14961,7 @@
       <c r="U55" s="11"/>
       <c r="V55" s="10"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:22" ns3:dyDescent="0.2">
       <c r="A56" s="58">
         <v>55</v>
       </c>
@@ -15018,7 +15021,7 @@
       <c r="U56" s="11"/>
       <c r="V56" s="10"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:22" ns3:dyDescent="0.2">
       <c r="A57" s="58">
         <v>56</v>
       </c>
@@ -15076,7 +15079,7 @@
       <c r="U57" s="11"/>
       <c r="V57" s="10"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" ns3:dyDescent="0.2">
       <c r="A58" s="58">
         <v>57</v>
       </c>
@@ -15134,7 +15137,7 @@
       <c r="U58" s="11"/>
       <c r="V58" s="10"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:22" ns3:dyDescent="0.2">
       <c r="A59" s="58">
         <v>58</v>
       </c>
@@ -15192,7 +15195,7 @@
       <c r="U59" s="11"/>
       <c r="V59" s="10"/>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:22" ns3:dyDescent="0.2">
       <c r="A60" s="58">
         <v>59</v>
       </c>
@@ -15250,7 +15253,7 @@
       <c r="U60" s="11"/>
       <c r="V60" s="10"/>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:22" ns3:dyDescent="0.2">
       <c r="A61" s="58">
         <v>60</v>
       </c>
@@ -15308,7 +15311,7 @@
       <c r="U61" s="11"/>
       <c r="V61" s="10"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:22" ns3:dyDescent="0.2">
       <c r="A62" s="58">
         <v>61</v>
       </c>
@@ -15366,7 +15369,7 @@
       <c r="U62" s="11"/>
       <c r="V62" s="10"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:22" ns3:dyDescent="0.2">
       <c r="A63" s="58">
         <v>62</v>
       </c>
@@ -15426,7 +15429,7 @@
       <c r="U63" s="11"/>
       <c r="V63" s="10"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:22" ns3:dyDescent="0.2">
       <c r="A64" s="58">
         <v>63</v>
       </c>
@@ -15484,7 +15487,7 @@
       <c r="U64" s="11"/>
       <c r="V64" s="10"/>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:22" ns3:dyDescent="0.2">
       <c r="A65" s="58">
         <v>64</v>
       </c>
@@ -15542,7 +15545,7 @@
       <c r="U65" s="11"/>
       <c r="V65" s="10"/>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:22" ns3:dyDescent="0.2">
       <c r="A66" s="58">
         <v>65</v>
       </c>
@@ -15600,7 +15603,7 @@
       <c r="U66" s="11"/>
       <c r="V66" s="10"/>
     </row>
-    <row r="67" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A67" s="58">
         <v>66</v>
       </c>
@@ -15658,7 +15661,7 @@
       <c r="U67" s="11"/>
       <c r="V67" s="10"/>
     </row>
-    <row r="68" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A68" s="58">
         <v>67</v>
       </c>
@@ -15716,7 +15719,7 @@
       <c r="U68" s="11"/>
       <c r="V68" s="10"/>
     </row>
-    <row r="69" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A69" s="58">
         <v>68</v>
       </c>
@@ -15774,7 +15777,7 @@
       <c r="U69" s="11"/>
       <c r="V69" s="10"/>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:22" ns3:dyDescent="0.2">
       <c r="A70" s="58">
         <v>69</v>
       </c>
@@ -15832,7 +15835,7 @@
       <c r="U70" s="11"/>
       <c r="V70" s="10"/>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:22" ns3:dyDescent="0.2">
       <c r="A71" s="58">
         <v>70</v>
       </c>
@@ -15890,7 +15893,7 @@
       <c r="U71" s="11"/>
       <c r="V71" s="10"/>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:22" ns3:dyDescent="0.2">
       <c r="A72" s="58">
         <v>71</v>
       </c>
@@ -15948,7 +15951,7 @@
       <c r="U72" s="11"/>
       <c r="V72" s="10"/>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:22" ns3:dyDescent="0.2">
       <c r="A73" s="58">
         <v>72</v>
       </c>
@@ -16008,7 +16011,7 @@
       <c r="U73" s="11"/>
       <c r="V73" s="10"/>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:22" ns3:dyDescent="0.2">
       <c r="A74" s="58">
         <v>73</v>
       </c>
@@ -16068,7 +16071,7 @@
       <c r="U74" s="11"/>
       <c r="V74" s="10"/>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:22" ns3:dyDescent="0.2">
       <c r="A75" s="58">
         <v>74</v>
       </c>
@@ -16128,7 +16131,7 @@
       <c r="U75" s="11"/>
       <c r="V75" s="10"/>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:22" ns3:dyDescent="0.2">
       <c r="A76" s="58">
         <v>75</v>
       </c>
@@ -16188,7 +16191,7 @@
       <c r="U76" s="11"/>
       <c r="V76" s="10"/>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:22" ns3:dyDescent="0.2">
       <c r="A77" s="58">
         <v>76</v>
       </c>
@@ -16248,7 +16251,7 @@
       <c r="U77" s="11"/>
       <c r="V77" s="10"/>
     </row>
-    <row r="78" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A78" s="58">
         <v>77</v>
       </c>
@@ -16306,7 +16309,7 @@
       <c r="U78" s="11"/>
       <c r="V78" s="10"/>
     </row>
-    <row r="79" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A79" s="58">
         <v>78</v>
       </c>
@@ -16364,7 +16367,7 @@
       <c r="U79" s="11"/>
       <c r="V79" s="10"/>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:22" ns3:dyDescent="0.2">
       <c r="A80" s="58">
         <v>79</v>
       </c>
@@ -16424,7 +16427,7 @@
       <c r="U80" s="11"/>
       <c r="V80" s="10"/>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:22" ns3:dyDescent="0.2">
       <c r="A81" s="58">
         <v>80</v>
       </c>
@@ -16484,7 +16487,7 @@
       <c r="U81" s="11"/>
       <c r="V81" s="10"/>
     </row>
-    <row r="82" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:22" ht="32" customHeight="1" ns3:dyDescent="0.2">
       <c r="A82" s="58">
         <v>81</v>
       </c>
@@ -16544,7 +16547,7 @@
       <c r="U82" s="11"/>
       <c r="V82" s="10"/>
     </row>
-    <row r="83" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:22" ht="32" customHeight="1" ns3:dyDescent="0.2">
       <c r="A83" s="58">
         <v>82</v>
       </c>
@@ -16604,7 +16607,7 @@
       <c r="U83" s="11"/>
       <c r="V83" s="10"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:22" ns3:dyDescent="0.2">
       <c r="A84" s="61">
         <v>83</v>
       </c>
@@ -16664,7 +16667,7 @@
       <c r="U84" s="11"/>
       <c r="V84" s="10"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:22" ns3:dyDescent="0.2">
       <c r="A85" s="61">
         <v>84</v>
       </c>
@@ -16724,7 +16727,7 @@
       <c r="U85" s="11"/>
       <c r="V85" s="10"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:22" ns3:dyDescent="0.2">
       <c r="A86" s="61">
         <v>85</v>
       </c>
@@ -16784,7 +16787,7 @@
       <c r="U86" s="11"/>
       <c r="V86" s="10"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:22" ns3:dyDescent="0.2">
       <c r="A87" s="61">
         <v>86</v>
       </c>
@@ -16842,7 +16845,7 @@
       <c r="U87" s="11"/>
       <c r="V87" s="10"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:22" ns3:dyDescent="0.2">
       <c r="A88" s="61">
         <v>87</v>
       </c>
@@ -16902,7 +16905,7 @@
       <c r="U88" s="11"/>
       <c r="V88" s="10"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:22" ns3:dyDescent="0.2">
       <c r="A89" s="58">
         <v>88</v>
       </c>
@@ -16960,7 +16963,7 @@
       <c r="U89" s="11"/>
       <c r="V89" s="10"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:22" ns3:dyDescent="0.2">
       <c r="A90" s="58">
         <v>89</v>
       </c>
@@ -17018,7 +17021,7 @@
       <c r="U90" s="11"/>
       <c r="V90" s="10"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:22" ns3:dyDescent="0.2">
       <c r="A91" s="61">
         <v>90</v>
       </c>
@@ -17076,7 +17079,7 @@
       <c r="U91" s="11"/>
       <c r="V91" s="10"/>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:22" ns3:dyDescent="0.2">
       <c r="A92" s="61">
         <v>91</v>
       </c>
@@ -17136,7 +17139,7 @@
       <c r="U92" s="11"/>
       <c r="V92" s="10"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:22" ns3:dyDescent="0.2">
       <c r="A93" s="58">
         <v>92</v>
       </c>
@@ -17192,7 +17195,7 @@
       <c r="U93" s="11"/>
       <c r="V93" s="10"/>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:22" ns3:dyDescent="0.2">
       <c r="A94" s="58">
         <v>93</v>
       </c>
@@ -17248,7 +17251,7 @@
       <c r="U94" s="11"/>
       <c r="V94" s="10"/>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:22" ns3:dyDescent="0.2">
       <c r="A95" s="58">
         <v>94</v>
       </c>
@@ -17304,7 +17307,7 @@
       <c r="U95" s="11"/>
       <c r="V95" s="10"/>
     </row>
-    <row r="96" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A96" s="58">
         <v>95</v>
       </c>
@@ -17364,7 +17367,7 @@
       <c r="U96" s="11"/>
       <c r="V96" s="10"/>
     </row>
-    <row r="97" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A97" s="61">
         <v>96</v>
       </c>
@@ -17422,7 +17425,7 @@
       <c r="U97" s="11"/>
       <c r="V97" s="10"/>
     </row>
-    <row r="98" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A98" s="61">
         <v>97</v>
       </c>
@@ -17482,7 +17485,7 @@
       </c>
       <c r="V98" s="10"/>
     </row>
-    <row r="99" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A99" s="58">
         <v>98</v>
       </c>
@@ -17539,7 +17542,7 @@
       <c r="T99" s="10"/>
       <c r="V99" s="10"/>
     </row>
-    <row r="100" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A100" s="58">
         <v>99</v>
       </c>
@@ -17599,7 +17602,7 @@
       </c>
       <c r="V100" s="10"/>
     </row>
-    <row r="101" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A101" s="61">
         <v>100</v>
       </c>
@@ -17659,7 +17662,7 @@
       </c>
       <c r="V101" s="10"/>
     </row>
-    <row r="102" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A102" s="61">
         <v>101</v>
       </c>
@@ -17719,7 +17722,7 @@
       </c>
       <c r="V102" s="10"/>
     </row>
-    <row r="103" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A103" s="61">
         <v>102</v>
       </c>
@@ -17778,7 +17781,7 @@
       </c>
       <c r="V103" s="10"/>
     </row>
-    <row r="104" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A104" s="61">
         <v>103</v>
       </c>
@@ -17837,7 +17840,7 @@
       </c>
       <c r="V104" s="10"/>
     </row>
-    <row r="105" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A105" s="61">
         <v>104</v>
       </c>
@@ -17896,7 +17899,7 @@
       </c>
       <c r="V105" s="10"/>
     </row>
-    <row r="106" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A106" s="61">
         <v>105</v>
       </c>
@@ -17955,7 +17958,7 @@
       </c>
       <c r="V106" s="10"/>
     </row>
-    <row r="107" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A107" s="61">
         <v>106</v>
       </c>
@@ -18014,7 +18017,7 @@
       </c>
       <c r="V107" s="10"/>
     </row>
-    <row r="108" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A108" s="61">
         <v>107</v>
       </c>
@@ -18074,7 +18077,7 @@
       </c>
       <c r="V108" s="10"/>
     </row>
-    <row r="109" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A109" s="61">
         <v>108</v>
       </c>
@@ -18134,7 +18137,7 @@
       </c>
       <c r="V109" s="10"/>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:22" ns3:dyDescent="0.2">
       <c r="A110" s="58">
         <v>109</v>
       </c>
@@ -18192,7 +18195,7 @@
       <c r="U110" s="11"/>
       <c r="V110" s="10"/>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:22" ns3:dyDescent="0.2">
       <c r="A111" s="58">
         <v>110</v>
       </c>
@@ -18250,7 +18253,7 @@
       <c r="U111" s="11"/>
       <c r="V111" s="10"/>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:22" ns3:dyDescent="0.2">
       <c r="A112" s="61">
         <v>111</v>
       </c>
@@ -18310,7 +18313,7 @@
       <c r="U112" s="11"/>
       <c r="V112" s="10"/>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:22" ns3:dyDescent="0.2">
       <c r="A113" s="61">
         <v>112</v>
       </c>
@@ -18370,7 +18373,7 @@
       <c r="U113" s="11"/>
       <c r="V113" s="10"/>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:22" ns3:dyDescent="0.2">
       <c r="A114" s="61">
         <v>113</v>
       </c>
@@ -18428,7 +18431,7 @@
       <c r="U114" s="11"/>
       <c r="V114" s="10"/>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:22" ns3:dyDescent="0.2">
       <c r="A115" s="61">
         <v>114</v>
       </c>
@@ -18486,7 +18489,7 @@
       <c r="U115" s="11"/>
       <c r="V115" s="10"/>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:22" ns3:dyDescent="0.2">
       <c r="A116" s="61">
         <v>115</v>
       </c>
@@ -18544,7 +18547,7 @@
       <c r="U116" s="11"/>
       <c r="V116" s="10"/>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:22" ns3:dyDescent="0.2">
       <c r="A117" s="61">
         <v>116</v>
       </c>
@@ -18602,7 +18605,7 @@
       <c r="U117" s="11"/>
       <c r="V117" s="10"/>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:22" ns3:dyDescent="0.2">
       <c r="A118" s="61">
         <v>117</v>
       </c>
@@ -18660,7 +18663,7 @@
       <c r="U118" s="11"/>
       <c r="V118" s="10"/>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:22" ns3:dyDescent="0.2">
       <c r="A119" s="61">
         <v>118</v>
       </c>
@@ -18718,7 +18721,7 @@
       <c r="U119" s="11"/>
       <c r="V119" s="10"/>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:22" ns3:dyDescent="0.2">
       <c r="A120" s="61">
         <v>119</v>
       </c>
@@ -18776,7 +18779,7 @@
       <c r="U120" s="11"/>
       <c r="V120" s="10"/>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:22" ns3:dyDescent="0.2">
       <c r="A121" s="61">
         <v>120</v>
       </c>
@@ -18834,7 +18837,7 @@
       <c r="U121" s="11"/>
       <c r="V121" s="10"/>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:22" ns3:dyDescent="0.2">
       <c r="A122" s="61">
         <v>121</v>
       </c>
@@ -18894,7 +18897,7 @@
       <c r="U122" s="11"/>
       <c r="V122" s="10"/>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:22" ns3:dyDescent="0.2">
       <c r="A123" s="61">
         <v>122</v>
       </c>
@@ -18954,7 +18957,7 @@
       <c r="U123" s="11"/>
       <c r="V123" s="10"/>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:22" ns3:dyDescent="0.2">
       <c r="A124" s="61">
         <v>123</v>
       </c>
@@ -19014,7 +19017,7 @@
       <c r="U124" s="11"/>
       <c r="V124" s="10"/>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:22" ns3:dyDescent="0.2">
       <c r="A125" s="61">
         <v>124</v>
       </c>
@@ -19074,7 +19077,7 @@
       <c r="U125" s="11"/>
       <c r="V125" s="10"/>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:22" ns3:dyDescent="0.2">
       <c r="A126" s="61">
         <v>125</v>
       </c>
@@ -19130,7 +19133,7 @@
       <c r="U126" s="11"/>
       <c r="V126" s="10"/>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:22" ns3:dyDescent="0.2">
       <c r="A127" s="61">
         <v>126</v>
       </c>
@@ -19186,7 +19189,7 @@
       <c r="U127" s="11"/>
       <c r="V127" s="10"/>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:22" ns3:dyDescent="0.2">
       <c r="A128" s="61">
         <v>127</v>
       </c>
@@ -19244,7 +19247,7 @@
       <c r="U128" s="11"/>
       <c r="V128" s="10"/>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:22" ns3:dyDescent="0.2">
       <c r="A129" s="61">
         <v>128</v>
       </c>
@@ -19302,7 +19305,7 @@
       <c r="U129" s="11"/>
       <c r="V129" s="10"/>
     </row>
-    <row r="130" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A130" s="58">
         <v>129</v>
       </c>
@@ -19358,7 +19361,7 @@
       <c r="U130" s="11"/>
       <c r="V130" s="10"/>
     </row>
-    <row r="131" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A131" s="58">
         <v>130</v>
       </c>
@@ -19416,7 +19419,7 @@
       <c r="U131" s="11"/>
       <c r="V131" s="10"/>
     </row>
-    <row r="132" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A132" s="58">
         <v>131</v>
       </c>
@@ -19476,7 +19479,7 @@
       <c r="U132" s="11"/>
       <c r="V132" s="10"/>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:22" ns3:dyDescent="0.2">
       <c r="A133" s="58">
         <v>132</v>
       </c>
@@ -19532,7 +19535,7 @@
       <c r="U133" s="11"/>
       <c r="V133" s="10"/>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:22" ns3:dyDescent="0.2">
       <c r="A134" s="61">
         <v>133</v>
       </c>
@@ -19588,7 +19591,7 @@
       <c r="U134" s="11"/>
       <c r="V134" s="10"/>
     </row>
-    <row r="135" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A135" s="58">
         <v>134</v>
       </c>
@@ -19644,7 +19647,7 @@
       <c r="U135" s="11"/>
       <c r="V135" s="10"/>
     </row>
-    <row r="136" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A136" s="58">
         <v>135</v>
       </c>
@@ -19700,7 +19703,7 @@
       <c r="U136" s="11"/>
       <c r="V136" s="10"/>
     </row>
-    <row r="137" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A137" s="58">
         <v>136</v>
       </c>
@@ -19756,7 +19759,7 @@
       <c r="U137" s="11"/>
       <c r="V137" s="10"/>
     </row>
-    <row r="138" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A138" s="58">
         <v>137</v>
       </c>
@@ -19814,7 +19817,7 @@
       <c r="U138" s="11"/>
       <c r="V138" s="10"/>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:22" ns3:dyDescent="0.2">
       <c r="A139" s="58">
         <v>138</v>
       </c>
@@ -19874,7 +19877,7 @@
       <c r="U139" s="11"/>
       <c r="V139" s="10"/>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:22" ns3:dyDescent="0.2">
       <c r="A140" s="58">
         <v>139</v>
       </c>
@@ -19934,7 +19937,7 @@
       <c r="U140" s="11"/>
       <c r="V140" s="10"/>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:22" ns3:dyDescent="0.2">
       <c r="A141" s="58">
         <v>140</v>
       </c>
@@ -19994,7 +19997,7 @@
       <c r="U141" s="11"/>
       <c r="V141" s="10"/>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:22" ns3:dyDescent="0.2">
       <c r="A142" s="58">
         <v>141</v>
       </c>
@@ -20054,7 +20057,7 @@
       <c r="U142" s="11"/>
       <c r="V142" s="10"/>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:22" ns3:dyDescent="0.2">
       <c r="A143" s="58">
         <v>142</v>
       </c>
@@ -20114,7 +20117,7 @@
       <c r="U143" s="11"/>
       <c r="V143" s="10"/>
     </row>
-    <row r="144" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A144" s="61">
         <v>143</v>
       </c>
@@ -20172,7 +20175,7 @@
       <c r="U144" s="11"/>
       <c r="V144" s="10"/>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:22" ns3:dyDescent="0.2">
       <c r="A145" s="58">
         <v>144</v>
       </c>
@@ -20230,7 +20233,7 @@
       <c r="U145" s="11"/>
       <c r="V145" s="10"/>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:22" ns3:dyDescent="0.2">
       <c r="A146" s="58">
         <v>145</v>
       </c>
@@ -20288,7 +20291,7 @@
       <c r="U146" s="11"/>
       <c r="V146" s="10"/>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:22" ns3:dyDescent="0.2">
       <c r="A147" s="58">
         <v>146</v>
       </c>
@@ -20346,7 +20349,7 @@
       <c r="U147" s="11"/>
       <c r="V147" s="10"/>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:22" ns3:dyDescent="0.2">
       <c r="A148" s="58">
         <v>147</v>
       </c>
@@ -20402,7 +20405,7 @@
       <c r="U148" s="11"/>
       <c r="V148" s="10"/>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:22" ns3:dyDescent="0.2">
       <c r="A149" s="58">
         <v>148</v>
       </c>
@@ -20458,7 +20461,7 @@
       <c r="U149" s="11"/>
       <c r="V149" s="10"/>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:22" ns3:dyDescent="0.2">
       <c r="A150" s="58">
         <v>149</v>
       </c>
@@ -20516,7 +20519,7 @@
       <c r="U150" s="11"/>
       <c r="V150" s="10"/>
     </row>
-    <row r="151" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A151" s="58">
         <v>150</v>
       </c>
@@ -20572,7 +20575,7 @@
       <c r="U151" s="11"/>
       <c r="V151" s="10"/>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:22" ns3:dyDescent="0.2">
       <c r="A152" s="58">
         <v>151</v>
       </c>
@@ -20626,7 +20629,7 @@
       <c r="U152" s="11"/>
       <c r="V152" s="10"/>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:22" ns3:dyDescent="0.2">
       <c r="A153" s="58">
         <v>152</v>
       </c>
@@ -20682,7 +20685,7 @@
       <c r="U153" s="11"/>
       <c r="V153" s="10"/>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:22" ns3:dyDescent="0.2">
       <c r="A154" s="58">
         <v>153</v>
       </c>
@@ -20738,7 +20741,7 @@
       <c r="U154" s="11"/>
       <c r="V154" s="10"/>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:22" ns3:dyDescent="0.2">
       <c r="A155" s="58">
         <v>154</v>
       </c>
@@ -20796,7 +20799,7 @@
       <c r="U155" s="11"/>
       <c r="V155" s="10"/>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:22" ns3:dyDescent="0.2">
       <c r="A156" s="58">
         <v>155</v>
       </c>
@@ -20852,7 +20855,7 @@
       <c r="U156" s="11"/>
       <c r="V156" s="10"/>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:22" ns3:dyDescent="0.2">
       <c r="A157" s="58">
         <v>156</v>
       </c>
@@ -20908,7 +20911,7 @@
       <c r="U157" s="11"/>
       <c r="V157" s="10"/>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:22" ns3:dyDescent="0.2">
       <c r="A158" s="58">
         <v>157</v>
       </c>
@@ -20966,7 +20969,7 @@
       <c r="U158" s="11"/>
       <c r="V158" s="10"/>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:22" ns3:dyDescent="0.2">
       <c r="A159" s="58">
         <v>158</v>
       </c>
@@ -21022,7 +21025,7 @@
       <c r="U159" s="11"/>
       <c r="V159" s="10"/>
     </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:22" ns3:dyDescent="0.2">
       <c r="A160" s="58">
         <v>159</v>
       </c>
@@ -21078,7 +21081,7 @@
       <c r="U160" s="11"/>
       <c r="V160" s="10"/>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:22" ns3:dyDescent="0.2">
       <c r="A161" s="58">
         <v>160</v>
       </c>
@@ -21136,7 +21139,7 @@
       <c r="U161" s="11"/>
       <c r="V161" s="10"/>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:22" ns3:dyDescent="0.2">
       <c r="A162" s="61">
         <v>161</v>
       </c>
@@ -21194,7 +21197,7 @@
       <c r="U162" s="11"/>
       <c r="V162" s="10"/>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:22" ns3:dyDescent="0.2">
       <c r="A163" s="61">
         <v>162</v>
       </c>
@@ -21252,7 +21255,7 @@
       <c r="U163" s="11"/>
       <c r="V163" s="10"/>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:22" ns3:dyDescent="0.2">
       <c r="A164" s="58">
         <v>163</v>
       </c>
@@ -21312,7 +21315,7 @@
       <c r="U164" s="11"/>
       <c r="V164" s="10"/>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:22" ns3:dyDescent="0.2">
       <c r="A165" s="58">
         <v>164</v>
       </c>
@@ -21372,7 +21375,7 @@
       <c r="U165" s="11"/>
       <c r="V165" s="10"/>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:22" ns3:dyDescent="0.2">
       <c r="A166" s="58">
         <v>165</v>
       </c>
@@ -21432,7 +21435,7 @@
       <c r="U166" s="11"/>
       <c r="V166" s="10"/>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:22" ns3:dyDescent="0.2">
       <c r="A167" s="58">
         <v>166</v>
       </c>
@@ -21492,7 +21495,7 @@
       <c r="U167" s="11"/>
       <c r="V167" s="10"/>
     </row>
-    <row r="168" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A168" s="58">
         <v>167</v>
       </c>
@@ -21552,7 +21555,7 @@
       <c r="U168" s="11"/>
       <c r="V168" s="10"/>
     </row>
-    <row r="169" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A169" s="58">
         <v>168</v>
       </c>
@@ -21614,7 +21617,7 @@
       <c r="U169" s="11"/>
       <c r="V169" s="10"/>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:22" ns3:dyDescent="0.2">
       <c r="A170" s="58">
         <v>169</v>
       </c>
@@ -21674,7 +21677,7 @@
       <c r="U170" s="11"/>
       <c r="V170" s="10"/>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:22" ns3:dyDescent="0.2">
       <c r="A171" s="58">
         <v>170</v>
       </c>
@@ -21736,7 +21739,7 @@
       <c r="U171" s="11"/>
       <c r="V171" s="10"/>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:22" ns3:dyDescent="0.2">
       <c r="A172" s="58">
         <v>171</v>
       </c>
@@ -21798,7 +21801,7 @@
       <c r="U172" s="11"/>
       <c r="V172" s="10"/>
     </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:22" ns3:dyDescent="0.2">
       <c r="A173" s="61">
         <v>172</v>
       </c>
@@ -21856,7 +21859,7 @@
       <c r="U173" s="11"/>
       <c r="V173" s="10"/>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:22" ns3:dyDescent="0.2">
       <c r="A174" s="61">
         <v>173</v>
       </c>
@@ -21913,7 +21916,7 @@
       <c r="U174" s="11"/>
       <c r="V174" s="10"/>
     </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:22" ns3:dyDescent="0.2">
       <c r="A175" s="61">
         <v>174</v>
       </c>
@@ -21973,7 +21976,7 @@
       <c r="U175" s="11"/>
       <c r="V175" s="10"/>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:22" ns3:dyDescent="0.2">
       <c r="A176" s="61">
         <v>175</v>
       </c>
@@ -22031,7 +22034,7 @@
       <c r="U176" s="11"/>
       <c r="V176" s="10"/>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:22" ns3:dyDescent="0.2">
       <c r="A177" s="61">
         <v>176</v>
       </c>
@@ -22091,7 +22094,7 @@
       <c r="U177" s="11"/>
       <c r="V177" s="10"/>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:22" ns3:dyDescent="0.2">
       <c r="A178" s="58">
         <v>177</v>
       </c>
@@ -22151,7 +22154,7 @@
       <c r="U178" s="11"/>
       <c r="V178" s="10"/>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:22" ns3:dyDescent="0.2">
       <c r="A179" s="58">
         <v>178</v>
       </c>
@@ -22211,7 +22214,7 @@
       <c r="U179" s="11"/>
       <c r="V179" s="10"/>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:22" ns3:dyDescent="0.2">
       <c r="A180" s="58">
         <v>179</v>
       </c>
@@ -22269,7 +22272,7 @@
       <c r="U180" s="11"/>
       <c r="V180" s="10"/>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:22" ns3:dyDescent="0.2">
       <c r="A181" s="58">
         <v>180</v>
       </c>
@@ -22327,7 +22330,7 @@
       <c r="U181" s="11"/>
       <c r="V181" s="10"/>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:22" ns3:dyDescent="0.2">
       <c r="A182" s="58">
         <v>181</v>
       </c>
@@ -22385,7 +22388,7 @@
       <c r="U182" s="11"/>
       <c r="V182" s="10"/>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:22" ns3:dyDescent="0.2">
       <c r="A183" s="61">
         <v>182</v>
       </c>
@@ -22441,7 +22444,7 @@
       <c r="U183" s="11"/>
       <c r="V183" s="10"/>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:22" ns3:dyDescent="0.2">
       <c r="A184" s="61">
         <v>183</v>
       </c>
@@ -22501,7 +22504,7 @@
       <c r="U184" s="11"/>
       <c r="V184" s="10"/>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:22" ns3:dyDescent="0.2">
       <c r="A185" s="61">
         <v>184</v>
       </c>
@@ -22561,7 +22564,7 @@
       <c r="U185" s="11"/>
       <c r="V185" s="10"/>
     </row>
-    <row r="186" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A186" s="58">
         <v>185</v>
       </c>
@@ -22621,7 +22624,7 @@
       <c r="U186" s="11"/>
       <c r="V186" s="10"/>
     </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:22" ns3:dyDescent="0.2">
       <c r="A187" s="58">
         <v>186</v>
       </c>
@@ -22679,7 +22682,7 @@
       <c r="U187" s="11"/>
       <c r="V187" s="10"/>
     </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:22" ns3:dyDescent="0.2">
       <c r="A188" s="58">
         <v>187</v>
       </c>
@@ -22739,7 +22742,7 @@
       <c r="U188" s="11"/>
       <c r="V188" s="10"/>
     </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:22" ns3:dyDescent="0.2">
       <c r="A189" s="58">
         <v>188</v>
       </c>
@@ -22799,7 +22802,7 @@
       <c r="U189" s="11"/>
       <c r="V189" s="10"/>
     </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:22" ns3:dyDescent="0.2">
       <c r="A190" s="58">
         <v>189</v>
       </c>
@@ -22859,7 +22862,7 @@
       <c r="U190" s="11"/>
       <c r="V190" s="10"/>
     </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:22" ns3:dyDescent="0.2">
       <c r="A191" s="58">
         <v>190</v>
       </c>
@@ -22917,7 +22920,7 @@
       <c r="U191" s="11"/>
       <c r="V191" s="10"/>
     </row>
-    <row r="192" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A192" s="58">
         <v>191</v>
       </c>
@@ -22975,7 +22978,7 @@
       <c r="U192" s="11"/>
       <c r="V192" s="10"/>
     </row>
-    <row r="193" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A193" s="58">
         <v>192</v>
       </c>
@@ -23033,7 +23036,7 @@
       <c r="U193" s="11"/>
       <c r="V193" s="10"/>
     </row>
-    <row r="194" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A194" s="58">
         <v>193</v>
       </c>
@@ -23093,7 +23096,7 @@
       <c r="U194" s="11"/>
       <c r="V194" s="10"/>
     </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:22" ns3:dyDescent="0.2">
       <c r="A195" s="58">
         <v>194</v>
       </c>
@@ -23153,7 +23156,7 @@
       <c r="U195" s="11"/>
       <c r="V195" s="10"/>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:22" ns3:dyDescent="0.2">
       <c r="A196" s="58">
         <v>195</v>
       </c>
@@ -23213,7 +23216,7 @@
       <c r="U196" s="11"/>
       <c r="V196" s="10"/>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:22" ns3:dyDescent="0.2">
       <c r="A197" s="58">
         <v>196</v>
       </c>
@@ -23269,7 +23272,7 @@
       <c r="U197" s="11"/>
       <c r="V197" s="10"/>
     </row>
-    <row r="198" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A198" s="58">
         <v>197</v>
       </c>
@@ -23325,7 +23328,7 @@
       <c r="U198" s="11"/>
       <c r="V198" s="10"/>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:22" ns3:dyDescent="0.2">
       <c r="A199" s="61">
         <v>198</v>
       </c>
@@ -23385,7 +23388,7 @@
       <c r="U199" s="11"/>
       <c r="V199" s="10"/>
     </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:22" ns3:dyDescent="0.2">
       <c r="A200" s="61">
         <v>199</v>
       </c>
@@ -23445,7 +23448,7 @@
       <c r="U200" s="11"/>
       <c r="V200" s="10"/>
     </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:22" ns3:dyDescent="0.2">
       <c r="A201" s="58">
         <v>200</v>
       </c>
@@ -23499,7 +23502,7 @@
       <c r="U201" s="11"/>
       <c r="V201" s="10"/>
     </row>
-    <row r="202" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A202" s="58">
         <v>201</v>
       </c>
@@ -23553,7 +23556,7 @@
       <c r="U202" s="11"/>
       <c r="V202" s="10"/>
     </row>
-    <row r="203" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A203" s="61">
         <v>202</v>
       </c>
@@ -23607,7 +23610,7 @@
       <c r="U203" s="11"/>
       <c r="V203" s="10"/>
     </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:22" ns3:dyDescent="0.2">
       <c r="A204" s="61">
         <v>203</v>
       </c>
@@ -23667,7 +23670,7 @@
       <c r="U204" s="11"/>
       <c r="V204" s="10"/>
     </row>
-    <row r="205" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A205" s="58">
         <v>204</v>
       </c>
@@ -23723,7 +23726,7 @@
       <c r="U205" s="11"/>
       <c r="V205" s="10"/>
     </row>
-    <row r="206" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A206" s="58">
         <v>205</v>
       </c>
@@ -23781,7 +23784,7 @@
       <c r="U206" s="11"/>
       <c r="V206" s="10"/>
     </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:22" ns3:dyDescent="0.2">
       <c r="A207" s="58">
         <v>206</v>
       </c>
@@ -23839,7 +23842,7 @@
       <c r="U207" s="11"/>
       <c r="V207" s="10"/>
     </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:22" ns3:dyDescent="0.2">
       <c r="A208" s="58">
         <v>207</v>
       </c>
@@ -23899,7 +23902,7 @@
       <c r="U208" s="11"/>
       <c r="V208" s="10"/>
     </row>
-    <row r="209" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A209" s="58">
         <v>208</v>
       </c>
@@ -23959,7 +23962,7 @@
       <c r="U209" s="11"/>
       <c r="V209" s="10"/>
     </row>
-    <row r="210" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A210" s="58">
         <v>209</v>
       </c>
@@ -24017,7 +24020,7 @@
       <c r="U210" s="11"/>
       <c r="V210" s="10"/>
     </row>
-    <row r="211" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A211" s="58">
         <v>210</v>
       </c>
@@ -24077,7 +24080,7 @@
       <c r="U211" s="11"/>
       <c r="V211" s="10"/>
     </row>
-    <row r="212" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:22" ns3:dyDescent="0.2">
       <c r="A212" s="61">
         <v>211</v>
       </c>
@@ -24137,7 +24140,7 @@
       <c r="U212" s="11"/>
       <c r="V212" s="10"/>
     </row>
-    <row r="213" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:22" ns3:dyDescent="0.2">
       <c r="A213" s="61">
         <v>212</v>
       </c>
@@ -24197,7 +24200,7 @@
       <c r="U213" s="11"/>
       <c r="V213" s="10"/>
     </row>
-    <row r="214" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A214" s="58">
         <v>213</v>
       </c>
@@ -24257,7 +24260,7 @@
       <c r="U214" s="11"/>
       <c r="V214" s="10"/>
     </row>
-    <row r="215" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:22" ns3:dyDescent="0.2">
       <c r="A215" s="61">
         <v>214</v>
       </c>
@@ -24317,7 +24320,7 @@
       <c r="U215" s="11"/>
       <c r="V215" s="10"/>
     </row>
-    <row r="216" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:22" ns3:dyDescent="0.2">
       <c r="A216" s="61">
         <v>215</v>
       </c>
@@ -24377,7 +24380,7 @@
       <c r="U216" s="11"/>
       <c r="V216" s="10"/>
     </row>
-    <row r="217" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:22" ns3:dyDescent="0.2">
       <c r="A217" s="61">
         <v>216</v>
       </c>
@@ -24435,7 +24438,7 @@
       <c r="U217" s="11"/>
       <c r="V217" s="10"/>
     </row>
-    <row r="218" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:22" ns3:dyDescent="0.2">
       <c r="A218" s="61">
         <v>217</v>
       </c>
@@ -24493,7 +24496,7 @@
       <c r="U218" s="11"/>
       <c r="V218" s="10"/>
     </row>
-    <row r="219" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A219" s="61">
         <v>218</v>
       </c>
@@ -24553,7 +24556,7 @@
       </c>
       <c r="V219" s="10"/>
     </row>
-    <row r="220" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A220" s="61">
         <v>219</v>
       </c>
@@ -24612,7 +24615,7 @@
       <c r="T220" s="10"/>
       <c r="V220" s="10"/>
     </row>
-    <row r="221" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A221" s="61">
         <v>220</v>
       </c>
@@ -24674,7 +24677,7 @@
       </c>
       <c r="V221" s="10"/>
     </row>
-    <row r="222" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A222" s="61">
         <v>221</v>
       </c>
@@ -24736,7 +24739,7 @@
       </c>
       <c r="V222" s="10"/>
     </row>
-    <row r="223" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A223" s="61">
         <v>222</v>
       </c>
@@ -24798,7 +24801,7 @@
       </c>
       <c r="V223" s="10"/>
     </row>
-    <row r="224" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A224" s="58">
         <v>223</v>
       </c>
@@ -24858,7 +24861,7 @@
       </c>
       <c r="V224" s="10"/>
     </row>
-    <row r="225" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A225" s="58">
         <v>224</v>
       </c>
@@ -24918,7 +24921,7 @@
       </c>
       <c r="V225" s="10"/>
     </row>
-    <row r="226" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A226" s="61">
         <v>225</v>
       </c>
@@ -24982,7 +24985,7 @@
       </c>
       <c r="V226" s="10"/>
     </row>
-    <row r="227" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A227" s="61">
         <v>226</v>
       </c>
@@ -25046,7 +25049,7 @@
       </c>
       <c r="V227" s="10"/>
     </row>
-    <row r="228" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:22" ns3:dyDescent="0.2">
       <c r="A228" s="61">
         <v>227</v>
       </c>
@@ -25108,7 +25111,7 @@
       <c r="U228" s="11"/>
       <c r="V228" s="10"/>
     </row>
-    <row r="229" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A229" s="58">
         <v>228</v>
       </c>
@@ -25170,7 +25173,7 @@
       <c r="U229" s="11"/>
       <c r="V229" s="10"/>
     </row>
-    <row r="230" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A230" s="58">
         <v>229</v>
       </c>
@@ -25232,7 +25235,7 @@
       <c r="U230" s="11"/>
       <c r="V230" s="10"/>
     </row>
-    <row r="231" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:22" ns3:dyDescent="0.2">
       <c r="A231" s="61">
         <v>230</v>
       </c>
@@ -25291,7 +25294,7 @@
       <c r="U231" s="11"/>
       <c r="V231" s="10"/>
     </row>
-    <row r="232" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A232" s="58">
         <v>231</v>
       </c>
@@ -25346,7 +25349,7 @@
       <c r="U232" s="11"/>
       <c r="V232" s="10"/>
     </row>
-    <row r="233" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A233" s="58">
         <v>232</v>
       </c>
@@ -25401,7 +25404,7 @@
       <c r="U233" s="11"/>
       <c r="V233" s="10"/>
     </row>
-    <row r="234" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A234" s="58">
         <v>233</v>
       </c>
@@ -25458,7 +25461,7 @@
       <c r="U234" s="11"/>
       <c r="V234" s="10"/>
     </row>
-    <row r="235" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:22" ns3:dyDescent="0.2">
       <c r="A235" s="61">
         <v>234</v>
       </c>
@@ -25515,7 +25518,7 @@
       <c r="U235" s="11"/>
       <c r="V235" s="10"/>
     </row>
-    <row r="236" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:22" ns3:dyDescent="0.2">
       <c r="A236" s="61">
         <v>235</v>
       </c>
@@ -25573,7 +25576,7 @@
       <c r="U236" s="11"/>
       <c r="V236" s="10"/>
     </row>
-    <row r="237" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:22" ns3:dyDescent="0.2">
       <c r="A237" s="61">
         <v>236</v>
       </c>
@@ -25629,7 +25632,7 @@
       <c r="U237" s="11"/>
       <c r="V237" s="10"/>
     </row>
-    <row r="238" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:22" ns3:dyDescent="0.2">
       <c r="A238" s="61">
         <v>237</v>
       </c>
@@ -25687,7 +25690,7 @@
       <c r="U238" s="11"/>
       <c r="V238" s="10"/>
     </row>
-    <row r="239" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:22" ns3:dyDescent="0.2">
       <c r="A239" s="61">
         <v>238</v>
       </c>
@@ -25747,7 +25750,7 @@
       <c r="U239" s="11"/>
       <c r="V239" s="10"/>
     </row>
-    <row r="240" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:22" ns3:dyDescent="0.2">
       <c r="A240" s="61">
         <v>239</v>
       </c>
@@ -25803,7 +25806,7 @@
       <c r="U240" s="11"/>
       <c r="V240" s="10"/>
     </row>
-    <row r="241" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:22" ns3:dyDescent="0.2">
       <c r="A241" s="61">
         <v>240</v>
       </c>
@@ -25859,7 +25862,7 @@
       <c r="U241" s="11"/>
       <c r="V241" s="10"/>
     </row>
-    <row r="242" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:22" ns3:dyDescent="0.2">
       <c r="A242" s="58">
         <v>241</v>
       </c>
@@ -25917,7 +25920,7 @@
       <c r="U242" s="11"/>
       <c r="V242" s="10"/>
     </row>
-    <row r="243" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:22" ns3:dyDescent="0.2">
       <c r="A243" s="61">
         <v>242</v>
       </c>
@@ -25975,7 +25978,7 @@
       <c r="U243" s="11"/>
       <c r="V243" s="10"/>
     </row>
-    <row r="244" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:22" ns3:dyDescent="0.2">
       <c r="A244" s="58">
         <v>243</v>
       </c>
@@ -26031,7 +26034,7 @@
       <c r="U244" s="11"/>
       <c r="V244" s="10"/>
     </row>
-    <row r="245" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:22" ns3:dyDescent="0.2">
       <c r="A245" s="58">
         <v>244</v>
       </c>
@@ -26087,7 +26090,7 @@
       <c r="U245" s="11"/>
       <c r="V245" s="10"/>
     </row>
-    <row r="246" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:22" ns3:dyDescent="0.2">
       <c r="A246" s="58">
         <v>245</v>
       </c>
@@ -26143,7 +26146,7 @@
       <c r="U246" s="11"/>
       <c r="V246" s="10"/>
     </row>
-    <row r="247" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:22" ns3:dyDescent="0.2">
       <c r="A247" s="58">
         <v>246</v>
       </c>
@@ -26201,7 +26204,7 @@
       <c r="U247" s="11"/>
       <c r="V247" s="10"/>
     </row>
-    <row r="248" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:22" ns3:dyDescent="0.2">
       <c r="A248" s="58">
         <v>247</v>
       </c>
@@ -26257,7 +26260,7 @@
       <c r="U248" s="11"/>
       <c r="V248" s="10"/>
     </row>
-    <row r="249" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:22" ns3:dyDescent="0.2">
       <c r="A249" s="58">
         <v>248</v>
       </c>
@@ -26315,7 +26318,7 @@
       <c r="U249" s="11"/>
       <c r="V249" s="10"/>
     </row>
-    <row r="250" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A250" s="61">
         <v>249</v>
       </c>
@@ -26373,7 +26376,7 @@
       <c r="U250" s="11"/>
       <c r="V250" s="10"/>
     </row>
-    <row r="251" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:22" ns3:dyDescent="0.2">
       <c r="A251" s="61">
         <v>250</v>
       </c>
@@ -26431,7 +26434,7 @@
       <c r="U251" s="11"/>
       <c r="V251" s="10"/>
     </row>
-    <row r="252" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:22" ns3:dyDescent="0.2">
       <c r="A252" s="61">
         <v>251</v>
       </c>
@@ -26487,7 +26490,7 @@
       <c r="U252" s="11"/>
       <c r="V252" s="10"/>
     </row>
-    <row r="253" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:22" ns3:dyDescent="0.2">
       <c r="A253" s="58">
         <v>252</v>
       </c>
@@ -26543,7 +26546,7 @@
       <c r="U253" s="11"/>
       <c r="V253" s="10"/>
     </row>
-    <row r="254" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:22" ns3:dyDescent="0.2">
       <c r="A254" s="58">
         <v>253</v>
       </c>
@@ -26601,7 +26604,7 @@
       <c r="U254" s="11"/>
       <c r="V254" s="10"/>
     </row>
-    <row r="255" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:22" ns3:dyDescent="0.2">
       <c r="A255" s="58">
         <v>254</v>
       </c>
@@ -26659,7 +26662,7 @@
       <c r="U255" s="11"/>
       <c r="V255" s="10"/>
     </row>
-    <row r="256" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:22" ns3:dyDescent="0.2">
       <c r="A256" s="58">
         <v>255</v>
       </c>
@@ -26715,7 +26718,7 @@
       <c r="U256" s="11"/>
       <c r="V256" s="10"/>
     </row>
-    <row r="257" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:22" ns3:dyDescent="0.2">
       <c r="A257" s="58">
         <v>256</v>
       </c>
@@ -26773,7 +26776,7 @@
       <c r="U257" s="11"/>
       <c r="V257" s="10"/>
     </row>
-    <row r="258" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:22" ns3:dyDescent="0.2">
       <c r="A258" s="58">
         <v>257</v>
       </c>
@@ -26831,7 +26834,7 @@
       <c r="U258" s="11"/>
       <c r="V258" s="10"/>
     </row>
-    <row r="259" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:22" ns3:dyDescent="0.2">
       <c r="A259" s="58">
         <v>258</v>
       </c>
@@ -26887,7 +26890,7 @@
       <c r="U259" s="11"/>
       <c r="V259" s="10"/>
     </row>
-    <row r="260" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:22" ns3:dyDescent="0.2">
       <c r="A260" s="58">
         <v>259</v>
       </c>
@@ -26945,7 +26948,7 @@
       <c r="U260" s="11"/>
       <c r="V260" s="10"/>
     </row>
-    <row r="261" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:22" ns3:dyDescent="0.2">
       <c r="A261" s="58">
         <v>260</v>
       </c>
@@ -27003,7 +27006,7 @@
       <c r="U261" s="11"/>
       <c r="V261" s="10"/>
     </row>
-    <row r="262" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A262" s="58">
         <v>261</v>
       </c>
@@ -27061,7 +27064,7 @@
       <c r="U262" s="11"/>
       <c r="V262" s="10"/>
     </row>
-    <row r="263" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A263" s="58">
         <v>262</v>
       </c>
@@ -27119,7 +27122,7 @@
       <c r="U263" s="11"/>
       <c r="V263" s="10"/>
     </row>
-    <row r="264" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:22" ns3:dyDescent="0.2">
       <c r="A264" s="58">
         <v>263</v>
       </c>
@@ -27177,7 +27180,7 @@
       <c r="U264" s="11"/>
       <c r="V264" s="10"/>
     </row>
-    <row r="265" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:22" ns3:dyDescent="0.2">
       <c r="A265" s="58">
         <v>264</v>
       </c>
@@ -27235,7 +27238,7 @@
       <c r="U265" s="11"/>
       <c r="V265" s="10"/>
     </row>
-    <row r="266" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A266" s="61">
         <v>265</v>
       </c>
@@ -27291,7 +27294,7 @@
       <c r="U266" s="11"/>
       <c r="V266" s="10"/>
     </row>
-    <row r="267" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A267" s="61">
         <v>266</v>
       </c>
@@ -27345,7 +27348,7 @@
       <c r="U267" s="11"/>
       <c r="V267" s="10"/>
     </row>
-    <row r="268" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A268" s="58">
         <v>267</v>
       </c>
@@ -27403,7 +27406,7 @@
       <c r="U268" s="11"/>
       <c r="V268" s="10"/>
     </row>
-    <row r="269" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A269" s="61">
         <v>268</v>
       </c>
@@ -27457,7 +27460,7 @@
       <c r="U269" s="11"/>
       <c r="V269" s="10"/>
     </row>
-    <row r="270" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A270" s="61">
         <v>269</v>
       </c>
@@ -27515,7 +27518,7 @@
       <c r="U270" s="11"/>
       <c r="V270" s="10"/>
     </row>
-    <row r="271" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:22" ns3:dyDescent="0.2">
       <c r="A271" s="61">
         <v>270</v>
       </c>
@@ -27575,7 +27578,7 @@
       <c r="U271" s="11"/>
       <c r="V271" s="10"/>
     </row>
-    <row r="272" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:22" ns3:dyDescent="0.2">
       <c r="A272" s="61">
         <v>271</v>
       </c>
@@ -27635,7 +27638,7 @@
       <c r="U272" s="11"/>
       <c r="V272" s="10"/>
     </row>
-    <row r="273" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:22" ns3:dyDescent="0.2">
       <c r="A273" s="61">
         <v>272</v>
       </c>
@@ -27695,7 +27698,7 @@
       <c r="U273" s="11"/>
       <c r="V273" s="10"/>
     </row>
-    <row r="274" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:22" ns3:dyDescent="0.2">
       <c r="A274" s="58">
         <v>273</v>
       </c>
@@ -27753,7 +27756,7 @@
       <c r="U274" s="11"/>
       <c r="V274" s="10"/>
     </row>
-    <row r="275" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:22" ns3:dyDescent="0.2">
       <c r="A275" s="58">
         <v>274</v>
       </c>
@@ -27813,7 +27816,7 @@
       <c r="U275" s="11"/>
       <c r="V275" s="10"/>
     </row>
-    <row r="276" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:22" ns3:dyDescent="0.2">
       <c r="A276" s="58">
         <v>275</v>
       </c>
@@ -27873,7 +27876,7 @@
       <c r="U276" s="11"/>
       <c r="V276" s="10"/>
     </row>
-    <row r="277" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:22" ns3:dyDescent="0.2">
       <c r="A277" s="58">
         <v>276</v>
       </c>
@@ -27933,7 +27936,7 @@
       <c r="U277" s="11"/>
       <c r="V277" s="10"/>
     </row>
-    <row r="278" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A278" s="58">
         <v>277</v>
       </c>
@@ -27993,7 +27996,7 @@
       <c r="U278" s="11"/>
       <c r="V278" s="10"/>
     </row>
-    <row r="279" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A279" s="58">
         <v>278</v>
       </c>
@@ -28053,7 +28056,7 @@
       <c r="U279" s="11"/>
       <c r="V279" s="10"/>
     </row>
-    <row r="280" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A280" s="58">
         <v>279</v>
       </c>
@@ -28113,7 +28116,7 @@
       <c r="U280" s="11"/>
       <c r="V280" s="10"/>
     </row>
-    <row r="281" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:22" ns3:dyDescent="0.2">
       <c r="A281" s="58">
         <v>280</v>
       </c>
@@ -28173,7 +28176,7 @@
       <c r="U281" s="11"/>
       <c r="V281" s="10"/>
     </row>
-    <row r="282" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:22" ns3:dyDescent="0.2">
       <c r="A282" s="58">
         <v>281</v>
       </c>
@@ -28233,7 +28236,7 @@
       <c r="U282" s="11"/>
       <c r="V282" s="10"/>
     </row>
-    <row r="283" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:22" ns3:dyDescent="0.2">
       <c r="A283" s="58">
         <v>282</v>
       </c>
@@ -28293,7 +28296,7 @@
       <c r="U283" s="11"/>
       <c r="V283" s="10"/>
     </row>
-    <row r="284" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A284" s="58">
         <v>283</v>
       </c>
@@ -28351,7 +28354,7 @@
       <c r="U284" s="11"/>
       <c r="V284" s="10"/>
     </row>
-    <row r="285" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A285" s="58">
         <v>284</v>
       </c>
@@ -28409,7 +28412,7 @@
       <c r="U285" s="11"/>
       <c r="V285" s="10"/>
     </row>
-    <row r="286" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:22" ns3:dyDescent="0.2">
       <c r="A286" s="58">
         <v>285</v>
       </c>
@@ -28467,7 +28470,7 @@
       <c r="U286" s="11"/>
       <c r="V286" s="10"/>
     </row>
-    <row r="287" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:22" ns3:dyDescent="0.2">
       <c r="A287" s="58">
         <v>286</v>
       </c>
@@ -28527,7 +28530,7 @@
       <c r="U287" s="11"/>
       <c r="V287" s="10"/>
     </row>
-    <row r="288" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:22" ns3:dyDescent="0.2">
       <c r="A288" s="58">
         <v>287</v>
       </c>
@@ -28581,7 +28584,7 @@
       <c r="U288" s="11"/>
       <c r="V288" s="10"/>
     </row>
-    <row r="289" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:22" ns3:dyDescent="0.2">
       <c r="A289" s="58">
         <v>288</v>
       </c>
@@ -28635,7 +28638,7 @@
       <c r="U289" s="11"/>
       <c r="V289" s="10"/>
     </row>
-    <row r="290" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:22" ns3:dyDescent="0.2">
       <c r="A290" s="58">
         <v>289</v>
       </c>
@@ -28689,7 +28692,7 @@
       <c r="U290" s="11"/>
       <c r="V290" s="10"/>
     </row>
-    <row r="291" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:22" ns3:dyDescent="0.2">
       <c r="A291" s="61">
         <v>290</v>
       </c>
@@ -28747,7 +28750,7 @@
       <c r="U291" s="11"/>
       <c r="V291" s="10"/>
     </row>
-    <row r="292" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:22" ns3:dyDescent="0.2">
       <c r="A292" s="61">
         <v>291</v>
       </c>
@@ -28805,7 +28808,7 @@
       <c r="U292" s="11"/>
       <c r="V292" s="10"/>
     </row>
-    <row r="293" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:22" ns3:dyDescent="0.2">
       <c r="A293" s="61">
         <v>292</v>
       </c>
@@ -28861,7 +28864,7 @@
       <c r="U293" s="11"/>
       <c r="V293" s="10"/>
     </row>
-    <row r="294" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A294" s="58">
         <v>293</v>
       </c>
@@ -28921,7 +28924,7 @@
       </c>
       <c r="V294" s="10"/>
     </row>
-    <row r="295" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A295" s="58">
         <v>294</v>
       </c>
@@ -28978,7 +28981,7 @@
       <c r="T295" s="10"/>
       <c r="V295" s="10"/>
     </row>
-    <row r="296" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A296" s="58">
         <v>295</v>
       </c>
@@ -29038,7 +29041,7 @@
       </c>
       <c r="V296" s="10"/>
     </row>
-    <row r="297" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A297" s="58">
         <v>296</v>
       </c>
@@ -29098,7 +29101,7 @@
       </c>
       <c r="V297" s="10"/>
     </row>
-    <row r="298" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A298" s="58">
         <v>297</v>
       </c>
@@ -29158,7 +29161,7 @@
       </c>
       <c r="V298" s="10"/>
     </row>
-    <row r="299" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A299" s="58">
         <v>298</v>
       </c>
@@ -29220,7 +29223,7 @@
       </c>
       <c r="V299" s="10"/>
     </row>
-    <row r="300" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A300" s="58">
         <v>299</v>
       </c>
@@ -29280,7 +29283,7 @@
       </c>
       <c r="V300" s="10"/>
     </row>
-    <row r="301" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A301" s="58">
         <v>300</v>
       </c>
@@ -29340,7 +29343,7 @@
       </c>
       <c r="V301" s="10"/>
     </row>
-    <row r="302" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A302" s="58">
         <v>301</v>
       </c>
@@ -29400,7 +29403,7 @@
       </c>
       <c r="V302" s="10"/>
     </row>
-    <row r="303" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A303" s="61">
         <v>302</v>
       </c>
@@ -29462,7 +29465,7 @@
       </c>
       <c r="V303" s="10"/>
     </row>
-    <row r="304" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A304" s="61">
         <v>303</v>
       </c>
@@ -29526,7 +29529,7 @@
       </c>
       <c r="V304" s="10"/>
     </row>
-    <row r="305" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A305" s="58">
         <v>304</v>
       </c>
@@ -29590,7 +29593,7 @@
       </c>
       <c r="V305" s="10"/>
     </row>
-    <row r="306" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:22" ns3:dyDescent="0.2">
       <c r="A306" s="58">
         <v>305</v>
       </c>
@@ -29652,7 +29655,7 @@
       <c r="U306" s="11"/>
       <c r="V306" s="10"/>
     </row>
-    <row r="307" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:22" ns3:dyDescent="0.2">
       <c r="A307" s="58">
         <v>306</v>
       </c>
@@ -29714,7 +29717,7 @@
       <c r="U307" s="11"/>
       <c r="V307" s="10"/>
     </row>
-    <row r="308" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:22" ns3:dyDescent="0.2">
       <c r="A308" s="61">
         <v>307</v>
       </c>
@@ -29774,7 +29777,7 @@
       <c r="U308" s="11"/>
       <c r="V308" s="10"/>
     </row>
-    <row r="309" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:22" ns3:dyDescent="0.2">
       <c r="A309" s="61">
         <v>308</v>
       </c>
@@ -29834,7 +29837,7 @@
       <c r="U309" s="11"/>
       <c r="V309" s="10"/>
     </row>
-    <row r="310" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:22" ns3:dyDescent="0.2">
       <c r="A310" s="61">
         <v>309</v>
       </c>
@@ -29894,7 +29897,7 @@
       <c r="U310" s="11"/>
       <c r="V310" s="10"/>
     </row>
-    <row r="311" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:22" ns3:dyDescent="0.2">
       <c r="A311" s="61">
         <v>310</v>
       </c>
@@ -29954,7 +29957,7 @@
       <c r="U311" s="11"/>
       <c r="V311" s="10"/>
     </row>
-    <row r="312" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:22" ns3:dyDescent="0.2">
       <c r="A312" s="61">
         <v>311</v>
       </c>
@@ -30012,7 +30015,7 @@
       <c r="U312" s="11"/>
       <c r="V312" s="10"/>
     </row>
-    <row r="313" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:22" ns3:dyDescent="0.2">
       <c r="A313" s="61">
         <v>312</v>
       </c>
@@ -30070,7 +30073,7 @@
       <c r="U313" s="11"/>
       <c r="V313" s="10"/>
     </row>
-    <row r="314" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:22" ns3:dyDescent="0.2">
       <c r="A314" s="58">
         <v>313</v>
       </c>
@@ -30129,7 +30132,7 @@
       <c r="U314" s="11"/>
       <c r="V314" s="10"/>
     </row>
-    <row r="315" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:22" ns3:dyDescent="0.2">
       <c r="A315" s="58">
         <v>314</v>
       </c>
@@ -30188,7 +30191,7 @@
       <c r="U315" s="11"/>
       <c r="V315" s="10"/>
     </row>
-    <row r="316" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A316" s="61">
         <v>315</v>
       </c>
@@ -30247,7 +30250,7 @@
       <c r="U316" s="11"/>
       <c r="V316" s="10"/>
     </row>
-    <row r="317" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A317" s="58">
         <v>316</v>
       </c>
@@ -30305,7 +30308,7 @@
       <c r="U317" s="11"/>
       <c r="V317" s="10"/>
     </row>
-    <row r="318" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A318" s="58">
         <v>317</v>
       </c>
@@ -30365,7 +30368,7 @@
       </c>
       <c r="V318" s="10"/>
     </row>
-    <row r="319" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:22" ns3:dyDescent="0.2">
       <c r="A319" s="58">
         <v>318</v>
       </c>
@@ -30424,7 +30427,7 @@
       <c r="T319" s="10"/>
       <c r="V319" s="10"/>
     </row>
-    <row r="320" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:22" ns3:dyDescent="0.2">
       <c r="A320" s="58">
         <v>319</v>
       </c>
@@ -30486,7 +30489,7 @@
       </c>
       <c r="V320" s="10"/>
     </row>
-    <row r="321" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:22" ns3:dyDescent="0.2">
       <c r="A321" s="58">
         <v>320</v>
       </c>
@@ -30546,7 +30549,7 @@
       </c>
       <c r="V321" s="10"/>
     </row>
-    <row r="322" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:22" ns3:dyDescent="0.2">
       <c r="A322" s="58">
         <v>321</v>
       </c>
@@ -30606,7 +30609,7 @@
       </c>
       <c r="V322" s="10"/>
     </row>
-    <row r="323" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A323" s="58">
         <v>322</v>
       </c>
@@ -30668,7 +30671,7 @@
       </c>
       <c r="V323" s="10"/>
     </row>
-    <row r="324" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:22" ht="17" customHeight="1" ns3:dyDescent="0.2">
       <c r="A324" s="58">
         <v>323</v>
       </c>
@@ -30730,7 +30733,7 @@
       </c>
       <c r="V324" s="10"/>
     </row>
-    <row r="325" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:22" ns3:dyDescent="0.2">
       <c r="A325" s="58">
         <v>324</v>
       </c>
@@ -30792,7 +30795,7 @@
       </c>
       <c r="V325" s="10"/>
     </row>
-    <row r="326" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A326" s="58">
         <v>325</v>
       </c>
@@ -30852,7 +30855,7 @@
       </c>
       <c r="V326" s="10"/>
     </row>
-    <row r="327" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A327" s="58">
         <v>326</v>
       </c>
@@ -30912,7 +30915,7 @@
       </c>
       <c r="V327" s="10"/>
     </row>
-    <row r="328" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A328" s="58">
         <v>327</v>
       </c>
@@ -30972,7 +30975,7 @@
       </c>
       <c r="V328" s="10"/>
     </row>
-    <row r="329" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:22" ns3:dyDescent="0.2">
       <c r="A329" s="58">
         <v>328</v>
       </c>
@@ -31032,7 +31035,7 @@
       </c>
       <c r="V329" s="10"/>
     </row>
-    <row r="330" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:22" ns3:dyDescent="0.2">
       <c r="A330" s="58">
         <v>329</v>
       </c>
@@ -31092,7 +31095,7 @@
       <c r="U330" s="11"/>
       <c r="V330" s="10"/>
     </row>
-    <row r="331" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:22" ns3:dyDescent="0.2">
       <c r="A331" s="58">
         <v>330</v>
       </c>
@@ -31152,7 +31155,7 @@
       <c r="U331" s="11"/>
       <c r="V331" s="10"/>
     </row>
-    <row r="332" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A332" s="58">
         <v>331</v>
       </c>
@@ -31210,7 +31213,7 @@
       <c r="U332" s="11"/>
       <c r="V332" s="10"/>
     </row>
-    <row r="333" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:22" ns3:dyDescent="0.2">
       <c r="A333" s="58">
         <v>332</v>
       </c>
@@ -31270,7 +31273,7 @@
       <c r="U333" s="11"/>
       <c r="V333" s="10"/>
     </row>
-    <row r="334" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A334" s="58">
         <v>333</v>
       </c>
@@ -31330,7 +31333,7 @@
       <c r="U334" s="11"/>
       <c r="V334" s="10"/>
     </row>
-    <row r="335" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:22" ns3:dyDescent="0.2">
       <c r="A335" s="58">
         <v>334</v>
       </c>
@@ -31390,7 +31393,7 @@
       <c r="U335" s="11"/>
       <c r="V335" s="10"/>
     </row>
-    <row r="336" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A336" s="58">
         <v>335</v>
       </c>
@@ -31448,7 +31451,7 @@
       <c r="U336" s="11"/>
       <c r="V336" s="10"/>
     </row>
-    <row r="337" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:22" ns3:dyDescent="0.2">
       <c r="A337" s="58">
         <v>336</v>
       </c>
@@ -31506,7 +31509,7 @@
       <c r="U337" s="11"/>
       <c r="V337" s="10"/>
     </row>
-    <row r="338" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:22" ns3:dyDescent="0.2">
       <c r="A338" s="58">
         <v>337</v>
       </c>
@@ -31562,7 +31565,7 @@
       <c r="U338" s="11"/>
       <c r="V338" s="10"/>
     </row>
-    <row r="339" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:22" ns3:dyDescent="0.2">
       <c r="A339" s="58">
         <v>338</v>
       </c>
@@ -31618,7 +31621,7 @@
       <c r="U339" s="11"/>
       <c r="V339" s="10"/>
     </row>
-    <row r="340" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:22" ns3:dyDescent="0.2">
       <c r="A340" s="58">
         <v>339</v>
       </c>
@@ -31678,7 +31681,7 @@
       <c r="U340" s="11"/>
       <c r="V340" s="10"/>
     </row>
-    <row r="341" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:22" ns3:dyDescent="0.2">
       <c r="A341" s="58">
         <v>340</v>
       </c>
@@ -31738,7 +31741,7 @@
       <c r="U341" s="11"/>
       <c r="V341" s="10"/>
     </row>
-    <row r="342" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:22" ns3:dyDescent="0.2">
       <c r="A342" s="58">
         <v>341</v>
       </c>
@@ -31796,7 +31799,7 @@
       <c r="U342" s="11"/>
       <c r="V342" s="10"/>
     </row>
-    <row r="343" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:22" ns3:dyDescent="0.2">
       <c r="A343" s="58">
         <v>342</v>
       </c>
@@ -31856,7 +31859,7 @@
       <c r="U343" s="11"/>
       <c r="V343" s="10"/>
     </row>
-    <row r="344" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A344" s="58">
         <v>343</v>
       </c>
@@ -31912,7 +31915,7 @@
       <c r="U344" s="11"/>
       <c r="V344" s="10"/>
     </row>
-    <row r="345" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A345" s="58">
         <v>344</v>
       </c>
@@ -31968,7 +31971,7 @@
       <c r="U345" s="11"/>
       <c r="V345" s="10"/>
     </row>
-    <row r="346" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:22" ht="20" customHeight="1" ns3:dyDescent="0.2">
       <c r="A346" s="58">
         <v>345</v>
       </c>
@@ -32026,7 +32029,7 @@
       <c r="U346" s="11"/>
       <c r="V346" s="10"/>
     </row>
-    <row r="347" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:22" ht="22" customHeight="1" ns3:dyDescent="0.2">
       <c r="A347" s="58">
         <v>346</v>
       </c>
@@ -32084,7 +32087,7 @@
       <c r="U347" s="11"/>
       <c r="V347" s="10"/>
     </row>
-    <row r="348" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:22" ns3:dyDescent="0.2">
       <c r="A348" s="61">
         <v>347</v>
       </c>
@@ -32142,7 +32145,7 @@
       <c r="U348" s="11"/>
       <c r="V348" s="10"/>
     </row>
-    <row r="349" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:22" ns3:dyDescent="0.2">
       <c r="A349" s="61">
         <v>348</v>
       </c>
@@ -32200,7 +32203,7 @@
       <c r="U349" s="11"/>
       <c r="V349" s="10"/>
     </row>
-    <row r="350" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:22" ns3:dyDescent="0.2">
       <c r="A350" s="58">
         <v>349</v>
       </c>
@@ -32258,7 +32261,7 @@
       <c r="U350" s="11"/>
       <c r="V350" s="10"/>
     </row>
-    <row r="351" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:22" ns3:dyDescent="0.2">
       <c r="A351" s="58">
         <v>350</v>
       </c>
@@ -32315,7 +32318,7 @@
       <c r="U351" s="11"/>
       <c r="V351" s="10"/>
     </row>
-    <row r="352" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:22" ns3:dyDescent="0.2">
       <c r="A352" s="58">
         <v>351</v>
       </c>
@@ -32369,7 +32372,7 @@
       <c r="U352" s="11"/>
       <c r="V352" s="10"/>
     </row>
-    <row r="353" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:22" ns3:dyDescent="0.2">
       <c r="A353" s="61">
         <v>352</v>
       </c>
@@ -32425,7 +32428,7 @@
       <c r="U353" s="11"/>
       <c r="V353" s="10"/>
     </row>
-    <row r="354" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:22" ns3:dyDescent="0.2">
       <c r="A354" s="61">
         <v>353</v>
       </c>
@@ -32483,7 +32486,7 @@
       <c r="U354" s="11"/>
       <c r="V354" s="10"/>
     </row>
-    <row r="355" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:22" ns3:dyDescent="0.2">
       <c r="A355" s="61">
         <v>354</v>
       </c>
@@ -32541,7 +32544,7 @@
       <c r="U355" s="11"/>
       <c r="V355" s="10"/>
     </row>
-    <row r="356" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:22" ns3:dyDescent="0.2">
       <c r="A356" s="61">
         <v>355</v>
       </c>
@@ -32597,7 +32600,7 @@
       <c r="U356" s="11"/>
       <c r="V356" s="10"/>
     </row>
-    <row r="357" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:22" ns3:dyDescent="0.2">
       <c r="A357" s="61">
         <v>356</v>
       </c>
@@ -32653,7 +32656,7 @@
       <c r="U357" s="11"/>
       <c r="V357" s="10"/>
     </row>
-    <row r="358" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:22" ns3:dyDescent="0.2">
       <c r="A358" s="58">
         <v>357</v>
       </c>
@@ -32713,7 +32716,7 @@
       <c r="U358" s="11"/>
       <c r="V358" s="10"/>
     </row>
-    <row r="359" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:22" ns3:dyDescent="0.2">
       <c r="A359" s="61">
         <v>358</v>
       </c>
@@ -32767,7 +32770,7 @@
       <c r="U359" s="11"/>
       <c r="V359" s="10"/>
     </row>
-    <row r="360" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:22" ns3:dyDescent="0.2">
       <c r="A360" s="58">
         <v>359</v>
       </c>
@@ -32825,7 +32828,7 @@
       <c r="U360" s="11"/>
       <c r="V360" s="10"/>
     </row>
-    <row r="361" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A361" s="61">
         <v>360</v>
       </c>
@@ -32879,7 +32882,7 @@
       <c r="U361" s="11"/>
       <c r="V361" s="10"/>
     </row>
-    <row r="362" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:22" ht="48" ns3:dyDescent="0.2">
       <c r="A362" s="61">
         <v>361</v>
       </c>
@@ -32939,7 +32942,7 @@
       <c r="U362" s="11"/>
       <c r="V362" s="10"/>
     </row>
-    <row r="363" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:22" ht="48" ns3:dyDescent="0.2">
       <c r="A363" s="61">
         <v>362</v>
       </c>
@@ -32999,7 +33002,7 @@
       <c r="U363" s="11"/>
       <c r="V363" s="10"/>
     </row>
-    <row r="364" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A364" s="58">
         <v>363</v>
       </c>
@@ -33059,7 +33062,7 @@
       <c r="U364" s="11"/>
       <c r="V364" s="10"/>
     </row>
-    <row r="365" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A365" s="58">
         <v>364</v>
       </c>
@@ -33119,7 +33122,7 @@
       <c r="U365" s="11"/>
       <c r="V365" s="10"/>
     </row>
-    <row r="366" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A366" s="58">
         <v>365</v>
       </c>
@@ -33179,7 +33182,7 @@
       <c r="U366" s="11"/>
       <c r="V366" s="10"/>
     </row>
-    <row r="367" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:22" ns3:dyDescent="0.2">
       <c r="A367" s="61">
         <v>366</v>
       </c>
@@ -33235,7 +33238,7 @@
       <c r="U367" s="11"/>
       <c r="V367" s="10"/>
     </row>
-    <row r="368" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:22" ns3:dyDescent="0.2">
       <c r="A368" s="61">
         <v>367</v>
       </c>
@@ -33292,7 +33295,7 @@
       <c r="U368" s="11"/>
       <c r="V368" s="10"/>
     </row>
-    <row r="369" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:22" ns3:dyDescent="0.2">
       <c r="A369" s="61">
         <v>368</v>
       </c>
@@ -33349,7 +33352,7 @@
       <c r="U369" s="11"/>
       <c r="V369" s="10"/>
     </row>
-    <row r="370" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:22" ns3:dyDescent="0.2">
       <c r="A370" s="61">
         <v>369</v>
       </c>
@@ -33407,7 +33410,7 @@
       <c r="U370" s="11"/>
       <c r="V370" s="10"/>
     </row>
-    <row r="371" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:22" ns3:dyDescent="0.2">
       <c r="A371" s="61">
         <v>370</v>
       </c>
@@ -33463,7 +33466,7 @@
       <c r="U371" s="11"/>
       <c r="V371" s="10"/>
     </row>
-    <row r="372" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:22" ns3:dyDescent="0.2">
       <c r="A372" s="61">
         <v>371</v>
       </c>
@@ -33519,7 +33522,7 @@
       <c r="U372" s="11"/>
       <c r="V372" s="10"/>
     </row>
-    <row r="373" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:22" ns3:dyDescent="0.2">
       <c r="A373" s="61">
         <v>372</v>
       </c>
@@ -33575,7 +33578,7 @@
       <c r="U373" s="11"/>
       <c r="V373" s="10"/>
     </row>
-    <row r="374" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:22" ns3:dyDescent="0.2">
       <c r="A374" s="61">
         <v>373</v>
       </c>
@@ -33633,7 +33636,7 @@
       <c r="U374" s="11"/>
       <c r="V374" s="10"/>
     </row>
-    <row r="375" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:22" ns3:dyDescent="0.2">
       <c r="A375" s="58">
         <v>374</v>
       </c>
@@ -33691,7 +33694,7 @@
       <c r="U375" s="11"/>
       <c r="V375" s="10"/>
     </row>
-    <row r="376" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:22" ns3:dyDescent="0.2">
       <c r="A376" s="58">
         <v>375</v>
       </c>
@@ -33749,7 +33752,7 @@
       <c r="U376" s="11"/>
       <c r="V376" s="10"/>
     </row>
-    <row r="377" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:22" ns3:dyDescent="0.2">
       <c r="A377" s="58">
         <v>376</v>
       </c>
@@ -33807,7 +33810,7 @@
       <c r="U377" s="11"/>
       <c r="V377" s="10"/>
     </row>
-    <row r="378" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:22" ns3:dyDescent="0.2">
       <c r="A378" s="61">
         <v>377</v>
       </c>
@@ -33863,7 +33866,7 @@
       <c r="U378" s="11"/>
       <c r="V378" s="10"/>
     </row>
-    <row r="379" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:22" ns3:dyDescent="0.2">
       <c r="A379" s="61">
         <v>378</v>
       </c>
@@ -33919,7 +33922,7 @@
       <c r="U379" s="11"/>
       <c r="V379" s="10"/>
     </row>
-    <row r="380" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:22" ns3:dyDescent="0.2">
       <c r="A380" s="61">
         <v>379</v>
       </c>
@@ -33975,7 +33978,7 @@
       <c r="U380" s="11"/>
       <c r="V380" s="10"/>
     </row>
-    <row r="381" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:22" ns3:dyDescent="0.2">
       <c r="A381" s="61">
         <v>380</v>
       </c>
@@ -34031,7 +34034,7 @@
       <c r="U381" s="11"/>
       <c r="V381" s="10"/>
     </row>
-    <row r="382" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:22" ns3:dyDescent="0.2">
       <c r="A382" s="61">
         <v>381</v>
       </c>
@@ -34087,7 +34090,7 @@
       <c r="U382" s="11"/>
       <c r="V382" s="10"/>
     </row>
-    <row r="383" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:22" ns3:dyDescent="0.2">
       <c r="A383" s="61">
         <v>382</v>
       </c>
@@ -34141,7 +34144,7 @@
       <c r="U383" s="11"/>
       <c r="V383" s="10"/>
     </row>
-    <row r="384" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:22" ns3:dyDescent="0.2">
       <c r="A384" s="61">
         <v>383</v>
       </c>
@@ -34195,7 +34198,7 @@
       <c r="U384" s="11"/>
       <c r="V384" s="10"/>
     </row>
-    <row r="385" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:22" ns3:dyDescent="0.2">
       <c r="A385" s="61">
         <v>384</v>
       </c>
@@ -34251,7 +34254,7 @@
       <c r="U385" s="11"/>
       <c r="V385" s="10"/>
     </row>
-    <row r="386" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A386" s="61">
         <v>385</v>
       </c>
@@ -34309,7 +34312,7 @@
       <c r="U386" s="11"/>
       <c r="V386" s="10"/>
     </row>
-    <row r="387" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:22" ns3:dyDescent="0.2">
       <c r="A387" s="61">
         <v>386</v>
       </c>
@@ -34364,7 +34367,7 @@
       <c r="U387" s="11"/>
       <c r="V387" s="10"/>
     </row>
-    <row r="388" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A388" s="61">
         <v>387</v>
       </c>
@@ -34422,7 +34425,7 @@
       <c r="U388" s="11"/>
       <c r="V388" s="10"/>
     </row>
-    <row r="389" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A389" s="61">
         <v>388</v>
       </c>
@@ -34480,7 +34483,7 @@
       <c r="U389" s="11"/>
       <c r="V389" s="10"/>
     </row>
-    <row r="390" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A390" s="61">
         <v>389</v>
       </c>
@@ -34540,7 +34543,7 @@
       <c r="U390" s="11"/>
       <c r="V390" s="10"/>
     </row>
-    <row r="391" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A391" s="61">
         <v>390</v>
       </c>
@@ -34598,7 +34601,7 @@
       <c r="U391" s="11"/>
       <c r="V391" s="10"/>
     </row>
-    <row r="392" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A392" s="61">
         <v>391</v>
       </c>
@@ -34658,7 +34661,7 @@
       <c r="U392" s="11"/>
       <c r="V392" s="10"/>
     </row>
-    <row r="393" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A393" s="61">
         <v>392</v>
       </c>
@@ -34718,7 +34721,7 @@
       <c r="U393" s="11"/>
       <c r="V393" s="10"/>
     </row>
-    <row r="394" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A394" s="61">
         <v>393</v>
       </c>
@@ -34776,7 +34779,7 @@
       <c r="U394" s="11"/>
       <c r="V394" s="10"/>
     </row>
-    <row r="395" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A395" s="61">
         <v>394</v>
       </c>
@@ -34834,7 +34837,7 @@
       <c r="U395" s="11"/>
       <c r="V395" s="10"/>
     </row>
-    <row r="396" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A396" s="61">
         <v>395</v>
       </c>
@@ -34894,7 +34897,7 @@
       <c r="U396" s="11"/>
       <c r="V396" s="10"/>
     </row>
-    <row r="397" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A397" s="58">
         <v>396</v>
       </c>
@@ -34954,7 +34957,7 @@
       <c r="U397" s="11"/>
       <c r="V397" s="10"/>
     </row>
-    <row r="398" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:22" ns3:dyDescent="0.2">
       <c r="A398" s="58">
         <v>397</v>
       </c>
@@ -35012,7 +35015,7 @@
       <c r="U398" s="11"/>
       <c r="V398" s="10"/>
     </row>
-    <row r="399" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:22" ns3:dyDescent="0.2">
       <c r="A399" s="58">
         <v>398</v>
       </c>
@@ -35070,7 +35073,7 @@
       <c r="U399" s="11"/>
       <c r="V399" s="10"/>
     </row>
-    <row r="400" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A400" s="61">
         <v>399</v>
       </c>
@@ -35128,7 +35131,7 @@
       <c r="U400" s="11"/>
       <c r="V400" s="10"/>
     </row>
-    <row r="401" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:22" ns3:dyDescent="0.2">
       <c r="A401" s="61">
         <v>400</v>
       </c>
@@ -35188,7 +35191,7 @@
       <c r="U401" s="11"/>
       <c r="V401" s="10"/>
     </row>
-    <row r="402" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:22" ns3:dyDescent="0.2">
       <c r="A402" s="58">
         <v>401</v>
       </c>
@@ -35244,7 +35247,7 @@
       <c r="U402" s="11"/>
       <c r="V402" s="10"/>
     </row>
-    <row r="403" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:22" ns3:dyDescent="0.2">
       <c r="A403" s="58">
         <v>402</v>
       </c>
@@ -35300,7 +35303,7 @@
       <c r="U403" s="11"/>
       <c r="V403" s="10"/>
     </row>
-    <row r="404" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:22" ns3:dyDescent="0.2">
       <c r="A404" s="61">
         <v>403</v>
       </c>
@@ -35358,7 +35361,7 @@
       <c r="U404" s="11"/>
       <c r="V404" s="10"/>
     </row>
-    <row r="405" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:22" ns3:dyDescent="0.2">
       <c r="A405" s="61">
         <v>404</v>
       </c>
@@ -35416,7 +35419,7 @@
       <c r="U405" s="11"/>
       <c r="V405" s="10"/>
     </row>
-    <row r="406" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:22" ns3:dyDescent="0.2">
       <c r="A406" s="61">
         <v>405</v>
       </c>
@@ -35474,7 +35477,7 @@
       <c r="U406" s="11"/>
       <c r="V406" s="10"/>
     </row>
-    <row r="407" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A407" s="58">
         <v>406</v>
       </c>
@@ -35534,7 +35537,7 @@
       <c r="U407" s="11"/>
       <c r="V407" s="10"/>
     </row>
-    <row r="408" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A408" s="58">
         <v>407</v>
       </c>
@@ -35594,7 +35597,7 @@
       <c r="U408" s="11"/>
       <c r="V408" s="10"/>
     </row>
-    <row r="409" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:22" ns3:dyDescent="0.2">
       <c r="A409" s="61">
         <v>408</v>
       </c>
@@ -35650,7 +35653,7 @@
       <c r="U409" s="11"/>
       <c r="V409" s="10"/>
     </row>
-    <row r="410" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:22" ns3:dyDescent="0.2">
       <c r="A410" s="61">
         <v>409</v>
       </c>
@@ -35706,7 +35709,7 @@
       <c r="U410" s="11"/>
       <c r="V410" s="10"/>
     </row>
-    <row r="411" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:22" ns3:dyDescent="0.2">
       <c r="A411" s="58">
         <v>410</v>
       </c>
@@ -35766,7 +35769,7 @@
       <c r="U411" s="11"/>
       <c r="V411" s="10"/>
     </row>
-    <row r="412" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:22" ns3:dyDescent="0.2">
       <c r="A412" s="58">
         <v>411</v>
       </c>
@@ -35826,7 +35829,7 @@
       <c r="U412" s="11"/>
       <c r="V412" s="10"/>
     </row>
-    <row r="413" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A413" s="58">
         <v>412</v>
       </c>
@@ -35884,7 +35887,7 @@
       <c r="U413" s="11"/>
       <c r="V413" s="10"/>
     </row>
-    <row r="414" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A414" s="58">
         <v>413</v>
       </c>
@@ -35944,7 +35947,7 @@
       <c r="U414" s="11"/>
       <c r="V414" s="10"/>
     </row>
-    <row r="415" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A415" s="61">
         <v>414</v>
       </c>
@@ -36002,7 +36005,7 @@
       <c r="U415" s="11"/>
       <c r="V415" s="10"/>
     </row>
-    <row r="416" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:22" ns3:dyDescent="0.2">
       <c r="A416" s="58">
         <v>415</v>
       </c>
@@ -36060,7 +36063,7 @@
       <c r="U416" s="11"/>
       <c r="V416" s="10"/>
     </row>
-    <row r="417" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:22" ns3:dyDescent="0.2">
       <c r="A417" s="58">
         <v>416</v>
       </c>
@@ -36118,7 +36121,7 @@
       <c r="U417" s="11"/>
       <c r="V417" s="10"/>
     </row>
-    <row r="418" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:22" ns3:dyDescent="0.2">
       <c r="A418" s="61">
         <v>417</v>
       </c>
@@ -36176,7 +36179,7 @@
       <c r="U418" s="11"/>
       <c r="V418" s="10"/>
     </row>
-    <row r="419" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:22" ns3:dyDescent="0.2">
       <c r="A419" s="61">
         <v>418</v>
       </c>
@@ -36232,7 +36235,7 @@
       <c r="U419" s="11"/>
       <c r="V419" s="10"/>
     </row>
-    <row r="420" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:22" ns3:dyDescent="0.2">
       <c r="A420" s="61">
         <v>419</v>
       </c>
@@ -36288,7 +36291,7 @@
       <c r="U420" s="11"/>
       <c r="V420" s="10"/>
     </row>
-    <row r="421" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A421" s="58">
         <v>420</v>
       </c>
@@ -36344,7 +36347,7 @@
       <c r="U421" s="11"/>
       <c r="V421" s="10"/>
     </row>
-    <row r="422" spans="1:22" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:22" ht="19" customHeight="1" ns3:dyDescent="0.25">
       <c r="A422" s="58">
         <v>421</v>
       </c>
@@ -36402,7 +36405,7 @@
       <c r="U422" s="11"/>
       <c r="V422" s="10"/>
     </row>
-    <row r="423" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:22" ns3:dyDescent="0.2">
       <c r="A423" s="61">
         <v>422</v>
       </c>
@@ -36459,7 +36462,7 @@
       <c r="U423" s="11"/>
       <c r="V423" s="10"/>
     </row>
-    <row r="424" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A424" s="61">
         <v>423</v>
       </c>
@@ -36521,7 +36524,7 @@
       <c r="U424" s="11"/>
       <c r="V424" s="10"/>
     </row>
-    <row r="425" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A425" s="58">
         <v>424</v>
       </c>
@@ -36580,7 +36583,7 @@
       </c>
       <c r="V425" s="10"/>
     </row>
-    <row r="426" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A426" s="58">
         <v>425</v>
       </c>
@@ -36641,7 +36644,7 @@
       </c>
       <c r="V426" s="10"/>
     </row>
-    <row r="427" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A427" s="58">
         <v>426</v>
       </c>
@@ -36705,7 +36708,7 @@
       </c>
       <c r="V427" s="10"/>
     </row>
-    <row r="428" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A428" s="61">
         <v>427</v>
       </c>
@@ -36765,7 +36768,7 @@
       <c r="U428" s="11"/>
       <c r="V428" s="10"/>
     </row>
-    <row r="429" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A429" s="61">
         <v>428</v>
       </c>
@@ -36827,7 +36830,7 @@
       </c>
       <c r="V429" s="10"/>
     </row>
-    <row r="430" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A430" s="61">
         <v>429</v>
       </c>
@@ -36885,7 +36888,7 @@
       </c>
       <c r="V430" s="10"/>
     </row>
-    <row r="431" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A431" s="61">
         <v>430</v>
       </c>
@@ -36949,7 +36952,7 @@
       </c>
       <c r="V431" s="10"/>
     </row>
-    <row r="432" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A432" s="61">
         <v>431</v>
       </c>
@@ -37011,7 +37014,7 @@
       </c>
       <c r="V432" s="10"/>
     </row>
-    <row r="433" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A433" s="61">
         <v>432</v>
       </c>
@@ -37073,7 +37076,7 @@
       </c>
       <c r="V433" s="10"/>
     </row>
-    <row r="434" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:22" ns3:dyDescent="0.2">
       <c r="A434" s="61">
         <v>433</v>
       </c>
@@ -37129,7 +37132,7 @@
       </c>
       <c r="V434" s="10"/>
     </row>
-    <row r="435" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:22" ns3:dyDescent="0.2">
       <c r="A435" s="61">
         <v>434</v>
       </c>
@@ -37191,7 +37194,7 @@
       </c>
       <c r="V435" s="10"/>
     </row>
-    <row r="436" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:22" ns3:dyDescent="0.2">
       <c r="A436" s="61">
         <v>435</v>
       </c>
@@ -37251,7 +37254,7 @@
       <c r="U436" s="11"/>
       <c r="V436" s="10"/>
     </row>
-    <row r="437" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:22" ns3:dyDescent="0.2">
       <c r="A437" s="58">
         <v>436</v>
       </c>
@@ -37311,7 +37314,7 @@
       <c r="U437" s="11"/>
       <c r="V437" s="10"/>
     </row>
-    <row r="438" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:22" ns3:dyDescent="0.2">
       <c r="A438" s="58">
         <v>437</v>
       </c>
@@ -37371,7 +37374,7 @@
       <c r="U438" s="11"/>
       <c r="V438" s="10"/>
     </row>
-    <row r="439" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A439" s="61">
         <v>438</v>
       </c>
@@ -37429,7 +37432,7 @@
       <c r="U439" s="11"/>
       <c r="V439" s="10"/>
     </row>
-    <row r="440" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:22" ns3:dyDescent="0.2">
       <c r="A440" s="61">
         <v>439</v>
       </c>
@@ -37489,7 +37492,7 @@
       <c r="U440" s="11"/>
       <c r="V440" s="10"/>
     </row>
-    <row r="441" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:22" ns3:dyDescent="0.2">
       <c r="A441" s="61">
         <v>440</v>
       </c>
@@ -37547,7 +37550,7 @@
       <c r="U441" s="11"/>
       <c r="V441" s="10"/>
     </row>
-    <row r="442" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:22" ns3:dyDescent="0.2">
       <c r="A442" s="61">
         <v>441</v>
       </c>
@@ -37607,7 +37610,7 @@
       <c r="U442" s="11"/>
       <c r="V442" s="10"/>
     </row>
-    <row r="443" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:22" ns3:dyDescent="0.2">
       <c r="A443" s="61">
         <v>442</v>
       </c>
@@ -37665,7 +37668,7 @@
       <c r="U443" s="11"/>
       <c r="V443" s="10"/>
     </row>
-    <row r="444" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:22" ns3:dyDescent="0.2">
       <c r="A444" s="58">
         <v>443</v>
       </c>
@@ -37723,7 +37726,7 @@
       <c r="U444" s="11"/>
       <c r="V444" s="10"/>
     </row>
-    <row r="445" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:22" ns3:dyDescent="0.2">
       <c r="A445" s="58">
         <v>444</v>
       </c>
@@ -37781,7 +37784,7 @@
       <c r="U445" s="11"/>
       <c r="V445" s="10"/>
     </row>
-    <row r="446" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:22" ns3:dyDescent="0.2">
       <c r="A446" s="58">
         <v>445</v>
       </c>
@@ -37839,7 +37842,7 @@
       <c r="U446" s="11"/>
       <c r="V446" s="10"/>
     </row>
-    <row r="447" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A447" s="61">
         <v>446</v>
       </c>
@@ -37897,7 +37900,7 @@
       <c r="U447" s="11"/>
       <c r="V447" s="10"/>
     </row>
-    <row r="448" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:22" ns3:dyDescent="0.2">
       <c r="A448" s="61">
         <v>447</v>
       </c>
@@ -37955,7 +37958,7 @@
       <c r="U448" s="11"/>
       <c r="V448" s="10"/>
     </row>
-    <row r="449" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:22" ns3:dyDescent="0.2">
       <c r="A449" s="61">
         <v>448</v>
       </c>
@@ -38015,7 +38018,7 @@
       <c r="U449" s="11"/>
       <c r="V449" s="10"/>
     </row>
-    <row r="450" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A450" s="58">
         <v>449</v>
       </c>
@@ -38071,7 +38074,7 @@
       <c r="U450" s="11"/>
       <c r="V450" s="10"/>
     </row>
-    <row r="451" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A451" s="58">
         <v>450</v>
       </c>
@@ -38127,7 +38130,7 @@
       <c r="U451" s="11"/>
       <c r="V451" s="10"/>
     </row>
-    <row r="452" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:22" ns3:dyDescent="0.2">
       <c r="A452" s="58">
         <v>451</v>
       </c>
@@ -38187,7 +38190,7 @@
       <c r="U452" s="11"/>
       <c r="V452" s="10"/>
     </row>
-    <row r="453" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:22" ns3:dyDescent="0.2">
       <c r="A453" s="58">
         <v>452</v>
       </c>
@@ -38247,7 +38250,7 @@
       <c r="U453" s="11"/>
       <c r="V453" s="10"/>
     </row>
-    <row r="454" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:22" ht="32" customHeight="1" ns3:dyDescent="0.2">
       <c r="A454" s="58">
         <v>453</v>
       </c>
@@ -38307,7 +38310,7 @@
       <c r="U454" s="11"/>
       <c r="V454" s="10"/>
     </row>
-    <row r="455" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:22" ht="32" customHeight="1" ns3:dyDescent="0.2">
       <c r="A455" s="58">
         <v>454</v>
       </c>
@@ -38367,7 +38370,7 @@
       <c r="U455" s="11"/>
       <c r="V455" s="10"/>
     </row>
-    <row r="456" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:22" ns3:dyDescent="0.2">
       <c r="A456" s="61">
         <v>455</v>
       </c>
@@ -38421,7 +38424,7 @@
       <c r="U456" s="11"/>
       <c r="V456" s="10"/>
     </row>
-    <row r="457" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:22" ns3:dyDescent="0.2">
       <c r="A457" s="61">
         <v>456</v>
       </c>
@@ -38479,7 +38482,7 @@
       <c r="U457" s="11"/>
       <c r="V457" s="10"/>
     </row>
-    <row r="458" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:22" ns3:dyDescent="0.2">
       <c r="A458" s="61">
         <v>457</v>
       </c>
@@ -38537,7 +38540,7 @@
       <c r="U458" s="11"/>
       <c r="V458" s="10"/>
     </row>
-    <row r="459" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:22" ns3:dyDescent="0.2">
       <c r="A459" s="61">
         <v>458</v>
       </c>
@@ -38597,7 +38600,7 @@
       <c r="U459" s="11"/>
       <c r="V459" s="10"/>
     </row>
-    <row r="460" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:22" ns3:dyDescent="0.2">
       <c r="A460" s="61">
         <v>459</v>
       </c>
@@ -38655,7 +38658,7 @@
       <c r="U460" s="11"/>
       <c r="V460" s="10"/>
     </row>
-    <row r="461" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:22" ns3:dyDescent="0.2">
       <c r="A461" s="61">
         <v>460</v>
       </c>
@@ -38713,7 +38716,7 @@
       <c r="U461" s="11"/>
       <c r="V461" s="10"/>
     </row>
-    <row r="462" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:22" ns3:dyDescent="0.2">
       <c r="A462" s="61">
         <v>461</v>
       </c>
@@ -38771,7 +38774,7 @@
       <c r="U462" s="11"/>
       <c r="V462" s="10"/>
     </row>
-    <row r="463" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:22" ht="32" customHeight="1" ns3:dyDescent="0.2">
       <c r="A463" s="58">
         <v>462</v>
       </c>
@@ -38831,7 +38834,7 @@
       <c r="U463" s="11"/>
       <c r="V463" s="10"/>
     </row>
-    <row r="464" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:22" ns3:dyDescent="0.2">
       <c r="A464" s="61">
         <v>463</v>
       </c>
@@ -38889,7 +38892,7 @@
       <c r="U464" s="11"/>
       <c r="V464" s="10"/>
     </row>
-    <row r="465" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:22" ns3:dyDescent="0.2">
       <c r="A465" s="61">
         <v>464</v>
       </c>
@@ -38949,7 +38952,7 @@
       <c r="U465" s="11"/>
       <c r="V465" s="10"/>
     </row>
-    <row r="466" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:22" ns3:dyDescent="0.2">
       <c r="A466" s="61">
         <v>465</v>
       </c>
@@ -39007,7 +39010,7 @@
       <c r="U466" s="11"/>
       <c r="V466" s="10"/>
     </row>
-    <row r="467" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:22" ns3:dyDescent="0.2">
       <c r="A467" s="61">
         <v>466</v>
       </c>
@@ -39063,7 +39066,7 @@
       <c r="U467" s="11"/>
       <c r="V467" s="10"/>
     </row>
-    <row r="468" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:22" ns3:dyDescent="0.2">
       <c r="A468" s="61">
         <v>467</v>
       </c>
@@ -39119,7 +39122,7 @@
       <c r="U468" s="11"/>
       <c r="V468" s="10"/>
     </row>
-    <row r="469" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:22" ns3:dyDescent="0.2">
       <c r="A469" s="61">
         <v>468</v>
       </c>
@@ -39179,7 +39182,7 @@
       <c r="U469" s="11"/>
       <c r="V469" s="10"/>
     </row>
-    <row r="470" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A470" s="58">
         <v>469</v>
       </c>
@@ -39239,7 +39242,7 @@
       <c r="U470" s="11"/>
       <c r="V470" s="10"/>
     </row>
-    <row r="471" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:22" ns3:dyDescent="0.2">
       <c r="A471" s="58">
         <v>470</v>
       </c>
@@ -39295,7 +39298,7 @@
       <c r="U471" s="11"/>
       <c r="V471" s="10"/>
     </row>
-    <row r="472" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:22" ns3:dyDescent="0.2">
       <c r="A472" s="58">
         <v>471</v>
       </c>
@@ -39351,7 +39354,7 @@
       <c r="U472" s="11"/>
       <c r="V472" s="10"/>
     </row>
-    <row r="473" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:22" ns3:dyDescent="0.2">
       <c r="A473" s="58">
         <v>472</v>
       </c>
@@ -39411,7 +39414,7 @@
       <c r="U473" s="11"/>
       <c r="V473" s="10"/>
     </row>
-    <row r="474" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:22" ns3:dyDescent="0.2">
       <c r="A474" s="61">
         <v>473</v>
       </c>
@@ -39471,7 +39474,7 @@
       <c r="U474" s="11"/>
       <c r="V474" s="10"/>
     </row>
-    <row r="475" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A475" s="58">
         <v>474</v>
       </c>
@@ -39531,7 +39534,7 @@
       <c r="U475" s="11"/>
       <c r="V475" s="10"/>
     </row>
-    <row r="476" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:22" ns3:dyDescent="0.2">
       <c r="A476" s="61">
         <v>475</v>
       </c>
@@ -39591,7 +39594,7 @@
       <c r="U476" s="11"/>
       <c r="V476" s="10"/>
     </row>
-    <row r="477" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A477" s="58">
         <v>476</v>
       </c>
@@ -39653,7 +39656,7 @@
       <c r="U477" s="11"/>
       <c r="V477" s="10"/>
     </row>
-    <row r="478" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:22" ns3:dyDescent="0.2">
       <c r="A478" s="61">
         <v>477</v>
       </c>
@@ -39711,7 +39714,7 @@
       <c r="U478" s="11"/>
       <c r="V478" s="10"/>
     </row>
-    <row r="479" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:22" ns3:dyDescent="0.2">
       <c r="A479" s="58">
         <v>478</v>
       </c>
@@ -39773,7 +39776,7 @@
       <c r="U479" s="11"/>
       <c r="V479" s="10"/>
     </row>
-    <row r="480" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:22" ns3:dyDescent="0.2">
       <c r="A480" s="58">
         <v>479</v>
       </c>
@@ -39833,7 +39836,7 @@
       <c r="U480" s="11"/>
       <c r="V480" s="10"/>
     </row>
-    <row r="481" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:23" ns3:dyDescent="0.2">
       <c r="A481" s="61">
         <v>480</v>
       </c>
@@ -39889,7 +39892,7 @@
       <c r="U481" s="11"/>
       <c r="V481" s="10"/>
     </row>
-    <row r="482" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:23" ns3:dyDescent="0.2">
       <c r="A482" s="61">
         <v>481</v>
       </c>
@@ -39945,7 +39948,7 @@
       <c r="U482" s="11"/>
       <c r="V482" s="10"/>
     </row>
-    <row r="483" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:23" ns3:dyDescent="0.2">
       <c r="A483" s="61">
         <v>482</v>
       </c>
@@ -40001,7 +40004,7 @@
       <c r="U483" s="11"/>
       <c r="V483" s="10"/>
     </row>
-    <row r="484" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:23" ns3:dyDescent="0.2">
       <c r="A484" s="61">
         <v>483</v>
       </c>
@@ -40063,7 +40066,7 @@
       </c>
       <c r="V484" s="10"/>
     </row>
-    <row r="485" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A485" s="61">
         <v>484</v>
       </c>
@@ -40124,7 +40127,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="486" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A486" s="61">
         <v>485</v>
       </c>
@@ -40185,7 +40188,7 @@
         <v>3388</v>
       </c>
     </row>
-    <row r="487" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A487" s="58">
         <v>486</v>
       </c>
@@ -40243,7 +40246,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="488" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A488" s="61">
         <v>487</v>
       </c>
@@ -40310,7 +40313,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="489" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A489" s="61">
         <v>488</v>
       </c>
@@ -40368,7 +40371,7 @@
         <v>3388</v>
       </c>
     </row>
-    <row r="490" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A490" s="61">
         <v>489</v>
       </c>
@@ -40429,7 +40432,7 @@
         <v>3388</v>
       </c>
     </row>
-    <row r="491" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A491" s="61">
         <v>490</v>
       </c>
@@ -40490,7 +40493,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="492" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:23" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A492" s="61">
         <v>491</v>
       </c>
@@ -40551,7 +40554,7 @@
         <v>3268</v>
       </c>
     </row>
-    <row r="493" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A493" s="61">
         <v>492</v>
       </c>
@@ -40614,7 +40617,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="494" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A494" s="61">
         <v>493</v>
       </c>
@@ -40673,7 +40676,7 @@
         <v>3399</v>
       </c>
     </row>
-    <row r="495" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A495" s="61">
         <v>494</v>
       </c>
@@ -40734,7 +40737,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="496" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A496" s="61">
         <v>495</v>
       </c>
@@ -40795,7 +40798,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="497" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A497" s="61">
         <v>496</v>
       </c>
@@ -40854,7 +40857,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="498" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:23" ns3:dyDescent="0.2">
       <c r="A498" s="61">
         <v>497</v>
       </c>
@@ -40910,7 +40913,7 @@
       <c r="U498" s="11"/>
       <c r="V498" s="10"/>
     </row>
-    <row r="499" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:23" ns3:dyDescent="0.2">
       <c r="A499" s="61">
         <v>498</v>
       </c>
@@ -40966,7 +40969,7 @@
       <c r="U499" s="11"/>
       <c r="V499" s="10"/>
     </row>
-    <row r="500" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:23" ns3:dyDescent="0.2">
       <c r="A500" s="61">
         <v>499</v>
       </c>
@@ -41024,7 +41027,7 @@
       <c r="U500" s="11"/>
       <c r="V500" s="10"/>
     </row>
-    <row r="501" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:23" ns3:dyDescent="0.2">
       <c r="A501" s="61">
         <v>500</v>
       </c>
@@ -41082,7 +41085,7 @@
       <c r="U501" s="11"/>
       <c r="V501" s="10"/>
     </row>
-    <row r="502" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:23" ns3:dyDescent="0.2">
       <c r="A502" s="61">
         <v>501</v>
       </c>
@@ -41138,7 +41141,7 @@
       <c r="U502" s="11"/>
       <c r="V502" s="10"/>
     </row>
-    <row r="503" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:23" ns3:dyDescent="0.2">
       <c r="A503" s="61">
         <v>502</v>
       </c>
@@ -41194,7 +41197,7 @@
       <c r="U503" s="11"/>
       <c r="V503" s="10"/>
     </row>
-    <row r="504" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:23" ns3:dyDescent="0.2">
       <c r="A504" s="61">
         <v>503</v>
       </c>
@@ -41250,7 +41253,7 @@
       <c r="U504" s="11"/>
       <c r="V504" s="10"/>
     </row>
-    <row r="505" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A505" s="61">
         <v>504</v>
       </c>
@@ -41308,7 +41311,7 @@
       <c r="U505" s="11"/>
       <c r="V505" s="10"/>
     </row>
-    <row r="506" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A506" s="61">
         <v>505</v>
       </c>
@@ -41366,7 +41369,7 @@
       <c r="U506" s="11"/>
       <c r="V506" s="10"/>
     </row>
-    <row r="507" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:23" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A507" s="61">
         <v>506</v>
       </c>
@@ -41424,7 +41427,7 @@
       <c r="U507" s="11"/>
       <c r="V507" s="10"/>
     </row>
-    <row r="508" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:23" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A508" s="61">
         <v>507</v>
       </c>
@@ -41482,7 +41485,7 @@
       <c r="U508" s="11"/>
       <c r="V508" s="10"/>
     </row>
-    <row r="509" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:23" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A509" s="58">
         <v>508</v>
       </c>
@@ -41540,7 +41543,7 @@
       <c r="U509" s="11"/>
       <c r="V509" s="10"/>
     </row>
-    <row r="510" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:23" ns3:dyDescent="0.2">
       <c r="A510" s="58">
         <v>509</v>
       </c>
@@ -41598,7 +41601,7 @@
       <c r="U510" s="11"/>
       <c r="V510" s="10"/>
     </row>
-    <row r="511" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:23" ns3:dyDescent="0.2">
       <c r="A511" s="58">
         <v>510</v>
       </c>
@@ -41656,7 +41659,7 @@
       <c r="U511" s="11"/>
       <c r="V511" s="10"/>
     </row>
-    <row r="512" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:23" ns3:dyDescent="0.2">
       <c r="A512" s="58">
         <v>511</v>
       </c>
@@ -41714,7 +41717,7 @@
       <c r="U512" s="11"/>
       <c r="V512" s="10"/>
     </row>
-    <row r="513" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:22" ns3:dyDescent="0.2">
       <c r="A513" s="58">
         <v>512</v>
       </c>
@@ -41772,7 +41775,7 @@
       <c r="U513" s="11"/>
       <c r="V513" s="10"/>
     </row>
-    <row r="514" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:22" ns3:dyDescent="0.2">
       <c r="A514" s="58">
         <v>513</v>
       </c>
@@ -41830,7 +41833,7 @@
       <c r="U514" s="11"/>
       <c r="V514" s="10"/>
     </row>
-    <row r="515" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:22" ns3:dyDescent="0.2">
       <c r="A515" s="58">
         <v>514</v>
       </c>
@@ -41888,7 +41891,7 @@
       <c r="U515" s="11"/>
       <c r="V515" s="10"/>
     </row>
-    <row r="516" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:22" ns3:dyDescent="0.2">
       <c r="A516" s="58">
         <v>515</v>
       </c>
@@ -41946,7 +41949,7 @@
       <c r="U516" s="11"/>
       <c r="V516" s="10"/>
     </row>
-    <row r="517" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:22" ns3:dyDescent="0.2">
       <c r="A517" s="58">
         <v>516</v>
       </c>
@@ -42004,7 +42007,7 @@
       <c r="U517" s="11"/>
       <c r="V517" s="10"/>
     </row>
-    <row r="518" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:22" ns3:dyDescent="0.2">
       <c r="A518" s="61">
         <v>517</v>
       </c>
@@ -42062,7 +42065,7 @@
       <c r="U518" s="11"/>
       <c r="V518" s="10"/>
     </row>
-    <row r="519" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:22" ns3:dyDescent="0.2">
       <c r="A519" s="61">
         <v>518</v>
       </c>
@@ -42120,7 +42123,7 @@
       <c r="U519" s="11"/>
       <c r="V519" s="10"/>
     </row>
-    <row r="520" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:22" ns3:dyDescent="0.2">
       <c r="A520" s="61">
         <v>519</v>
       </c>
@@ -42180,7 +42183,7 @@
       <c r="U520" s="11"/>
       <c r="V520" s="10"/>
     </row>
-    <row r="521" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:22" ns3:dyDescent="0.2">
       <c r="A521" s="61">
         <v>520</v>
       </c>
@@ -42240,7 +42243,7 @@
       <c r="U521" s="11"/>
       <c r="V521" s="10"/>
     </row>
-    <row r="522" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:22" ns3:dyDescent="0.2">
       <c r="A522" s="61">
         <v>521</v>
       </c>
@@ -42300,7 +42303,7 @@
       <c r="U522" s="11"/>
       <c r="V522" s="10"/>
     </row>
-    <row r="523" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:22" ns3:dyDescent="0.2">
       <c r="A523" s="61">
         <v>522</v>
       </c>
@@ -42358,7 +42361,7 @@
       <c r="U523" s="11"/>
       <c r="V523" s="10"/>
     </row>
-    <row r="524" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:22" ns3:dyDescent="0.2">
       <c r="A524" s="61">
         <v>523</v>
       </c>
@@ -42416,7 +42419,7 @@
       <c r="U524" s="11"/>
       <c r="V524" s="10"/>
     </row>
-    <row r="525" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:22" ns3:dyDescent="0.2">
       <c r="A525" s="61">
         <v>524</v>
       </c>
@@ -42474,7 +42477,7 @@
       <c r="U525" s="11"/>
       <c r="V525" s="10"/>
     </row>
-    <row r="526" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:22" ns3:dyDescent="0.2">
       <c r="A526" s="61">
         <v>525</v>
       </c>
@@ -42532,7 +42535,7 @@
       <c r="U526" s="11"/>
       <c r="V526" s="10"/>
     </row>
-    <row r="527" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:22" ns3:dyDescent="0.2">
       <c r="A527" s="61">
         <v>526</v>
       </c>
@@ -42590,7 +42593,7 @@
       <c r="U527" s="11"/>
       <c r="V527" s="10"/>
     </row>
-    <row r="528" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:22" ns3:dyDescent="0.2">
       <c r="A528" s="61">
         <v>527</v>
       </c>
@@ -42650,7 +42653,7 @@
       <c r="U528" s="11"/>
       <c r="V528" s="10"/>
     </row>
-    <row r="529" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:22" ns3:dyDescent="0.2">
       <c r="A529" s="61">
         <v>528</v>
       </c>
@@ -42710,7 +42713,7 @@
       <c r="U529" s="11"/>
       <c r="V529" s="10"/>
     </row>
-    <row r="530" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A530" s="61">
         <v>529</v>
       </c>
@@ -42768,7 +42771,7 @@
       <c r="U530" s="11"/>
       <c r="V530" s="10"/>
     </row>
-    <row r="531" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A531" s="61">
         <v>530</v>
       </c>
@@ -42828,7 +42831,7 @@
       <c r="U531" s="11"/>
       <c r="V531" s="10"/>
     </row>
-    <row r="532" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A532" s="61">
         <v>531</v>
       </c>
@@ -42886,7 +42889,7 @@
       <c r="U532" s="11"/>
       <c r="V532" s="10"/>
     </row>
-    <row r="533" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:22" ns3:dyDescent="0.2">
       <c r="A533" s="61">
         <v>532</v>
       </c>
@@ -42944,7 +42947,7 @@
       <c r="U533" s="11"/>
       <c r="V533" s="10"/>
     </row>
-    <row r="534" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:22" ns3:dyDescent="0.2">
       <c r="A534" s="61">
         <v>533</v>
       </c>
@@ -43002,7 +43005,7 @@
       <c r="U534" s="11"/>
       <c r="V534" s="10"/>
     </row>
-    <row r="535" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:22" ns3:dyDescent="0.2">
       <c r="A535" s="61">
         <v>534</v>
       </c>
@@ -43060,7 +43063,7 @@
       <c r="U535" s="11"/>
       <c r="V535" s="10"/>
     </row>
-    <row r="536" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:22" ns3:dyDescent="0.2">
       <c r="A536" s="61">
         <v>535</v>
       </c>
@@ -43118,7 +43121,7 @@
       <c r="U536" s="11"/>
       <c r="V536" s="10"/>
     </row>
-    <row r="537" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:22" ns3:dyDescent="0.2">
       <c r="A537" s="61">
         <v>536</v>
       </c>
@@ -43178,7 +43181,7 @@
       <c r="U537" s="11"/>
       <c r="V537" s="10"/>
     </row>
-    <row r="538" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:22" ns3:dyDescent="0.2">
       <c r="A538" s="61">
         <v>537</v>
       </c>
@@ -43238,7 +43241,7 @@
       <c r="U538" s="11"/>
       <c r="V538" s="10"/>
     </row>
-    <row r="539" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:22" ns3:dyDescent="0.2">
       <c r="A539" s="61">
         <v>538</v>
       </c>
@@ -43296,7 +43299,7 @@
       <c r="U539" s="11"/>
       <c r="V539" s="10"/>
     </row>
-    <row r="540" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:22" ns3:dyDescent="0.2">
       <c r="A540" s="61">
         <v>539</v>
       </c>
@@ -43354,7 +43357,7 @@
       <c r="U540" s="11"/>
       <c r="V540" s="10"/>
     </row>
-    <row r="541" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:22" ns3:dyDescent="0.2">
       <c r="A541" s="61">
         <v>540</v>
       </c>
@@ -43414,7 +43417,7 @@
       <c r="U541" s="11"/>
       <c r="V541" s="10"/>
     </row>
-    <row r="542" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:22" ns3:dyDescent="0.2">
       <c r="A542" s="61">
         <v>541</v>
       </c>
@@ -43474,7 +43477,7 @@
       <c r="U542" s="11"/>
       <c r="V542" s="10"/>
     </row>
-    <row r="543" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:22" ns3:dyDescent="0.2">
       <c r="A543" s="61">
         <v>542</v>
       </c>
@@ -43534,7 +43537,7 @@
       <c r="U543" s="11"/>
       <c r="V543" s="10"/>
     </row>
-    <row r="544" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:22" ns3:dyDescent="0.2">
       <c r="A544" s="61">
         <v>543</v>
       </c>
@@ -43594,7 +43597,7 @@
       <c r="U544" s="11"/>
       <c r="V544" s="10"/>
     </row>
-    <row r="545" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:22" ns3:dyDescent="0.2">
       <c r="A545" s="61">
         <v>544</v>
       </c>
@@ -43654,7 +43657,7 @@
       <c r="U545" s="11"/>
       <c r="V545" s="10"/>
     </row>
-    <row r="546" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:22" ns3:dyDescent="0.2">
       <c r="A546" s="61">
         <v>545</v>
       </c>
@@ -43714,7 +43717,7 @@
       <c r="U546" s="11"/>
       <c r="V546" s="10"/>
     </row>
-    <row r="547" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:22" ns3:dyDescent="0.2">
       <c r="A547" s="61">
         <v>546</v>
       </c>
@@ -43774,7 +43777,7 @@
       <c r="U547" s="11"/>
       <c r="V547" s="10"/>
     </row>
-    <row r="548" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:22" ns3:dyDescent="0.2">
       <c r="A548" s="61">
         <v>547</v>
       </c>
@@ -43834,7 +43837,7 @@
       <c r="U548" s="11"/>
       <c r="V548" s="10"/>
     </row>
-    <row r="549" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A549" s="61">
         <v>548</v>
       </c>
@@ -43892,7 +43895,7 @@
       <c r="U549" s="11"/>
       <c r="V549" s="10"/>
     </row>
-    <row r="550" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A550" s="61">
         <v>549</v>
       </c>
@@ -43949,7 +43952,7 @@
       <c r="U550" s="11"/>
       <c r="V550" s="10"/>
     </row>
-    <row r="551" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:22" ns3:dyDescent="0.2">
       <c r="A551" s="61">
         <v>550</v>
       </c>
@@ -43997,10 +44000,10 @@
         <v>5</v>
       </c>
       <c r="Q551" s="70" t="s">
-        <v>1256</v>
+        <v>1994</v>
       </c>
       <c r="R551" t="s">
-        <v>1257</v>
+        <v>3576</v>
       </c>
       <c r="S551" s="11" t="s">
         <v>29</v>
@@ -44009,7 +44012,7 @@
       <c r="U551" s="11"/>
       <c r="V551" s="10"/>
     </row>
-    <row r="552" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:22" ns3:dyDescent="0.2">
       <c r="A552" s="61">
         <v>551</v>
       </c>
@@ -44069,7 +44072,7 @@
       <c r="U552" s="11"/>
       <c r="V552" s="10"/>
     </row>
-    <row r="553" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:22" ns3:dyDescent="0.2">
       <c r="A553" s="61">
         <v>552</v>
       </c>
@@ -44129,7 +44132,7 @@
       <c r="U553" s="11"/>
       <c r="V553" s="10"/>
     </row>
-    <row r="554" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:22" ns3:dyDescent="0.2">
       <c r="A554" s="61">
         <v>553</v>
       </c>
@@ -44189,7 +44192,7 @@
       <c r="U554" s="11"/>
       <c r="V554" s="10"/>
     </row>
-    <row r="555" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:22" ns3:dyDescent="0.2">
       <c r="A555" s="61">
         <v>554</v>
       </c>
@@ -44245,7 +44248,7 @@
       <c r="U555" s="11"/>
       <c r="V555" s="10"/>
     </row>
-    <row r="556" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:22" ns3:dyDescent="0.2">
       <c r="A556" s="61">
         <v>555</v>
       </c>
@@ -44303,7 +44306,7 @@
       <c r="U556" s="11"/>
       <c r="V556" s="10"/>
     </row>
-    <row r="557" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:22" ns3:dyDescent="0.2">
       <c r="A557" s="61">
         <v>556</v>
       </c>
@@ -44361,7 +44364,7 @@
       <c r="U557" s="11"/>
       <c r="V557" s="10"/>
     </row>
-    <row r="558" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A558" s="61">
         <v>557</v>
       </c>
@@ -44421,7 +44424,7 @@
       <c r="U558" s="11"/>
       <c r="V558" s="10"/>
     </row>
-    <row r="559" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A559" s="61">
         <v>558</v>
       </c>
@@ -44483,7 +44486,7 @@
       </c>
       <c r="V559" s="10"/>
     </row>
-    <row r="560" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:22" ns3:dyDescent="0.2">
       <c r="A560" s="61">
         <v>559</v>
       </c>
@@ -44542,7 +44545,7 @@
       <c r="T560" s="10"/>
       <c r="V560" s="10"/>
     </row>
-    <row r="561" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A561" s="61">
         <v>560</v>
       </c>
@@ -44604,7 +44607,7 @@
       </c>
       <c r="V561" s="10"/>
     </row>
-    <row r="562" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A562" s="58">
         <v>561</v>
       </c>
@@ -44668,7 +44671,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="563" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A563" s="61">
         <v>562</v>
       </c>
@@ -44723,7 +44726,7 @@
         <v>3245</v>
       </c>
     </row>
-    <row r="564" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A564" s="61">
         <v>563</v>
       </c>
@@ -44781,7 +44784,7 @@
         <v>3456</v>
       </c>
     </row>
-    <row r="565" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A565" s="61">
         <v>564</v>
       </c>
@@ -44843,7 +44846,7 @@
         <v>3457</v>
       </c>
     </row>
-    <row r="566" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A566" s="61">
         <v>565</v>
       </c>
@@ -44905,7 +44908,7 @@
         <v>3458</v>
       </c>
     </row>
-    <row r="567" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A567" s="61">
         <v>566</v>
       </c>
@@ -44963,7 +44966,7 @@
         <v>3459</v>
       </c>
     </row>
-    <row r="568" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A568" s="61">
         <v>567</v>
       </c>
@@ -45021,7 +45024,7 @@
         <v>3460</v>
       </c>
     </row>
-    <row r="569" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A569" s="61">
         <v>568</v>
       </c>
@@ -45079,7 +45082,7 @@
       <c r="U569" s="11"/>
       <c r="V569" s="10"/>
     </row>
-    <row r="570" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A570" s="61">
         <v>569</v>
       </c>
@@ -45139,7 +45142,7 @@
       <c r="U570" s="11"/>
       <c r="V570" s="10"/>
     </row>
-    <row r="571" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:22" ht="17" customHeight="1" ns3:dyDescent="0.2">
       <c r="A571" s="58">
         <v>570</v>
       </c>
@@ -45192,7 +45195,7 @@
       <c r="U571" s="11"/>
       <c r="V571" s="10"/>
     </row>
-    <row r="572" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A572" s="58">
         <v>571</v>
       </c>
@@ -45248,7 +45251,7 @@
       <c r="U572" s="11"/>
       <c r="V572" s="10"/>
     </row>
-    <row r="573" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A573" s="61">
         <v>572</v>
       </c>
@@ -45308,7 +45311,7 @@
       <c r="U573" s="11"/>
       <c r="V573" s="10"/>
     </row>
-    <row r="574" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A574" s="61">
         <v>573</v>
       </c>
@@ -45368,7 +45371,7 @@
       <c r="U574" s="11"/>
       <c r="V574" s="10"/>
     </row>
-    <row r="575" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A575" s="58">
         <v>574</v>
       </c>
@@ -45428,7 +45431,7 @@
       <c r="U575" s="11"/>
       <c r="V575" s="10"/>
     </row>
-    <row r="576" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A576" s="58">
         <v>575</v>
       </c>
@@ -45488,7 +45491,7 @@
       <c r="U576" s="11"/>
       <c r="V576" s="10"/>
     </row>
-    <row r="577" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A577" s="58">
         <v>576</v>
       </c>
@@ -45548,7 +45551,7 @@
       <c r="U577" s="11"/>
       <c r="V577" s="10"/>
     </row>
-    <row r="578" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A578" s="58">
         <v>577</v>
       </c>
@@ -45608,7 +45611,7 @@
       <c r="U578" s="11"/>
       <c r="V578" s="10"/>
     </row>
-    <row r="579" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A579" s="58">
         <v>578</v>
       </c>
@@ -45668,7 +45671,7 @@
       <c r="U579" s="11"/>
       <c r="V579" s="10"/>
     </row>
-    <row r="580" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A580" s="58">
         <v>579</v>
       </c>
@@ -45728,7 +45731,7 @@
       <c r="U580" s="11"/>
       <c r="V580" s="10"/>
     </row>
-    <row r="581" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A581" s="61">
         <v>580</v>
       </c>
@@ -45790,7 +45793,7 @@
       <c r="U581" s="11"/>
       <c r="V581" s="10"/>
     </row>
-    <row r="582" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:22" ns3:dyDescent="0.2">
       <c r="A582" s="61">
         <v>581</v>
       </c>
@@ -45850,7 +45853,7 @@
       <c r="U582" s="11"/>
       <c r="V582" s="10"/>
     </row>
-    <row r="583" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:22" ns3:dyDescent="0.2">
       <c r="A583" s="61">
         <v>582</v>
       </c>
@@ -45908,7 +45911,7 @@
       <c r="U583" s="11"/>
       <c r="V583" s="10"/>
     </row>
-    <row r="584" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:22" ns3:dyDescent="0.2">
       <c r="A584" s="61">
         <v>583</v>
       </c>
@@ -45966,7 +45969,7 @@
       <c r="U584" s="11"/>
       <c r="V584" s="10"/>
     </row>
-    <row r="585" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:22" ns3:dyDescent="0.2">
       <c r="A585" s="61">
         <v>584</v>
       </c>
@@ -46024,7 +46027,7 @@
       <c r="U585" s="11"/>
       <c r="V585" s="10"/>
     </row>
-    <row r="586" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:22" ns3:dyDescent="0.2">
       <c r="A586" s="61">
         <v>585</v>
       </c>
@@ -46084,7 +46087,7 @@
       <c r="U586" s="11"/>
       <c r="V586" s="10"/>
     </row>
-    <row r="587" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:22" ns3:dyDescent="0.2">
       <c r="A587" s="61">
         <v>586</v>
       </c>
@@ -46144,7 +46147,7 @@
       <c r="U587" s="11"/>
       <c r="V587" s="10"/>
     </row>
-    <row r="588" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:22" ns3:dyDescent="0.2">
       <c r="A588" s="61">
         <v>587</v>
       </c>
@@ -46202,7 +46205,7 @@
       <c r="U588" s="11"/>
       <c r="V588" s="10"/>
     </row>
-    <row r="589" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:22" ns3:dyDescent="0.2">
       <c r="A589" s="61">
         <v>588</v>
       </c>
@@ -46260,7 +46263,7 @@
       <c r="U589" s="11"/>
       <c r="V589" s="10"/>
     </row>
-    <row r="590" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:22" ns3:dyDescent="0.2">
       <c r="A590" s="61">
         <v>589</v>
       </c>
@@ -46320,7 +46323,7 @@
       <c r="U590" s="11"/>
       <c r="V590" s="10"/>
     </row>
-    <row r="591" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:22" ns3:dyDescent="0.2">
       <c r="A591" s="58">
         <v>590</v>
       </c>
@@ -46378,7 +46381,7 @@
       <c r="U591" s="11"/>
       <c r="V591" s="10"/>
     </row>
-    <row r="592" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:22" ns3:dyDescent="0.2">
       <c r="A592" s="58">
         <v>591</v>
       </c>
@@ -46436,7 +46439,7 @@
       <c r="U592" s="11"/>
       <c r="V592" s="10"/>
     </row>
-    <row r="593" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:22" ns3:dyDescent="0.2">
       <c r="A593" s="61">
         <v>592</v>
       </c>
@@ -46496,7 +46499,7 @@
       <c r="U593" s="11"/>
       <c r="V593" s="10"/>
     </row>
-    <row r="594" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:22" ns3:dyDescent="0.2">
       <c r="A594" s="61">
         <v>593</v>
       </c>
@@ -46556,7 +46559,7 @@
       <c r="U594" s="11"/>
       <c r="V594" s="10"/>
     </row>
-    <row r="595" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:22" ns3:dyDescent="0.2">
       <c r="A595" s="61">
         <v>594</v>
       </c>
@@ -46614,7 +46617,7 @@
       <c r="U595" s="11"/>
       <c r="V595" s="10"/>
     </row>
-    <row r="596" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:22" ns3:dyDescent="0.2">
       <c r="A596" s="61">
         <v>595</v>
       </c>
@@ -46674,7 +46677,7 @@
       <c r="U596" s="11"/>
       <c r="V596" s="10"/>
     </row>
-    <row r="597" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:22" ns3:dyDescent="0.2">
       <c r="A597" s="61">
         <v>596</v>
       </c>
@@ -46734,7 +46737,7 @@
       <c r="U597" s="11"/>
       <c r="V597" s="10"/>
     </row>
-    <row r="598" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:22" ns3:dyDescent="0.2">
       <c r="A598" s="58">
         <v>597</v>
       </c>
@@ -46790,7 +46793,7 @@
       <c r="U598" s="11"/>
       <c r="V598" s="10"/>
     </row>
-    <row r="599" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:22" ns3:dyDescent="0.2">
       <c r="A599" s="58">
         <v>598</v>
       </c>
@@ -46846,7 +46849,7 @@
       <c r="U599" s="11"/>
       <c r="V599" s="10"/>
     </row>
-    <row r="600" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:22" ns3:dyDescent="0.2">
       <c r="A600" s="61">
         <v>599</v>
       </c>
@@ -46904,7 +46907,7 @@
       <c r="U600" s="11"/>
       <c r="V600" s="10"/>
     </row>
-    <row r="601" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:22" ns3:dyDescent="0.2">
       <c r="A601" s="61">
         <v>600</v>
       </c>
@@ -46962,7 +46965,7 @@
       <c r="U601" s="11"/>
       <c r="V601" s="10"/>
     </row>
-    <row r="602" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:22" ns3:dyDescent="0.2">
       <c r="A602" s="61">
         <v>601</v>
       </c>
@@ -47020,7 +47023,7 @@
       <c r="U602" s="11"/>
       <c r="V602" s="10"/>
     </row>
-    <row r="603" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:22" ns3:dyDescent="0.2">
       <c r="A603" s="61">
         <v>602</v>
       </c>
@@ -47074,7 +47077,7 @@
       <c r="U603" s="11"/>
       <c r="V603" s="10"/>
     </row>
-    <row r="604" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:22" ns3:dyDescent="0.2">
       <c r="A604" s="61">
         <v>603</v>
       </c>
@@ -47128,7 +47131,7 @@
       <c r="U604" s="11"/>
       <c r="V604" s="10"/>
     </row>
-    <row r="605" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:22" ns3:dyDescent="0.2">
       <c r="A605" s="61">
         <v>604</v>
       </c>
@@ -47182,7 +47185,7 @@
       <c r="U605" s="11"/>
       <c r="V605" s="10"/>
     </row>
-    <row r="606" spans="1:22" ht="96" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:22" ht="96" ns3:dyDescent="0.25">
       <c r="A606" s="58">
         <v>605</v>
       </c>
@@ -47242,7 +47245,7 @@
       <c r="U606" s="11"/>
       <c r="V606" s="10"/>
     </row>
-    <row r="607" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A607" s="58">
         <v>606</v>
       </c>
@@ -47300,7 +47303,7 @@
       <c r="U607" s="11"/>
       <c r="V607" s="10"/>
     </row>
-    <row r="608" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:22" ns3:dyDescent="0.2">
       <c r="A608" s="58">
         <v>607</v>
       </c>
@@ -47360,7 +47363,7 @@
       <c r="U608" s="11"/>
       <c r="V608" s="10"/>
     </row>
-    <row r="609" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:22" ns3:dyDescent="0.2">
       <c r="A609" s="58">
         <v>608</v>
       </c>
@@ -47420,7 +47423,7 @@
       <c r="U609" s="11"/>
       <c r="V609" s="10"/>
     </row>
-    <row r="610" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:22" ns3:dyDescent="0.2">
       <c r="A610" s="58">
         <v>609</v>
       </c>
@@ -47480,7 +47483,7 @@
       <c r="U610" s="11"/>
       <c r="V610" s="10"/>
     </row>
-    <row r="611" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:22" ns3:dyDescent="0.2">
       <c r="A611" s="58">
         <v>610</v>
       </c>
@@ -47538,7 +47541,7 @@
       <c r="U611" s="11"/>
       <c r="V611" s="10"/>
     </row>
-    <row r="612" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:22" ns3:dyDescent="0.2">
       <c r="A612" s="58">
         <v>611</v>
       </c>
@@ -47596,7 +47599,7 @@
       <c r="U612" s="11"/>
       <c r="V612" s="10"/>
     </row>
-    <row r="613" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:22" ns3:dyDescent="0.2">
       <c r="A613" s="58">
         <v>612</v>
       </c>
@@ -47654,7 +47657,7 @@
       <c r="U613" s="11"/>
       <c r="V613" s="10"/>
     </row>
-    <row r="614" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A614" s="61">
         <v>613</v>
       </c>
@@ -47714,7 +47717,7 @@
       <c r="U614" s="11"/>
       <c r="V614" s="10"/>
     </row>
-    <row r="615" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A615" s="61">
         <v>614</v>
       </c>
@@ -47771,7 +47774,7 @@
       <c r="U615" s="11"/>
       <c r="V615" s="10"/>
     </row>
-    <row r="616" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A616" s="61">
         <v>615</v>
       </c>
@@ -47827,7 +47830,7 @@
       <c r="U616" s="11"/>
       <c r="V616" s="10"/>
     </row>
-    <row r="617" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A617" s="61">
         <v>616</v>
       </c>
@@ -47887,7 +47890,7 @@
       <c r="U617" s="11"/>
       <c r="V617" s="10"/>
     </row>
-    <row r="618" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A618" s="61">
         <v>617</v>
       </c>
@@ -47947,7 +47950,7 @@
       <c r="U618" s="11"/>
       <c r="V618" s="10"/>
     </row>
-    <row r="619" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A619" s="61">
         <v>618</v>
       </c>
@@ -48009,7 +48012,7 @@
       <c r="U619" s="11"/>
       <c r="V619" s="10"/>
     </row>
-    <row r="620" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A620" s="61">
         <v>619</v>
       </c>
@@ -48069,7 +48072,7 @@
       <c r="U620" s="11"/>
       <c r="V620" s="10"/>
     </row>
-    <row r="621" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:22" ns3:dyDescent="0.2">
       <c r="A621" s="61">
         <v>620</v>
       </c>
@@ -48127,7 +48130,7 @@
       <c r="U621" s="11"/>
       <c r="V621" s="10"/>
     </row>
-    <row r="622" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:22" ns3:dyDescent="0.2">
       <c r="A622" s="61">
         <v>621</v>
       </c>
@@ -48185,7 +48188,7 @@
       <c r="U622" s="11"/>
       <c r="V622" s="10"/>
     </row>
-    <row r="623" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:22" ns3:dyDescent="0.2">
       <c r="A623" s="61">
         <v>622</v>
       </c>
@@ -48245,7 +48248,7 @@
       <c r="U623" s="11"/>
       <c r="V623" s="10"/>
     </row>
-    <row r="624" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:22" ns3:dyDescent="0.2">
       <c r="A624" s="61">
         <v>623</v>
       </c>
@@ -48305,7 +48308,7 @@
       <c r="U624" s="11"/>
       <c r="V624" s="10"/>
     </row>
-    <row r="625" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:22" ns3:dyDescent="0.2">
       <c r="A625" s="61">
         <v>624</v>
       </c>
@@ -48365,7 +48368,7 @@
       <c r="U625" s="11"/>
       <c r="V625" s="10"/>
     </row>
-    <row r="626" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:22" ns3:dyDescent="0.2">
       <c r="A626" s="61">
         <v>625</v>
       </c>
@@ -48425,7 +48428,7 @@
       <c r="U626" s="11"/>
       <c r="V626" s="10"/>
     </row>
-    <row r="627" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:22" ns3:dyDescent="0.2">
       <c r="A627" s="61">
         <v>626</v>
       </c>
@@ -48483,7 +48486,7 @@
       <c r="U627" s="11"/>
       <c r="V627" s="10"/>
     </row>
-    <row r="628" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:22" ns3:dyDescent="0.2">
       <c r="A628" s="61">
         <v>627</v>
       </c>
@@ -48543,7 +48546,7 @@
       <c r="U628" s="11"/>
       <c r="V628" s="10"/>
     </row>
-    <row r="629" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:22" ns3:dyDescent="0.2">
       <c r="A629" s="61">
         <v>628</v>
       </c>
@@ -48603,7 +48606,7 @@
       <c r="U629" s="11"/>
       <c r="V629" s="10"/>
     </row>
-    <row r="630" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:22" ns3:dyDescent="0.2">
       <c r="A630" s="61">
         <v>629</v>
       </c>
@@ -48663,7 +48666,7 @@
       <c r="U630" s="11"/>
       <c r="V630" s="10"/>
     </row>
-    <row r="631" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:22" ns3:dyDescent="0.2">
       <c r="A631" s="61">
         <v>630</v>
       </c>
@@ -48723,7 +48726,7 @@
       <c r="U631" s="11"/>
       <c r="V631" s="10"/>
     </row>
-    <row r="632" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:22" ns3:dyDescent="0.2">
       <c r="A632" s="61">
         <v>631</v>
       </c>
@@ -48781,7 +48784,7 @@
       <c r="U632" s="11"/>
       <c r="V632" s="10"/>
     </row>
-    <row r="633" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:22" ns3:dyDescent="0.2">
       <c r="A633" s="61">
         <v>632</v>
       </c>
@@ -48841,7 +48844,7 @@
       <c r="U633" s="11"/>
       <c r="V633" s="10"/>
     </row>
-    <row r="634" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:22" ns3:dyDescent="0.2">
       <c r="A634" s="58">
         <v>633</v>
       </c>
@@ -48897,7 +48900,7 @@
       <c r="U634" s="11"/>
       <c r="V634" s="10"/>
     </row>
-    <row r="635" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:22" ns3:dyDescent="0.2">
       <c r="A635" s="58">
         <v>634</v>
       </c>
@@ -48953,7 +48956,7 @@
       <c r="U635" s="11"/>
       <c r="V635" s="10"/>
     </row>
-    <row r="636" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:22" ns3:dyDescent="0.2">
       <c r="A636" s="58">
         <v>635</v>
       </c>
@@ -49009,7 +49012,7 @@
       <c r="U636" s="11"/>
       <c r="V636" s="10"/>
     </row>
-    <row r="637" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:22" ns3:dyDescent="0.2">
       <c r="A637" s="61">
         <v>636</v>
       </c>
@@ -49067,7 +49070,7 @@
       <c r="U637" s="11"/>
       <c r="V637" s="10"/>
     </row>
-    <row r="638" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:22" ns3:dyDescent="0.2">
       <c r="A638" s="61">
         <v>637</v>
       </c>
@@ -49125,7 +49128,7 @@
       <c r="U638" s="11"/>
       <c r="V638" s="10"/>
     </row>
-    <row r="639" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:22" ns3:dyDescent="0.2">
       <c r="A639" s="61">
         <v>638</v>
       </c>
@@ -49181,7 +49184,7 @@
       <c r="U639" s="11"/>
       <c r="V639" s="10"/>
     </row>
-    <row r="640" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:22" ns3:dyDescent="0.2">
       <c r="A640" s="61">
         <v>639</v>
       </c>
@@ -49237,7 +49240,7 @@
       <c r="U640" s="11"/>
       <c r="V640" s="10"/>
     </row>
-    <row r="641" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:22" ns3:dyDescent="0.2">
       <c r="A641" s="61">
         <v>640</v>
       </c>
@@ -49293,7 +49296,7 @@
       <c r="U641" s="11"/>
       <c r="V641" s="10"/>
     </row>
-    <row r="642" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:22" ns3:dyDescent="0.2">
       <c r="A642" s="61">
         <v>641</v>
       </c>
@@ -49351,7 +49354,7 @@
       <c r="U642" s="11"/>
       <c r="V642" s="10"/>
     </row>
-    <row r="643" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:22" ns3:dyDescent="0.2">
       <c r="A643" s="61">
         <v>642</v>
       </c>
@@ -49411,7 +49414,7 @@
       <c r="U643" s="11"/>
       <c r="V643" s="10"/>
     </row>
-    <row r="644" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:22" ns3:dyDescent="0.2">
       <c r="A644" s="61">
         <v>643</v>
       </c>
@@ -49467,7 +49470,7 @@
       <c r="U644" s="11"/>
       <c r="V644" s="10"/>
     </row>
-    <row r="645" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:22" ns3:dyDescent="0.2">
       <c r="A645" s="61">
         <v>644</v>
       </c>
@@ -49523,7 +49526,7 @@
       <c r="U645" s="11"/>
       <c r="V645" s="10"/>
     </row>
-    <row r="646" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:22" ns3:dyDescent="0.2">
       <c r="A646" s="61">
         <v>645</v>
       </c>
@@ -49583,7 +49586,7 @@
       <c r="U646" s="11"/>
       <c r="V646" s="10"/>
     </row>
-    <row r="647" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:22" ns3:dyDescent="0.2">
       <c r="A647" s="61">
         <v>646</v>
       </c>
@@ -49639,7 +49642,7 @@
       <c r="U647" s="11"/>
       <c r="V647" s="10"/>
     </row>
-    <row r="648" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:22" ns3:dyDescent="0.2">
       <c r="A648" s="61">
         <v>647</v>
       </c>
@@ -49697,7 +49700,7 @@
       <c r="U648" s="11"/>
       <c r="V648" s="10"/>
     </row>
-    <row r="649" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:22" ns3:dyDescent="0.2">
       <c r="A649" s="61">
         <v>648</v>
       </c>
@@ -49755,7 +49758,7 @@
       <c r="U649" s="11"/>
       <c r="V649" s="10"/>
     </row>
-    <row r="650" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:22" ns3:dyDescent="0.2">
       <c r="A650" s="61">
         <v>649</v>
       </c>
@@ -49811,7 +49814,7 @@
       <c r="U650" s="11"/>
       <c r="V650" s="10"/>
     </row>
-    <row r="651" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A651" s="61">
         <v>650</v>
       </c>
@@ -49867,7 +49870,7 @@
       <c r="U651" s="11"/>
       <c r="V651" s="10"/>
     </row>
-    <row r="652" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A652" s="61">
         <v>651</v>
       </c>
@@ -49923,7 +49926,7 @@
       <c r="U652" s="11"/>
       <c r="V652" s="10"/>
     </row>
-    <row r="653" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A653" s="61">
         <v>652</v>
       </c>
@@ -49983,7 +49986,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="654" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:22" ns3:dyDescent="0.2">
       <c r="A654" s="61">
         <v>653</v>
       </c>
@@ -50040,7 +50043,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="655" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A655" s="61">
         <v>654</v>
       </c>
@@ -50097,7 +50100,7 @@
         <v>3245</v>
       </c>
     </row>
-    <row r="656" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A656" s="61">
         <v>655</v>
       </c>
@@ -50159,7 +50162,7 @@
         <v>3329</v>
       </c>
     </row>
-    <row r="657" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A657" s="61">
         <v>656</v>
       </c>
@@ -50219,7 +50222,7 @@
         <v>3364</v>
       </c>
     </row>
-    <row r="658" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A658" s="61">
         <v>657</v>
       </c>
@@ -50279,7 +50282,7 @@
         <v>3365</v>
       </c>
     </row>
-    <row r="659" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A659" s="61">
         <v>658</v>
       </c>
@@ -50344,7 +50347,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="660" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A660" s="61">
         <v>659</v>
       </c>
@@ -50408,7 +50411,7 @@
         <v>3367</v>
       </c>
     </row>
-    <row r="661" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A661" s="61">
         <v>660</v>
       </c>
@@ -50477,7 +50480,7 @@
         <v>3274</v>
       </c>
     </row>
-    <row r="662" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A662" s="58">
         <v>661</v>
       </c>
@@ -50544,7 +50547,7 @@
         <v>3373</v>
       </c>
     </row>
-    <row r="663" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A663" s="58">
         <v>662</v>
       </c>
@@ -50611,7 +50614,7 @@
         <v>3249</v>
       </c>
     </row>
-    <row r="664" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A664" s="58">
         <v>663</v>
       </c>
@@ -50678,7 +50681,7 @@
         <v>3374</v>
       </c>
     </row>
-    <row r="665" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A665" s="61">
         <v>664</v>
       </c>
@@ -50743,7 +50746,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="666" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A666" s="61">
         <v>665</v>
       </c>
@@ -50806,7 +50809,7 @@
         <v>3376</v>
       </c>
     </row>
-    <row r="667" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A667" s="61">
         <v>666</v>
       </c>
@@ -50871,7 +50874,7 @@
         <v>3245</v>
       </c>
     </row>
-    <row r="668" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A668" s="61">
         <v>667</v>
       </c>
@@ -50934,7 +50937,7 @@
         <v>3271</v>
       </c>
     </row>
-    <row r="669" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A669" s="61">
         <v>668</v>
       </c>
@@ -50997,7 +51000,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="670" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A670" s="61">
         <v>669</v>
       </c>
@@ -51056,7 +51059,7 @@
         <v>3344</v>
       </c>
     </row>
-    <row r="671" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A671" s="61">
         <v>670</v>
       </c>
@@ -51115,7 +51118,7 @@
         <v>3353</v>
       </c>
     </row>
-    <row r="672" spans="1:23" ht="16" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:23" ht="16" ns3:dyDescent="0.25">
       <c r="A672" s="61">
         <v>671</v>
       </c>
@@ -51174,7 +51177,7 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="673" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:22" ns3:dyDescent="0.2">
       <c r="A673" s="61">
         <v>672</v>
       </c>
@@ -51230,7 +51233,7 @@
       <c r="U673" s="11"/>
       <c r="V673" s="10"/>
     </row>
-    <row r="674" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:22" ns3:dyDescent="0.2">
       <c r="A674" s="61">
         <v>673</v>
       </c>
@@ -51286,7 +51289,7 @@
       <c r="U674" s="11"/>
       <c r="V674" s="10"/>
     </row>
-    <row r="675" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:22" ns3:dyDescent="0.2">
       <c r="A675" s="61">
         <v>674</v>
       </c>
@@ -51344,7 +51347,7 @@
       <c r="U675" s="11"/>
       <c r="V675" s="10"/>
     </row>
-    <row r="676" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:22" ns3:dyDescent="0.2">
       <c r="A676" s="61">
         <v>675</v>
       </c>
@@ -51404,7 +51407,7 @@
       <c r="U676" s="11"/>
       <c r="V676" s="10"/>
     </row>
-    <row r="677" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A677" s="61">
         <v>676</v>
       </c>
@@ -51458,7 +51461,7 @@
       <c r="U677" s="11"/>
       <c r="V677" s="10"/>
     </row>
-    <row r="678" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:22" ns3:dyDescent="0.2">
       <c r="A678" s="61">
         <v>677</v>
       </c>
@@ -51516,7 +51519,7 @@
       <c r="U678" s="11"/>
       <c r="V678" s="10"/>
     </row>
-    <row r="679" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:22" ns3:dyDescent="0.2">
       <c r="A679" s="61">
         <v>678</v>
       </c>
@@ -51576,7 +51579,7 @@
       <c r="U679" s="11"/>
       <c r="V679" s="10"/>
     </row>
-    <row r="680" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A680" s="58">
         <v>679</v>
       </c>
@@ -51632,7 +51635,7 @@
       <c r="U680" s="11"/>
       <c r="V680" s="10"/>
     </row>
-    <row r="681" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A681" s="58">
         <v>680</v>
       </c>
@@ -51688,7 +51691,7 @@
       <c r="U681" s="11"/>
       <c r="V681" s="10"/>
     </row>
-    <row r="682" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A682" s="58">
         <v>681</v>
       </c>
@@ -51746,7 +51749,7 @@
       <c r="U682" s="11"/>
       <c r="V682" s="10"/>
     </row>
-    <row r="683" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:22" ns3:dyDescent="0.2">
       <c r="A683" s="61">
         <v>682</v>
       </c>
@@ -51802,7 +51805,7 @@
       <c r="U683" s="11"/>
       <c r="V683" s="10"/>
     </row>
-    <row r="684" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:22" ns3:dyDescent="0.2">
       <c r="A684" s="61">
         <v>683</v>
       </c>
@@ -51858,7 +51861,7 @@
       <c r="U684" s="11"/>
       <c r="V684" s="10"/>
     </row>
-    <row r="685" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:22" ns3:dyDescent="0.2">
       <c r="A685" s="61">
         <v>684</v>
       </c>
@@ -51914,7 +51917,7 @@
       <c r="U685" s="11"/>
       <c r="V685" s="10"/>
     </row>
-    <row r="686" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:22" ns3:dyDescent="0.2">
       <c r="A686" s="61">
         <v>685</v>
       </c>
@@ -51970,7 +51973,7 @@
       <c r="U686" s="11"/>
       <c r="V686" s="10"/>
     </row>
-    <row r="687" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:22" ns3:dyDescent="0.2">
       <c r="A687" s="61">
         <v>686</v>
       </c>
@@ -52030,7 +52033,7 @@
       <c r="U687" s="11"/>
       <c r="V687" s="10"/>
     </row>
-    <row r="688" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:22" ns3:dyDescent="0.2">
       <c r="A688" s="61">
         <v>687</v>
       </c>
@@ -52090,7 +52093,7 @@
       <c r="U688" s="11"/>
       <c r="V688" s="10"/>
     </row>
-    <row r="689" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:22" ns3:dyDescent="0.2">
       <c r="A689" s="61">
         <v>688</v>
       </c>
@@ -52150,7 +52153,7 @@
       <c r="U689" s="11"/>
       <c r="V689" s="10"/>
     </row>
-    <row r="690" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:22" ns3:dyDescent="0.2">
       <c r="A690" s="61">
         <v>689</v>
       </c>
@@ -52210,7 +52213,7 @@
       <c r="U690" s="11"/>
       <c r="V690" s="10"/>
     </row>
-    <row r="691" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:22" ns3:dyDescent="0.2">
       <c r="A691" s="61">
         <v>690</v>
       </c>
@@ -52270,7 +52273,7 @@
       <c r="U691" s="11"/>
       <c r="V691" s="10"/>
     </row>
-    <row r="692" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:22" ns3:dyDescent="0.2">
       <c r="A692" s="61">
         <v>691</v>
       </c>
@@ -52330,7 +52333,7 @@
       <c r="U692" s="11"/>
       <c r="V692" s="10"/>
     </row>
-    <row r="693" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:22" ns3:dyDescent="0.2">
       <c r="A693" s="61">
         <v>692</v>
       </c>
@@ -52384,7 +52387,7 @@
       <c r="U693" s="11"/>
       <c r="V693" s="10"/>
     </row>
-    <row r="694" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:22" ns3:dyDescent="0.2">
       <c r="A694" s="61">
         <v>693</v>
       </c>
@@ -52438,7 +52441,7 @@
       <c r="U694" s="11"/>
       <c r="V694" s="10"/>
     </row>
-    <row r="695" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A695" s="61">
         <v>694</v>
       </c>
@@ -52498,7 +52501,7 @@
       <c r="U695" s="11"/>
       <c r="V695" s="10"/>
     </row>
-    <row r="696" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A696" s="61">
         <v>695</v>
       </c>
@@ -52558,7 +52561,7 @@
       <c r="U696" s="11"/>
       <c r="V696" s="10"/>
     </row>
-    <row r="697" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:22" ns3:dyDescent="0.2">
       <c r="A697" s="61">
         <v>696</v>
       </c>
@@ -52616,7 +52619,7 @@
       <c r="U697" s="11"/>
       <c r="V697" s="10"/>
     </row>
-    <row r="698" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:22" ns3:dyDescent="0.2">
       <c r="A698" s="61">
         <v>697</v>
       </c>
@@ -52674,7 +52677,7 @@
       <c r="U698" s="11"/>
       <c r="V698" s="10"/>
     </row>
-    <row r="699" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:22" ns3:dyDescent="0.2">
       <c r="A699" s="61">
         <v>698</v>
       </c>
@@ -52732,7 +52735,7 @@
       <c r="U699" s="11"/>
       <c r="V699" s="10"/>
     </row>
-    <row r="700" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:22" ns3:dyDescent="0.2">
       <c r="A700" s="61">
         <v>699</v>
       </c>
@@ -52790,7 +52793,7 @@
       <c r="U700" s="11"/>
       <c r="V700" s="10"/>
     </row>
-    <row r="701" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:22" ns3:dyDescent="0.2">
       <c r="A701" s="61">
         <v>700</v>
       </c>
@@ -52846,7 +52849,7 @@
       <c r="U701" s="11"/>
       <c r="V701" s="10"/>
     </row>
-    <row r="702" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:22" ns3:dyDescent="0.2">
       <c r="A702" s="61">
         <v>701</v>
       </c>
@@ -52906,7 +52909,7 @@
       <c r="U702" s="11"/>
       <c r="V702" s="10"/>
     </row>
-    <row r="703" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:22" ns3:dyDescent="0.2">
       <c r="A703" s="61">
         <v>702</v>
       </c>
@@ -52966,7 +52969,7 @@
       <c r="U703" s="11"/>
       <c r="V703" s="10"/>
     </row>
-    <row r="704" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:22" ns3:dyDescent="0.2">
       <c r="A704" s="61">
         <v>703</v>
       </c>
@@ -53024,7 +53027,7 @@
       <c r="U704" s="11"/>
       <c r="V704" s="10"/>
     </row>
-    <row r="705" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:22" ns3:dyDescent="0.2">
       <c r="A705" s="61">
         <v>704</v>
       </c>
@@ -53082,7 +53085,7 @@
       <c r="U705" s="11"/>
       <c r="V705" s="10"/>
     </row>
-    <row r="706" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:22" ns3:dyDescent="0.2">
       <c r="A706" s="61">
         <v>705</v>
       </c>
@@ -53140,7 +53143,7 @@
       <c r="U706" s="11"/>
       <c r="V706" s="10"/>
     </row>
-    <row r="707" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:22" ns3:dyDescent="0.2">
       <c r="A707" s="61">
         <v>706</v>
       </c>
@@ -53198,7 +53201,7 @@
       <c r="U707" s="11"/>
       <c r="V707" s="10"/>
     </row>
-    <row r="708" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A708" s="61">
         <v>707</v>
       </c>
@@ -53258,7 +53261,7 @@
       <c r="U708" s="11"/>
       <c r="V708" s="10"/>
     </row>
-    <row r="709" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A709" s="61">
         <v>708</v>
       </c>
@@ -53320,7 +53323,7 @@
       <c r="U709" s="11"/>
       <c r="V709" s="10"/>
     </row>
-    <row r="710" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A710" s="61">
         <v>709</v>
       </c>
@@ -53382,7 +53385,7 @@
       <c r="U710" s="11"/>
       <c r="V710" s="10"/>
     </row>
-    <row r="711" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:22" ns3:dyDescent="0.2">
       <c r="A711" s="61">
         <v>710</v>
       </c>
@@ -53446,7 +53449,7 @@
       <c r="U711" s="11"/>
       <c r="V711" s="10"/>
     </row>
-    <row r="712" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:22" ns3:dyDescent="0.2">
       <c r="A712" s="61">
         <v>711</v>
       </c>
@@ -53510,7 +53513,7 @@
       <c r="U712" s="11"/>
       <c r="V712" s="10"/>
     </row>
-    <row r="713" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A713" s="58">
         <v>712</v>
       </c>
@@ -53570,7 +53573,7 @@
       <c r="U713" s="11"/>
       <c r="V713" s="10"/>
     </row>
-    <row r="714" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A714" s="58">
         <v>713</v>
       </c>
@@ -53630,7 +53633,7 @@
       <c r="U714" s="11"/>
       <c r="V714" s="10"/>
     </row>
-    <row r="715" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:22" ns3:dyDescent="0.2">
       <c r="A715" s="61">
         <v>714</v>
       </c>
@@ -53692,7 +53695,7 @@
       <c r="U715" s="11"/>
       <c r="V715" s="10"/>
     </row>
-    <row r="716" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:22" ns3:dyDescent="0.2">
       <c r="A716" s="61">
         <v>715</v>
       </c>
@@ -53754,7 +53757,7 @@
       <c r="U716" s="11"/>
       <c r="V716" s="10"/>
     </row>
-    <row r="717" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:22" ns3:dyDescent="0.2">
       <c r="A717" s="58">
         <v>716</v>
       </c>
@@ -53808,7 +53811,7 @@
       <c r="U717" s="11"/>
       <c r="V717" s="10"/>
     </row>
-    <row r="718" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:22" ns3:dyDescent="0.2">
       <c r="A718" s="58">
         <v>717</v>
       </c>
@@ -53864,7 +53867,7 @@
       <c r="U718" s="11"/>
       <c r="V718" s="10"/>
     </row>
-    <row r="719" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A719" s="61">
         <v>718</v>
       </c>
@@ -53922,7 +53925,7 @@
       <c r="U719" s="11"/>
       <c r="V719" s="10"/>
     </row>
-    <row r="720" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:22" ns3:dyDescent="0.2">
       <c r="A720" s="61">
         <v>719</v>
       </c>
@@ -53978,7 +53981,7 @@
       <c r="U720" s="11"/>
       <c r="V720" s="10"/>
     </row>
-    <row r="721" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:22" ns3:dyDescent="0.2">
       <c r="A721" s="61">
         <v>720</v>
       </c>
@@ -54036,7 +54039,7 @@
       <c r="U721" s="11"/>
       <c r="V721" s="10"/>
     </row>
-    <row r="722" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:22" ns3:dyDescent="0.2">
       <c r="A722" s="61">
         <v>721</v>
       </c>
@@ -54092,7 +54095,7 @@
       <c r="U722" s="11"/>
       <c r="V722" s="10"/>
     </row>
-    <row r="723" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:22" ns3:dyDescent="0.2">
       <c r="A723" s="61">
         <v>722</v>
       </c>
@@ -54150,7 +54153,7 @@
       <c r="U723" s="11"/>
       <c r="V723" s="10"/>
     </row>
-    <row r="724" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:22" ns3:dyDescent="0.2">
       <c r="A724" s="61">
         <v>723</v>
       </c>
@@ -54208,7 +54211,7 @@
       <c r="U724" s="11"/>
       <c r="V724" s="10"/>
     </row>
-    <row r="725" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:22" ns3:dyDescent="0.2">
       <c r="A725" s="61">
         <v>724</v>
       </c>
@@ -54266,7 +54269,7 @@
       <c r="U725" s="11"/>
       <c r="V725" s="10"/>
     </row>
-    <row r="726" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:22" ns3:dyDescent="0.2">
       <c r="A726" s="61">
         <v>725</v>
       </c>
@@ -54322,7 +54325,7 @@
       <c r="U726" s="11"/>
       <c r="V726" s="10"/>
     </row>
-    <row r="727" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:22" ns3:dyDescent="0.2">
       <c r="A727" s="61">
         <v>726</v>
       </c>
@@ -54378,7 +54381,7 @@
       <c r="U727" s="11"/>
       <c r="V727" s="10"/>
     </row>
-    <row r="728" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:22" ns3:dyDescent="0.2">
       <c r="A728" s="61">
         <v>727</v>
       </c>
@@ -54436,7 +54439,7 @@
       <c r="U728" s="11"/>
       <c r="V728" s="10"/>
     </row>
-    <row r="729" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:22" ns3:dyDescent="0.2">
       <c r="A729" s="61">
         <v>728</v>
       </c>
@@ -54492,7 +54495,7 @@
       <c r="U729" s="11"/>
       <c r="V729" s="10"/>
     </row>
-    <row r="730" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:22" ns3:dyDescent="0.2">
       <c r="A730" s="61">
         <v>729</v>
       </c>
@@ -54548,7 +54551,7 @@
       <c r="U730" s="11"/>
       <c r="V730" s="10"/>
     </row>
-    <row r="731" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:22" ns3:dyDescent="0.2">
       <c r="A731" s="61">
         <v>730</v>
       </c>
@@ -54606,7 +54609,7 @@
       <c r="U731" s="11"/>
       <c r="V731" s="10"/>
     </row>
-    <row r="732" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:22" ns3:dyDescent="0.2">
       <c r="A732" s="61">
         <v>731</v>
       </c>
@@ -54666,7 +54669,7 @@
       <c r="U732" s="11"/>
       <c r="V732" s="10"/>
     </row>
-    <row r="733" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:22" ns3:dyDescent="0.2">
       <c r="A733" s="61">
         <v>732</v>
       </c>
@@ -54726,7 +54729,7 @@
       <c r="U733" s="11"/>
       <c r="V733" s="10"/>
     </row>
-    <row r="734" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:22" ns3:dyDescent="0.2">
       <c r="A734" s="61">
         <v>733</v>
       </c>
@@ -54786,7 +54789,7 @@
       <c r="U734" s="11"/>
       <c r="V734" s="10"/>
     </row>
-    <row r="735" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:22" ns3:dyDescent="0.2">
       <c r="A735" s="61">
         <v>734</v>
       </c>
@@ -54844,7 +54847,7 @@
       <c r="U735" s="11"/>
       <c r="V735" s="10"/>
     </row>
-    <row r="736" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:22" ns3:dyDescent="0.2">
       <c r="A736" s="61">
         <v>735</v>
       </c>
@@ -54902,7 +54905,7 @@
       <c r="U736" s="11"/>
       <c r="V736" s="10"/>
     </row>
-    <row r="737" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:22" ns3:dyDescent="0.2">
       <c r="A737" s="61">
         <v>736</v>
       </c>
@@ -54956,7 +54959,7 @@
       <c r="U737" s="11"/>
       <c r="V737" s="10"/>
     </row>
-    <row r="738" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:22" ns3:dyDescent="0.2">
       <c r="A738" s="61">
         <v>737</v>
       </c>
@@ -55012,7 +55015,7 @@
       <c r="U738" s="11"/>
       <c r="V738" s="10"/>
     </row>
-    <row r="739" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:22" ns3:dyDescent="0.2">
       <c r="A739" s="61">
         <v>738</v>
       </c>
@@ -55068,7 +55071,7 @@
       <c r="U739" s="11"/>
       <c r="V739" s="10"/>
     </row>
-    <row r="740" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:22" ns3:dyDescent="0.2">
       <c r="A740" s="61">
         <v>739</v>
       </c>
@@ -55126,7 +55129,7 @@
       <c r="U740" s="11"/>
       <c r="V740" s="10"/>
     </row>
-    <row r="741" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:22" ns3:dyDescent="0.2">
       <c r="A741" s="61">
         <v>740</v>
       </c>
@@ -55186,7 +55189,7 @@
       <c r="U741" s="11"/>
       <c r="V741" s="10"/>
     </row>
-    <row r="742" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:22" ns3:dyDescent="0.2">
       <c r="A742" s="61">
         <v>741</v>
       </c>
@@ -55244,7 +55247,7 @@
       <c r="U742" s="11"/>
       <c r="V742" s="10"/>
     </row>
-    <row r="743" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:22" ns3:dyDescent="0.2">
       <c r="A743" s="61">
         <v>742</v>
       </c>
@@ -55304,7 +55307,7 @@
       <c r="U743" s="11"/>
       <c r="V743" s="10"/>
     </row>
-    <row r="744" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:22" ns3:dyDescent="0.2">
       <c r="A744" s="61">
         <v>743</v>
       </c>
@@ -55364,7 +55367,7 @@
       <c r="U744" s="11"/>
       <c r="V744" s="10"/>
     </row>
-    <row r="745" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:22" ns3:dyDescent="0.2">
       <c r="A745" s="61">
         <v>744</v>
       </c>
@@ -55422,7 +55425,7 @@
       <c r="U745" s="11"/>
       <c r="V745" s="10"/>
     </row>
-    <row r="746" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:22" ns3:dyDescent="0.2">
       <c r="A746" s="61">
         <v>745</v>
       </c>
@@ -55482,7 +55485,7 @@
       <c r="U746" s="11"/>
       <c r="V746" s="10"/>
     </row>
-    <row r="747" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:22" ns3:dyDescent="0.2">
       <c r="A747" s="61">
         <v>746</v>
       </c>
@@ -55538,7 +55541,7 @@
       <c r="U747" s="11"/>
       <c r="V747" s="10"/>
     </row>
-    <row r="748" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A748" s="61">
         <v>747</v>
       </c>
@@ -55598,7 +55601,7 @@
       <c r="U748" s="11"/>
       <c r="V748" s="10"/>
     </row>
-    <row r="749" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A749" s="61">
         <v>748</v>
       </c>
@@ -55658,7 +55661,7 @@
       <c r="U749" s="11"/>
       <c r="V749" s="10"/>
     </row>
-    <row r="750" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A750" s="61">
         <v>749</v>
       </c>
@@ -55716,7 +55719,7 @@
       <c r="U750" s="11"/>
       <c r="V750" s="10"/>
     </row>
-    <row r="751" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A751" s="61">
         <v>750</v>
       </c>
@@ -55774,7 +55777,7 @@
       <c r="U751" s="11"/>
       <c r="V751" s="10"/>
     </row>
-    <row r="752" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A752" s="61">
         <v>751</v>
       </c>
@@ -55832,7 +55835,7 @@
       <c r="U752" s="11"/>
       <c r="V752" s="10"/>
     </row>
-    <row r="753" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A753" s="61">
         <v>752</v>
       </c>
@@ -55890,7 +55893,7 @@
       <c r="U753" s="11"/>
       <c r="V753" s="10"/>
     </row>
-    <row r="754" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:22" ns3:dyDescent="0.2">
       <c r="A754" s="61">
         <v>753</v>
       </c>
@@ -55946,7 +55949,7 @@
       <c r="U754" s="11"/>
       <c r="V754" s="10"/>
     </row>
-    <row r="755" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:22" ns3:dyDescent="0.2">
       <c r="A755" s="61">
         <v>754</v>
       </c>
@@ -56002,7 +56005,7 @@
       <c r="U755" s="11"/>
       <c r="V755" s="10"/>
     </row>
-    <row r="756" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:22" ns3:dyDescent="0.2">
       <c r="A756" s="61">
         <v>755</v>
       </c>
@@ -56062,7 +56065,7 @@
       <c r="U756" s="11"/>
       <c r="V756" s="10"/>
     </row>
-    <row r="757" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:22" ns3:dyDescent="0.2">
       <c r="A757" s="61">
         <v>756</v>
       </c>
@@ -56122,7 +56125,7 @@
       <c r="U757" s="11"/>
       <c r="V757" s="10"/>
     </row>
-    <row r="758" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:22" ns3:dyDescent="0.2">
       <c r="A758" s="61">
         <v>757</v>
       </c>
@@ -56180,7 +56183,7 @@
       <c r="U758" s="11"/>
       <c r="V758" s="10"/>
     </row>
-    <row r="759" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:22" ns3:dyDescent="0.2">
       <c r="A759" s="61">
         <v>758</v>
       </c>
@@ -56238,7 +56241,7 @@
       <c r="U759" s="11"/>
       <c r="V759" s="10"/>
     </row>
-    <row r="760" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A760" s="61">
         <v>759</v>
       </c>
@@ -56298,7 +56301,7 @@
       <c r="U760" s="11"/>
       <c r="V760" s="10"/>
     </row>
-    <row r="761" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A761" s="61">
         <v>760</v>
       </c>
@@ -56358,7 +56361,7 @@
       <c r="U761" s="11"/>
       <c r="V761" s="10"/>
     </row>
-    <row r="762" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:22" ns3:dyDescent="0.2">
       <c r="A762" s="61">
         <v>761</v>
       </c>
@@ -56416,7 +56419,7 @@
       <c r="U762" s="11"/>
       <c r="V762" s="10"/>
     </row>
-    <row r="763" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:22" ns3:dyDescent="0.2">
       <c r="A763" s="61">
         <v>762</v>
       </c>
@@ -56474,7 +56477,7 @@
       <c r="U763" s="11"/>
       <c r="V763" s="10"/>
     </row>
-    <row r="764" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:22" ns3:dyDescent="0.2">
       <c r="A764" s="61">
         <v>763</v>
       </c>
@@ -56532,7 +56535,7 @@
       <c r="U764" s="11"/>
       <c r="V764" s="10"/>
     </row>
-    <row r="765" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:22" ns3:dyDescent="0.2">
       <c r="A765" s="61">
         <v>764</v>
       </c>
@@ -56590,7 +56593,7 @@
       <c r="U765" s="11"/>
       <c r="V765" s="10"/>
     </row>
-    <row r="766" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:22" ns3:dyDescent="0.2">
       <c r="A766" s="61">
         <v>765</v>
       </c>
@@ -56650,7 +56653,7 @@
       <c r="U766" s="11"/>
       <c r="V766" s="10"/>
     </row>
-    <row r="767" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:22" ns3:dyDescent="0.2">
       <c r="A767" s="61">
         <v>766</v>
       </c>
@@ -56706,7 +56709,7 @@
       <c r="U767" s="11"/>
       <c r="V767" s="10"/>
     </row>
-    <row r="768" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:22" ns3:dyDescent="0.2">
       <c r="A768" s="61">
         <v>767</v>
       </c>
@@ -56762,7 +56765,7 @@
       <c r="U768" s="11"/>
       <c r="V768" s="10"/>
     </row>
-    <row r="769" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:22" ns3:dyDescent="0.2">
       <c r="A769" s="61">
         <v>768</v>
       </c>
@@ -56818,7 +56821,7 @@
       <c r="U769" s="11"/>
       <c r="V769" s="10"/>
     </row>
-    <row r="770" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:22" ns3:dyDescent="0.2">
       <c r="A770" s="61">
         <v>769</v>
       </c>
@@ -56876,7 +56879,7 @@
       <c r="U770" s="11"/>
       <c r="V770" s="10"/>
     </row>
-    <row r="771" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:22" ns3:dyDescent="0.2">
       <c r="A771" s="61">
         <v>770</v>
       </c>
@@ -56934,7 +56937,7 @@
       <c r="U771" s="11"/>
       <c r="V771" s="10"/>
     </row>
-    <row r="772" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:22" ns3:dyDescent="0.2">
       <c r="A772" s="61">
         <v>771</v>
       </c>
@@ -56990,7 +56993,7 @@
       <c r="U772" s="11"/>
       <c r="V772" s="10"/>
     </row>
-    <row r="773" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:22" ns3:dyDescent="0.2">
       <c r="A773" s="61">
         <v>772</v>
       </c>
@@ -57044,7 +57047,7 @@
       <c r="U773" s="11"/>
       <c r="V773" s="10"/>
     </row>
-    <row r="774" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:22" ns3:dyDescent="0.2">
       <c r="A774" s="61">
         <v>773</v>
       </c>
@@ -57098,7 +57101,7 @@
       <c r="U774" s="11"/>
       <c r="V774" s="10"/>
     </row>
-    <row r="775" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A775" s="61">
         <v>774</v>
       </c>
@@ -57156,7 +57159,7 @@
       <c r="U775" s="11"/>
       <c r="V775" s="10"/>
     </row>
-    <row r="776" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A776" s="61">
         <v>775</v>
       </c>
@@ -57210,7 +57213,7 @@
       <c r="U776" s="11"/>
       <c r="V776" s="10"/>
     </row>
-    <row r="777" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:22" ns3:dyDescent="0.2">
       <c r="A777" s="61">
         <v>776</v>
       </c>
@@ -57266,7 +57269,7 @@
       <c r="U777" s="11"/>
       <c r="V777" s="10"/>
     </row>
-    <row r="778" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:22" ns3:dyDescent="0.2">
       <c r="A778" s="61">
         <v>777</v>
       </c>
@@ -57326,7 +57329,7 @@
       <c r="U778" s="11"/>
       <c r="V778" s="10"/>
     </row>
-    <row r="779" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A779" s="61">
         <v>778</v>
       </c>
@@ -57382,7 +57385,7 @@
       <c r="U779" s="11"/>
       <c r="V779" s="10"/>
     </row>
-    <row r="780" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:22" ns3:dyDescent="0.2">
       <c r="A780" s="61">
         <v>779</v>
       </c>
@@ -57442,7 +57445,7 @@
       <c r="U780" s="11"/>
       <c r="V780" s="10"/>
     </row>
-    <row r="781" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A781" s="61">
         <v>780</v>
       </c>
@@ -57502,7 +57505,7 @@
       <c r="U781" s="11"/>
       <c r="V781" s="10"/>
     </row>
-    <row r="782" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A782" s="61">
         <v>781</v>
       </c>
@@ -57560,7 +57563,7 @@
       <c r="U782" s="11"/>
       <c r="V782" s="10"/>
     </row>
-    <row r="783" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:22" ns3:dyDescent="0.2">
       <c r="A783" s="61">
         <v>782</v>
       </c>
@@ -57617,7 +57620,7 @@
       <c r="U783" s="11"/>
       <c r="V783" s="10"/>
     </row>
-    <row r="784" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A784" s="61">
         <v>783</v>
       </c>
@@ -57679,7 +57682,7 @@
       <c r="U784" s="11"/>
       <c r="V784" s="10"/>
     </row>
-    <row r="785" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A785" s="61">
         <v>784</v>
       </c>
@@ -57741,7 +57744,7 @@
       <c r="U785" s="11"/>
       <c r="V785" s="10"/>
     </row>
-    <row r="786" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A786" s="61">
         <v>785</v>
       </c>
@@ -57801,7 +57804,7 @@
       <c r="U786" s="11"/>
       <c r="V786" s="10"/>
     </row>
-    <row r="787" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A787" s="61">
         <v>786</v>
       </c>
@@ -57861,7 +57864,7 @@
       <c r="U787" s="11"/>
       <c r="V787" s="10"/>
     </row>
-    <row r="788" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A788" s="61">
         <v>787</v>
       </c>
@@ -57921,7 +57924,7 @@
       <c r="U788" s="11"/>
       <c r="V788" s="10"/>
     </row>
-    <row r="789" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:22" ns3:dyDescent="0.2">
       <c r="A789" s="61">
         <v>788</v>
       </c>
@@ -57979,7 +57982,7 @@
       <c r="U789" s="11"/>
       <c r="V789" s="10"/>
     </row>
-    <row r="790" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:22" ns3:dyDescent="0.2">
       <c r="A790" s="61">
         <v>789</v>
       </c>
@@ -58033,7 +58036,7 @@
       <c r="U790" s="11"/>
       <c r="V790" s="10"/>
     </row>
-    <row r="791" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:22" ns3:dyDescent="0.2">
       <c r="A791" s="61">
         <v>790</v>
       </c>
@@ -58087,7 +58090,7 @@
       <c r="U791" s="11"/>
       <c r="V791" s="10"/>
     </row>
-    <row r="792" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:22" ns3:dyDescent="0.2">
       <c r="A792" s="61">
         <v>791</v>
       </c>
@@ -58143,7 +58146,7 @@
       <c r="U792" s="11"/>
       <c r="V792" s="10"/>
     </row>
-    <row r="793" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A793" s="61">
         <v>792</v>
       </c>
@@ -58199,7 +58202,7 @@
       <c r="U793" s="11"/>
       <c r="V793" s="10"/>
     </row>
-    <row r="794" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:22" ns3:dyDescent="0.2">
       <c r="A794" s="61">
         <v>793</v>
       </c>
@@ -58255,7 +58258,7 @@
       <c r="U794" s="11"/>
       <c r="V794" s="10"/>
     </row>
-    <row r="795" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A795" s="61">
         <v>794</v>
       </c>
@@ -58311,7 +58314,7 @@
       <c r="U795" s="11"/>
       <c r="V795" s="10"/>
     </row>
-    <row r="796" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A796" s="61">
         <v>795</v>
       </c>
@@ -58367,7 +58370,7 @@
       <c r="U796" s="11"/>
       <c r="V796" s="10"/>
     </row>
-    <row r="797" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:22" ns3:dyDescent="0.2">
       <c r="A797" s="61">
         <v>796</v>
       </c>
@@ -58421,7 +58424,7 @@
       <c r="U797" s="11"/>
       <c r="V797" s="10"/>
     </row>
-    <row r="798" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A798" s="61">
         <v>797</v>
       </c>
@@ -58477,7 +58480,7 @@
       <c r="U798" s="11"/>
       <c r="V798" s="10"/>
     </row>
-    <row r="799" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A799" s="61">
         <v>798</v>
       </c>
@@ -58533,7 +58536,7 @@
       <c r="U799" s="11"/>
       <c r="V799" s="10"/>
     </row>
-    <row r="800" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:22" ns3:dyDescent="0.2">
       <c r="A800" s="61">
         <v>799</v>
       </c>
@@ -58589,7 +58592,7 @@
       <c r="U800" s="11"/>
       <c r="V800" s="10"/>
     </row>
-    <row r="801" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:22" ns3:dyDescent="0.2">
       <c r="A801" s="61">
         <v>800</v>
       </c>
@@ -58641,7 +58644,7 @@
       <c r="U801" s="11"/>
       <c r="V801" s="10"/>
     </row>
-    <row r="802" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:22" ns3:dyDescent="0.2">
       <c r="A802" s="61">
         <v>801</v>
       </c>
@@ -58697,7 +58700,7 @@
       <c r="U802" s="11"/>
       <c r="V802" s="10"/>
     </row>
-    <row r="803" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:22" ns3:dyDescent="0.2">
       <c r="A803" s="61">
         <v>802</v>
       </c>
@@ -58751,7 +58754,7 @@
       <c r="U803" s="11"/>
       <c r="V803" s="10"/>
     </row>
-    <row r="804" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:22" ns3:dyDescent="0.2">
       <c r="A804" s="61">
         <v>803</v>
       </c>
@@ -58805,7 +58808,7 @@
       <c r="U804" s="11"/>
       <c r="V804" s="10"/>
     </row>
-    <row r="805" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A805" s="61">
         <v>804</v>
       </c>
@@ -58861,7 +58864,7 @@
       <c r="U805" s="11"/>
       <c r="V805" s="10"/>
     </row>
-    <row r="806" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A806" s="61">
         <v>805</v>
       </c>
@@ -58917,7 +58920,7 @@
       <c r="U806" s="11"/>
       <c r="V806" s="10"/>
     </row>
-    <row r="807" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A807" s="61">
         <v>806</v>
       </c>
@@ -58973,7 +58976,7 @@
       <c r="U807" s="11"/>
       <c r="V807" s="10"/>
     </row>
-    <row r="808" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A808" s="61">
         <v>807</v>
       </c>
@@ -59027,7 +59030,7 @@
       <c r="U808" s="11"/>
       <c r="V808" s="10"/>
     </row>
-    <row r="809" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A809" s="61">
         <v>808</v>
       </c>
@@ -59081,7 +59084,7 @@
       <c r="U809" s="11"/>
       <c r="V809" s="10"/>
     </row>
-    <row r="810" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A810" s="61">
         <v>809</v>
       </c>
@@ -59135,7 +59138,7 @@
       <c r="U810" s="11"/>
       <c r="V810" s="10"/>
     </row>
-    <row r="811" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:22" ns3:dyDescent="0.2">
       <c r="A811" s="61">
         <v>810</v>
       </c>
@@ -59191,7 +59194,7 @@
       <c r="U811" s="11"/>
       <c r="V811" s="10"/>
     </row>
-    <row r="812" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:22" ns3:dyDescent="0.2">
       <c r="A812" s="61">
         <v>811</v>
       </c>
@@ -59247,7 +59250,7 @@
       <c r="U812" s="11"/>
       <c r="V812" s="10"/>
     </row>
-    <row r="813" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:22" ns3:dyDescent="0.2">
       <c r="A813" s="61">
         <v>812</v>
       </c>
@@ -59303,7 +59306,7 @@
       <c r="U813" s="11"/>
       <c r="V813" s="10"/>
     </row>
-    <row r="814" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:22" ns3:dyDescent="0.2">
       <c r="A814" s="61">
         <v>813</v>
       </c>
@@ -59359,7 +59362,7 @@
       <c r="U814" s="11"/>
       <c r="V814" s="10"/>
     </row>
-    <row r="815" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:22" ns3:dyDescent="0.2">
       <c r="A815" s="61">
         <v>814</v>
       </c>
@@ -59415,7 +59418,7 @@
       <c r="U815" s="11"/>
       <c r="V815" s="10"/>
     </row>
-    <row r="816" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:22" ns3:dyDescent="0.2">
       <c r="A816" s="61">
         <v>815</v>
       </c>
@@ -59471,7 +59474,7 @@
       <c r="U816" s="11"/>
       <c r="V816" s="10"/>
     </row>
-    <row r="817" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:22" ns3:dyDescent="0.2">
       <c r="A817" s="61">
         <v>816</v>
       </c>
@@ -59527,7 +59530,7 @@
       <c r="U817" s="11"/>
       <c r="V817" s="10"/>
     </row>
-    <row r="818" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:22" ns3:dyDescent="0.2">
       <c r="A818" s="61">
         <v>817</v>
       </c>
@@ -59583,7 +59586,7 @@
       <c r="U818" s="11"/>
       <c r="V818" s="10"/>
     </row>
-    <row r="819" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:22" ns3:dyDescent="0.2">
       <c r="A819" s="61">
         <v>818</v>
       </c>
@@ -59639,7 +59642,7 @@
       <c r="U819" s="11"/>
       <c r="V819" s="10"/>
     </row>
-    <row r="820" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:22" ns3:dyDescent="0.2">
       <c r="A820" s="61">
         <v>819</v>
       </c>
@@ -59695,7 +59698,7 @@
       <c r="U820" s="11"/>
       <c r="V820" s="10"/>
     </row>
-    <row r="821" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:22" ns3:dyDescent="0.2">
       <c r="A821" s="61">
         <v>820</v>
       </c>
@@ -59751,7 +59754,7 @@
       <c r="U821" s="11"/>
       <c r="V821" s="10"/>
     </row>
-    <row r="822" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:22" ns3:dyDescent="0.2">
       <c r="A822" s="61">
         <v>821</v>
       </c>
@@ -59809,7 +59812,7 @@
       <c r="U822" s="11"/>
       <c r="V822" s="10"/>
     </row>
-    <row r="823" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:22" ns3:dyDescent="0.2">
       <c r="A823" s="61">
         <v>822</v>
       </c>
@@ -59867,7 +59870,7 @@
       <c r="U823" s="11"/>
       <c r="V823" s="10"/>
     </row>
-    <row r="824" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:22" ns3:dyDescent="0.2">
       <c r="A824" s="61">
         <v>823</v>
       </c>
@@ -59927,7 +59930,7 @@
       <c r="U824" s="11"/>
       <c r="V824" s="10"/>
     </row>
-    <row r="825" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:22" ns3:dyDescent="0.2">
       <c r="A825" s="61">
         <v>824</v>
       </c>
@@ -59985,7 +59988,7 @@
       <c r="U825" s="11"/>
       <c r="V825" s="10"/>
     </row>
-    <row r="826" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:22" ns3:dyDescent="0.2">
       <c r="A826" s="61">
         <v>825</v>
       </c>
@@ -60045,7 +60048,7 @@
       <c r="U826" s="11"/>
       <c r="V826" s="10"/>
     </row>
-    <row r="827" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:22" ns3:dyDescent="0.2">
       <c r="A827" s="61">
         <v>826</v>
       </c>
@@ -60105,7 +60108,7 @@
       <c r="U827" s="11"/>
       <c r="V827" s="10"/>
     </row>
-    <row r="828" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A828" s="61">
         <v>827</v>
       </c>
@@ -60163,7 +60166,7 @@
       <c r="U828" s="11"/>
       <c r="V828" s="10"/>
     </row>
-    <row r="829" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A829" s="61">
         <v>828</v>
       </c>
@@ -60223,7 +60226,7 @@
       <c r="U829" s="11"/>
       <c r="V829" s="10"/>
     </row>
-    <row r="830" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:22" ns3:dyDescent="0.2">
       <c r="A830" s="61">
         <v>829</v>
       </c>
@@ -60280,7 +60283,7 @@
       <c r="U830" s="11"/>
       <c r="V830" s="10"/>
     </row>
-    <row r="831" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A831" s="61">
         <v>830</v>
       </c>
@@ -60340,7 +60343,7 @@
       <c r="U831" s="11"/>
       <c r="V831" s="10"/>
     </row>
-    <row r="832" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A832" s="61">
         <v>831</v>
       </c>
@@ -60400,7 +60403,7 @@
       <c r="U832" s="11"/>
       <c r="V832" s="10"/>
     </row>
-    <row r="833" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A833" s="61">
         <v>832</v>
       </c>
@@ -60460,7 +60463,7 @@
       <c r="U833" s="11"/>
       <c r="V833" s="10"/>
     </row>
-    <row r="834" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A834" s="61">
         <v>833</v>
       </c>
@@ -60520,7 +60523,7 @@
       <c r="U834" s="11"/>
       <c r="V834" s="10"/>
     </row>
-    <row r="835" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A835" s="61">
         <v>834</v>
       </c>
@@ -60582,7 +60585,7 @@
       <c r="U835" s="11"/>
       <c r="V835" s="10"/>
     </row>
-    <row r="836" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A836" s="61">
         <v>835</v>
       </c>
@@ -60640,7 +60643,7 @@
       <c r="U836" s="11"/>
       <c r="V836" s="10"/>
     </row>
-    <row r="837" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A837" s="61">
         <v>836</v>
       </c>
@@ -60698,7 +60701,7 @@
       <c r="U837" s="11"/>
       <c r="V837" s="10"/>
     </row>
-    <row r="838" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A838" s="61">
         <v>837</v>
       </c>
@@ -60758,7 +60761,7 @@
       <c r="U838" s="11"/>
       <c r="V838" s="10"/>
     </row>
-    <row r="839" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A839" s="61">
         <v>838</v>
       </c>
@@ -60820,7 +60823,7 @@
       <c r="U839" s="11"/>
       <c r="V839" s="10"/>
     </row>
-    <row r="840" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A840" s="61">
         <v>839</v>
       </c>
@@ -60882,7 +60885,7 @@
       <c r="U840" s="11"/>
       <c r="V840" s="10"/>
     </row>
-    <row r="841" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A841" s="61">
         <v>840</v>
       </c>
@@ -60944,7 +60947,7 @@
       <c r="U841" s="11"/>
       <c r="V841" s="10"/>
     </row>
-    <row r="842" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:22" ns3:dyDescent="0.2">
       <c r="A842" s="61">
         <v>841</v>
       </c>
@@ -61004,7 +61007,7 @@
       <c r="U842" s="11"/>
       <c r="V842" s="10"/>
     </row>
-    <row r="843" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:22" ns3:dyDescent="0.2">
       <c r="A843" s="61">
         <v>842</v>
       </c>
@@ -61064,7 +61067,7 @@
       <c r="U843" s="11"/>
       <c r="V843" s="10"/>
     </row>
-    <row r="844" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:22" ns3:dyDescent="0.2">
       <c r="A844" s="61">
         <v>843</v>
       </c>
@@ -61122,7 +61125,7 @@
       <c r="U844" s="11"/>
       <c r="V844" s="10"/>
     </row>
-    <row r="845" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:22" ns3:dyDescent="0.2">
       <c r="A845" s="61">
         <v>844</v>
       </c>
@@ -61180,7 +61183,7 @@
       <c r="U845" s="11"/>
       <c r="V845" s="10"/>
     </row>
-    <row r="846" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:22" ns3:dyDescent="0.2">
       <c r="A846" s="61">
         <v>845</v>
       </c>
@@ -61236,7 +61239,7 @@
       <c r="U846" s="11"/>
       <c r="V846" s="10"/>
     </row>
-    <row r="847" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:22" ns3:dyDescent="0.2">
       <c r="A847" s="61">
         <v>846</v>
       </c>
@@ -61292,7 +61295,7 @@
       <c r="U847" s="11"/>
       <c r="V847" s="10"/>
     </row>
-    <row r="848" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:22" ns3:dyDescent="0.2">
       <c r="A848" s="61">
         <v>847</v>
       </c>
@@ -61348,7 +61351,7 @@
       <c r="U848" s="11"/>
       <c r="V848" s="10"/>
     </row>
-    <row r="849" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:22" ns3:dyDescent="0.2">
       <c r="A849" s="61">
         <v>848</v>
       </c>
@@ -61408,7 +61411,7 @@
       <c r="U849" s="11"/>
       <c r="V849" s="10"/>
     </row>
-    <row r="850" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:22" ns3:dyDescent="0.2">
       <c r="A850" s="61">
         <v>849</v>
       </c>
@@ -61470,7 +61473,7 @@
       <c r="U850" s="11"/>
       <c r="V850" s="10"/>
     </row>
-    <row r="851" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:22" ns3:dyDescent="0.2">
       <c r="A851" s="61">
         <v>850</v>
       </c>
@@ -61530,7 +61533,7 @@
       <c r="U851" s="11"/>
       <c r="V851" s="10"/>
     </row>
-    <row r="852" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:22" ns3:dyDescent="0.2">
       <c r="A852" s="61">
         <v>851</v>
       </c>
@@ -61590,7 +61593,7 @@
       <c r="U852" s="11"/>
       <c r="V852" s="10"/>
     </row>
-    <row r="853" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A853" s="61">
         <v>852</v>
       </c>
@@ -61646,7 +61649,7 @@
       <c r="U853" s="11"/>
       <c r="V853" s="10"/>
     </row>
-    <row r="854" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A854" s="61">
         <v>853</v>
       </c>
@@ -61704,7 +61707,7 @@
       <c r="U854" s="11"/>
       <c r="V854" s="10"/>
     </row>
-    <row r="855" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A855" s="61">
         <v>854</v>
       </c>
@@ -61759,7 +61762,7 @@
       <c r="U855" s="11"/>
       <c r="V855" s="10"/>
     </row>
-    <row r="856" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A856" s="61">
         <v>855</v>
       </c>
@@ -61819,7 +61822,7 @@
       </c>
       <c r="V856" s="10"/>
     </row>
-    <row r="857" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A857" s="61">
         <v>856</v>
       </c>
@@ -61878,7 +61881,7 @@
       </c>
       <c r="V857" s="10"/>
     </row>
-    <row r="858" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A858" s="61">
         <v>857</v>
       </c>
@@ -61940,7 +61943,7 @@
       </c>
       <c r="V858" s="10"/>
     </row>
-    <row r="859" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A859" s="61">
         <v>858</v>
       </c>
@@ -62004,7 +62007,7 @@
       </c>
       <c r="V859" s="10"/>
     </row>
-    <row r="860" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A860" s="61">
         <v>859</v>
       </c>
@@ -62068,7 +62071,7 @@
       </c>
       <c r="V860" s="10"/>
     </row>
-    <row r="861" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A861" s="61">
         <v>860</v>
       </c>
@@ -62132,7 +62135,7 @@
       </c>
       <c r="V861" s="10"/>
     </row>
-    <row r="862" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A862" s="61">
         <v>861</v>
       </c>
@@ -62196,7 +62199,7 @@
       </c>
       <c r="V862" s="10"/>
     </row>
-    <row r="863" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A863" s="58">
         <v>862</v>
       </c>
@@ -62260,7 +62263,7 @@
       </c>
       <c r="V863" s="10"/>
     </row>
-    <row r="864" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A864" s="61">
         <v>863</v>
       </c>
@@ -62322,7 +62325,7 @@
       </c>
       <c r="V864" s="10"/>
     </row>
-    <row r="865" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A865" s="61">
         <v>864</v>
       </c>
@@ -62382,7 +62385,7 @@
       </c>
       <c r="V865" s="10"/>
     </row>
-    <row r="866" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A866" s="61">
         <v>865</v>
       </c>
@@ -62440,7 +62443,7 @@
       </c>
       <c r="V866" s="10"/>
     </row>
-    <row r="867" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A867" s="61">
         <v>866</v>
       </c>
@@ -62502,7 +62505,7 @@
       </c>
       <c r="V867" s="10"/>
     </row>
-    <row r="868" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A868" s="61">
         <v>867</v>
       </c>
@@ -62558,7 +62561,7 @@
       <c r="U868" s="11"/>
       <c r="V868" s="10"/>
     </row>
-    <row r="869" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A869" s="61">
         <v>868</v>
       </c>
@@ -62614,7 +62617,7 @@
       <c r="U869" s="11"/>
       <c r="V869" s="10"/>
     </row>
-    <row r="870" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A870" s="61">
         <v>869</v>
       </c>
@@ -62670,7 +62673,7 @@
       <c r="U870" s="11"/>
       <c r="V870" s="10"/>
     </row>
-    <row r="871" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A871" s="61">
         <v>870</v>
       </c>
@@ -62728,7 +62731,7 @@
       <c r="U871" s="11"/>
       <c r="V871" s="10"/>
     </row>
-    <row r="872" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A872" s="61">
         <v>871</v>
       </c>
@@ -62783,7 +62786,7 @@
       <c r="U872" s="11"/>
       <c r="V872" s="10"/>
     </row>
-    <row r="873" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A873" s="61">
         <v>872</v>
       </c>
@@ -62843,7 +62846,7 @@
       <c r="U873" s="11"/>
       <c r="V873" s="10"/>
     </row>
-    <row r="874" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A874" s="61">
         <v>873</v>
       </c>
@@ -62903,7 +62906,7 @@
       <c r="U874" s="11"/>
       <c r="V874" s="10"/>
     </row>
-    <row r="875" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A875" s="61">
         <v>874</v>
       </c>
@@ -62959,7 +62962,7 @@
       <c r="U875" s="11"/>
       <c r="V875" s="10"/>
     </row>
-    <row r="876" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A876" s="61">
         <v>875</v>
       </c>
@@ -63017,7 +63020,7 @@
       <c r="U876" s="11"/>
       <c r="V876" s="10"/>
     </row>
-    <row r="877" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A877" s="61">
         <v>876</v>
       </c>
@@ -63081,7 +63084,7 @@
       <c r="U877" s="11"/>
       <c r="V877" s="10"/>
     </row>
-    <row r="878" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A878" s="61">
         <v>877</v>
       </c>
@@ -63141,7 +63144,7 @@
       <c r="U878" s="11"/>
       <c r="V878" s="10"/>
     </row>
-    <row r="879" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A879" s="61">
         <v>878</v>
       </c>
@@ -63199,7 +63202,7 @@
       <c r="U879" s="11"/>
       <c r="V879" s="10"/>
     </row>
-    <row r="880" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A880" s="61">
         <v>879</v>
       </c>
@@ -63257,7 +63260,7 @@
       <c r="U880" s="11"/>
       <c r="V880" s="10"/>
     </row>
-    <row r="881" spans="1:24" ht="16" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:24" ht="16" ns3:dyDescent="0.25">
       <c r="A881" s="61">
         <v>880</v>
       </c>
@@ -63321,7 +63324,7 @@
       </c>
       <c r="V881" s="10"/>
     </row>
-    <row r="882" spans="1:24" ht="16" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:24" ht="16" ns3:dyDescent="0.25">
       <c r="A882" s="61">
         <v>881</v>
       </c>
@@ -63387,7 +63390,7 @@
         <v>3472</v>
       </c>
     </row>
-    <row r="883" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:24" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A883" s="61">
         <v>882</v>
       </c>
@@ -63454,7 +63457,7 @@
         <v>3477</v>
       </c>
     </row>
-    <row r="884" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:24" ns3:dyDescent="0.2">
       <c r="A884" s="61">
         <v>883</v>
       </c>
@@ -63524,7 +63527,7 @@
         <v>3482</v>
       </c>
     </row>
-    <row r="885" spans="1:24" ht="16" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:24" ht="16" ns3:dyDescent="0.25">
       <c r="A885" s="61">
         <v>884</v>
       </c>
@@ -63594,7 +63597,7 @@
         <v>3483</v>
       </c>
     </row>
-    <row r="886" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:24" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A886" s="61">
         <v>885</v>
       </c>
@@ -63662,7 +63665,7 @@
         <v>3484</v>
       </c>
     </row>
-    <row r="887" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:24" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A887" s="61">
         <v>886</v>
       </c>
@@ -63728,7 +63731,7 @@
         <v>3485</v>
       </c>
     </row>
-    <row r="888" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:24" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A888" s="61">
         <v>887</v>
       </c>
@@ -63791,7 +63794,7 @@
         <v>3486</v>
       </c>
     </row>
-    <row r="889" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:24" ns3:dyDescent="0.2">
       <c r="A889" s="61">
         <v>888</v>
       </c>
@@ -63847,7 +63850,7 @@
       <c r="U889" s="11"/>
       <c r="V889" s="10"/>
     </row>
-    <row r="890" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:24" ns3:dyDescent="0.2">
       <c r="A890" s="61">
         <v>889</v>
       </c>
@@ -63903,7 +63906,7 @@
       <c r="U890" s="11"/>
       <c r="V890" s="10"/>
     </row>
-    <row r="891" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:24" ns3:dyDescent="0.2">
       <c r="A891" s="61">
         <v>890</v>
       </c>
@@ -63957,7 +63960,7 @@
       <c r="U891" s="11"/>
       <c r="V891" s="10"/>
     </row>
-    <row r="892" spans="1:24" ht="16" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:24" ht="16" ns3:dyDescent="0.25">
       <c r="A892" s="61">
         <v>891</v>
       </c>
@@ -64011,7 +64014,7 @@
       <c r="U892" s="11"/>
       <c r="V892" s="10"/>
     </row>
-    <row r="893" spans="1:24" ht="16" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:24" ht="16" ns3:dyDescent="0.25">
       <c r="A893" s="61">
         <v>892</v>
       </c>
@@ -64069,7 +64072,7 @@
       <c r="U893" s="11"/>
       <c r="V893" s="10"/>
     </row>
-    <row r="894" spans="1:24" ht="16" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:24" ht="16" ns3:dyDescent="0.25">
       <c r="A894" s="61">
         <v>893</v>
       </c>
@@ -64125,7 +64128,7 @@
       <c r="U894" s="11"/>
       <c r="V894" s="10"/>
     </row>
-    <row r="895" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:24" ns3:dyDescent="0.2">
       <c r="A895" s="61">
         <v>894</v>
       </c>
@@ -64179,7 +64182,7 @@
       <c r="U895" s="11"/>
       <c r="V895" s="10"/>
     </row>
-    <row r="896" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:24" ns3:dyDescent="0.2">
       <c r="A896" s="61">
         <v>895</v>
       </c>
@@ -64233,7 +64236,7 @@
       <c r="U896" s="11"/>
       <c r="V896" s="10"/>
     </row>
-    <row r="897" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:22" ns3:dyDescent="0.2">
       <c r="A897" s="61">
         <v>896</v>
       </c>
@@ -64287,7 +64290,7 @@
       <c r="U897" s="11"/>
       <c r="V897" s="10"/>
     </row>
-    <row r="898" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:22" ns3:dyDescent="0.2">
       <c r="A898" s="61">
         <v>897</v>
       </c>
@@ -64341,7 +64344,7 @@
       <c r="U898" s="11"/>
       <c r="V898" s="10"/>
     </row>
-    <row r="899" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:22" ns3:dyDescent="0.2">
       <c r="A899" s="61">
         <v>898</v>
       </c>
@@ -64397,7 +64400,7 @@
       <c r="U899" s="11"/>
       <c r="V899" s="10"/>
     </row>
-    <row r="900" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:22" ns3:dyDescent="0.2">
       <c r="A900" s="61">
         <v>899</v>
       </c>
@@ -64457,7 +64460,7 @@
       <c r="U900" s="11"/>
       <c r="V900" s="10"/>
     </row>
-    <row r="901" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A901" s="61">
         <v>900</v>
       </c>
@@ -64517,7 +64520,7 @@
       <c r="U901" s="11"/>
       <c r="V901" s="10"/>
     </row>
-    <row r="902" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:22" ns3:dyDescent="0.2">
       <c r="A902" s="61">
         <v>901</v>
       </c>
@@ -64575,7 +64578,7 @@
       <c r="U902" s="11"/>
       <c r="V902" s="10"/>
     </row>
-    <row r="903" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A903" s="61">
         <v>902</v>
       </c>
@@ -64637,7 +64640,7 @@
       <c r="U903" s="11"/>
       <c r="V903" s="10"/>
     </row>
-    <row r="904" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A904" s="61">
         <v>903</v>
       </c>
@@ -64697,7 +64700,7 @@
       <c r="U904" s="11"/>
       <c r="V904" s="10"/>
     </row>
-    <row r="905" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A905" s="61">
         <v>904</v>
       </c>
@@ -64757,7 +64760,7 @@
       <c r="U905" s="11"/>
       <c r="V905" s="10"/>
     </row>
-    <row r="906" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A906" s="61">
         <v>905</v>
       </c>
@@ -64817,7 +64820,7 @@
       <c r="U906" s="11"/>
       <c r="V906" s="10"/>
     </row>
-    <row r="907" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A907" s="61">
         <v>906</v>
       </c>
@@ -64873,7 +64876,7 @@
       <c r="U907" s="11"/>
       <c r="V907" s="10"/>
     </row>
-    <row r="908" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A908" s="61">
         <v>907</v>
       </c>
@@ -64929,7 +64932,7 @@
       <c r="U908" s="11"/>
       <c r="V908" s="10"/>
     </row>
-    <row r="909" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A909" s="61">
         <v>908</v>
       </c>
@@ -64987,7 +64990,7 @@
       <c r="U909" s="11"/>
       <c r="V909" s="10"/>
     </row>
-    <row r="910" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:22" ns3:dyDescent="0.2">
       <c r="A910" s="61">
         <v>909</v>
       </c>
@@ -65043,7 +65046,7 @@
       <c r="U910" s="11"/>
       <c r="V910" s="10"/>
     </row>
-    <row r="911" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:22" ns3:dyDescent="0.2">
       <c r="A911" s="61">
         <v>910</v>
       </c>
@@ -65099,7 +65102,7 @@
       <c r="U911" s="11"/>
       <c r="V911" s="10"/>
     </row>
-    <row r="912" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:22" ns3:dyDescent="0.2">
       <c r="A912" s="61">
         <v>911</v>
       </c>
@@ -65157,7 +65160,7 @@
       <c r="U912" s="11"/>
       <c r="V912" s="10"/>
     </row>
-    <row r="913" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A913" s="61">
         <v>912</v>
       </c>
@@ -65213,7 +65216,7 @@
       <c r="U913" s="11"/>
       <c r="V913" s="10"/>
     </row>
-    <row r="914" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A914" s="61">
         <v>913</v>
       </c>
@@ -65269,7 +65272,7 @@
       <c r="U914" s="11"/>
       <c r="V914" s="10"/>
     </row>
-    <row r="915" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A915" s="61">
         <v>914</v>
       </c>
@@ -65327,7 +65330,7 @@
       <c r="U915" s="11"/>
       <c r="V915" s="10"/>
     </row>
-    <row r="916" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:22" ns3:dyDescent="0.2">
       <c r="A916" s="61">
         <v>915</v>
       </c>
@@ -65383,7 +65386,7 @@
       <c r="U916" s="11"/>
       <c r="V916" s="10"/>
     </row>
-    <row r="917" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:22" ns3:dyDescent="0.2">
       <c r="A917" s="61">
         <v>916</v>
       </c>
@@ -65441,7 +65444,7 @@
       <c r="U917" s="11"/>
       <c r="V917" s="10"/>
     </row>
-    <row r="918" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:22" ns3:dyDescent="0.2">
       <c r="A918" s="61">
         <v>917</v>
       </c>
@@ -65495,7 +65498,7 @@
       <c r="U918" s="11"/>
       <c r="V918" s="10"/>
     </row>
-    <row r="919" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:22" ns3:dyDescent="0.2">
       <c r="A919" s="61">
         <v>918</v>
       </c>
@@ -65549,7 +65552,7 @@
       <c r="U919" s="11"/>
       <c r="V919" s="10"/>
     </row>
-    <row r="920" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:22" ns3:dyDescent="0.2">
       <c r="A920" s="61">
         <v>919</v>
       </c>
@@ -65603,7 +65606,7 @@
       <c r="U920" s="11"/>
       <c r="V920" s="10"/>
     </row>
-    <row r="921" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:22" ns3:dyDescent="0.2">
       <c r="A921" s="61">
         <v>920</v>
       </c>
@@ -65659,7 +65662,7 @@
       <c r="U921" s="11"/>
       <c r="V921" s="10"/>
     </row>
-    <row r="922" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:22" ns3:dyDescent="0.2">
       <c r="A922" s="61">
         <v>921</v>
       </c>
@@ -65717,7 +65720,7 @@
       <c r="U922" s="11"/>
       <c r="V922" s="10"/>
     </row>
-    <row r="923" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:22" ns3:dyDescent="0.2">
       <c r="A923" s="61">
         <v>922</v>
       </c>
@@ -65777,7 +65780,7 @@
       <c r="U923" s="11"/>
       <c r="V923" s="10"/>
     </row>
-    <row r="924" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:22" ns3:dyDescent="0.2">
       <c r="A924" s="61">
         <v>923</v>
       </c>
@@ -65837,7 +65840,7 @@
       <c r="U924" s="11"/>
       <c r="V924" s="10"/>
     </row>
-    <row r="925" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A925" s="61">
         <v>924</v>
       </c>
@@ -65895,7 +65898,7 @@
       <c r="U925" s="11"/>
       <c r="V925" s="10"/>
     </row>
-    <row r="926" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A926" s="61">
         <v>925</v>
       </c>
@@ -65955,7 +65958,7 @@
       <c r="U926" s="11"/>
       <c r="V926" s="10"/>
     </row>
-    <row r="927" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:22" ns3:dyDescent="0.2">
       <c r="A927" s="61">
         <v>926</v>
       </c>
@@ -66011,7 +66014,7 @@
       <c r="U927" s="11"/>
       <c r="V927" s="10"/>
     </row>
-    <row r="928" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:22" ns3:dyDescent="0.2">
       <c r="A928" s="61">
         <v>927</v>
       </c>
@@ -66067,7 +66070,7 @@
       <c r="U928" s="11"/>
       <c r="V928" s="10"/>
     </row>
-    <row r="929" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:22" ns3:dyDescent="0.2">
       <c r="A929" s="61">
         <v>928</v>
       </c>
@@ -66123,7 +66126,7 @@
       <c r="U929" s="11"/>
       <c r="V929" s="10"/>
     </row>
-    <row r="930" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:22" ns3:dyDescent="0.2">
       <c r="A930" s="61">
         <v>929</v>
       </c>
@@ -66179,7 +66182,7 @@
       <c r="U930" s="11"/>
       <c r="V930" s="10"/>
     </row>
-    <row r="931" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:22" ns3:dyDescent="0.2">
       <c r="A931" s="61">
         <v>930</v>
       </c>
@@ -66235,7 +66238,7 @@
       <c r="U931" s="11"/>
       <c r="V931" s="10"/>
     </row>
-    <row r="932" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:22" ns3:dyDescent="0.2">
       <c r="A932" s="61">
         <v>931</v>
       </c>
@@ -66297,7 +66300,7 @@
       <c r="U932" s="11"/>
       <c r="V932" s="10"/>
     </row>
-    <row r="933" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:22" ns3:dyDescent="0.2">
       <c r="A933" s="61">
         <v>932</v>
       </c>
@@ -66353,7 +66356,7 @@
       <c r="U933" s="11"/>
       <c r="V933" s="10"/>
     </row>
-    <row r="934" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:22" ns3:dyDescent="0.2">
       <c r="A934" s="61">
         <v>933</v>
       </c>
@@ -66409,7 +66412,7 @@
       <c r="U934" s="11"/>
       <c r="V934" s="10"/>
     </row>
-    <row r="935" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:22" ns3:dyDescent="0.2">
       <c r="A935" s="61">
         <v>934</v>
       </c>
@@ -66465,7 +66468,7 @@
       <c r="U935" s="11"/>
       <c r="V935" s="10"/>
     </row>
-    <row r="936" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:22" ns3:dyDescent="0.2">
       <c r="A936" s="61">
         <v>935</v>
       </c>
@@ -66519,7 +66522,7 @@
       <c r="U936" s="11"/>
       <c r="V936" s="10"/>
     </row>
-    <row r="937" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:22" ns3:dyDescent="0.2">
       <c r="A937" s="61">
         <v>936</v>
       </c>
@@ -66575,7 +66578,7 @@
       <c r="U937" s="11"/>
       <c r="V937" s="10"/>
     </row>
-    <row r="938" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:22" ns3:dyDescent="0.2">
       <c r="A938" s="61">
         <v>937</v>
       </c>
@@ -66631,7 +66634,7 @@
       <c r="U938" s="11"/>
       <c r="V938" s="10"/>
     </row>
-    <row r="939" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:22" ns3:dyDescent="0.2">
       <c r="A939" s="61">
         <v>938</v>
       </c>
@@ -66687,7 +66690,7 @@
       <c r="U939" s="11"/>
       <c r="V939" s="10"/>
     </row>
-    <row r="940" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:22" ns3:dyDescent="0.2">
       <c r="A940" s="61">
         <v>939</v>
       </c>
@@ -66743,7 +66746,7 @@
       <c r="U940" s="11"/>
       <c r="V940" s="10"/>
     </row>
-    <row r="941" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:22" ns3:dyDescent="0.2">
       <c r="A941" s="61">
         <v>940</v>
       </c>
@@ -66803,7 +66806,7 @@
       <c r="U941" s="11"/>
       <c r="V941" s="10"/>
     </row>
-    <row r="942" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:22" ns3:dyDescent="0.2">
       <c r="A942" s="61">
         <v>941</v>
       </c>
@@ -66863,7 +66866,7 @@
       <c r="U942" s="11"/>
       <c r="V942" s="10"/>
     </row>
-    <row r="943" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:22" ns3:dyDescent="0.2">
       <c r="A943" s="61">
         <v>942</v>
       </c>
@@ -66921,7 +66924,7 @@
       <c r="U943" s="11"/>
       <c r="V943" s="10"/>
     </row>
-    <row r="944" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:22" ns3:dyDescent="0.2">
       <c r="A944" s="61">
         <v>943</v>
       </c>
@@ -66979,7 +66982,7 @@
       <c r="U944" s="11"/>
       <c r="V944" s="10"/>
     </row>
-    <row r="945" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A945" s="61">
         <v>944</v>
       </c>
@@ -67039,7 +67042,7 @@
       <c r="U945" s="11"/>
       <c r="V945" s="10"/>
     </row>
-    <row r="946" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A946" s="61">
         <v>945</v>
       </c>
@@ -67099,7 +67102,7 @@
       <c r="U946" s="11"/>
       <c r="V946" s="10"/>
     </row>
-    <row r="947" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:22" ns3:dyDescent="0.2">
       <c r="A947" s="61">
         <v>946</v>
       </c>
@@ -67157,7 +67160,7 @@
       <c r="U947" s="11"/>
       <c r="V947" s="10"/>
     </row>
-    <row r="948" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:22" ns3:dyDescent="0.2">
       <c r="A948" s="61">
         <v>947</v>
       </c>
@@ -67215,7 +67218,7 @@
       <c r="U948" s="11"/>
       <c r="V948" s="10"/>
     </row>
-    <row r="949" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A949" s="61">
         <v>948</v>
       </c>
@@ -67271,7 +67274,7 @@
       <c r="U949" s="11"/>
       <c r="V949" s="10"/>
     </row>
-    <row r="950" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.2">
       <c r="A950" s="61">
         <v>949</v>
       </c>
@@ -67327,7 +67330,7 @@
       <c r="U950" s="11"/>
       <c r="V950" s="10"/>
     </row>
-    <row r="951" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:22" ns3:dyDescent="0.2">
       <c r="A951" s="61">
         <v>950</v>
       </c>
@@ -67385,7 +67388,7 @@
       <c r="U951" s="11"/>
       <c r="V951" s="10"/>
     </row>
-    <row r="952" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:22" ns3:dyDescent="0.2">
       <c r="A952" s="61">
         <v>951</v>
       </c>
@@ -67443,7 +67446,7 @@
       <c r="U952" s="11"/>
       <c r="V952" s="10"/>
     </row>
-    <row r="953" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:22" ns3:dyDescent="0.2">
       <c r="A953" s="61">
         <v>952</v>
       </c>
@@ -67503,7 +67506,7 @@
       <c r="U953" s="11"/>
       <c r="V953" s="10"/>
     </row>
-    <row r="954" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:22" ns3:dyDescent="0.2">
       <c r="A954" s="61">
         <v>953</v>
       </c>
@@ -67559,7 +67562,7 @@
       <c r="U954" s="11"/>
       <c r="V954" s="10"/>
     </row>
-    <row r="955" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:22" ns3:dyDescent="0.2">
       <c r="A955" s="61">
         <v>954</v>
       </c>
@@ -67617,7 +67620,7 @@
       <c r="U955" s="11"/>
       <c r="V955" s="10"/>
     </row>
-    <row r="956" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:22" ns3:dyDescent="0.2">
       <c r="A956" s="61">
         <v>955</v>
       </c>
@@ -67673,7 +67676,7 @@
       <c r="U956" s="11"/>
       <c r="V956" s="10"/>
     </row>
-    <row r="957" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:22" ns3:dyDescent="0.2">
       <c r="A957" s="61">
         <v>956</v>
       </c>
@@ -67731,7 +67734,7 @@
       <c r="U957" s="11"/>
       <c r="V957" s="10"/>
     </row>
-    <row r="958" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:22" ns3:dyDescent="0.2">
       <c r="A958" s="61">
         <v>957</v>
       </c>
@@ -67789,7 +67792,7 @@
       <c r="U958" s="11"/>
       <c r="V958" s="10"/>
     </row>
-    <row r="959" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:22" ns3:dyDescent="0.2">
       <c r="A959" s="61">
         <v>958</v>
       </c>
@@ -67847,7 +67850,7 @@
       <c r="U959" s="11"/>
       <c r="V959" s="10"/>
     </row>
-    <row r="960" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:22" ns3:dyDescent="0.2">
       <c r="A960" s="61">
         <v>959</v>
       </c>
@@ -67905,7 +67908,7 @@
       <c r="U960" s="11"/>
       <c r="V960" s="10"/>
     </row>
-    <row r="961" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A961" s="61">
         <v>960</v>
       </c>
@@ -67963,7 +67966,7 @@
       <c r="U961" s="11"/>
       <c r="V961" s="10"/>
     </row>
-    <row r="962" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A962" s="61">
         <v>961</v>
       </c>
@@ -68021,7 +68024,7 @@
       <c r="U962" s="11"/>
       <c r="V962" s="10"/>
     </row>
-    <row r="963" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:22" ns3:dyDescent="0.2">
       <c r="A963" s="61">
         <v>962</v>
       </c>
@@ -68081,7 +68084,7 @@
       <c r="U963" s="11"/>
       <c r="V963" s="10"/>
     </row>
-    <row r="964" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:22" ns3:dyDescent="0.2">
       <c r="A964" s="61">
         <v>963</v>
       </c>
@@ -68133,7 +68136,7 @@
       <c r="U964" s="11"/>
       <c r="V964" s="10"/>
     </row>
-    <row r="965" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:22" ns3:dyDescent="0.2">
       <c r="A965" s="61">
         <v>964</v>
       </c>
@@ -68187,7 +68190,7 @@
       <c r="U965" s="11"/>
       <c r="V965" s="10"/>
     </row>
-    <row r="966" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A966" s="61">
         <v>965</v>
       </c>
@@ -68245,7 +68248,7 @@
       <c r="U966" s="11"/>
       <c r="V966" s="10"/>
     </row>
-    <row r="967" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A967" s="61">
         <v>966</v>
       </c>
@@ -68305,7 +68308,7 @@
       <c r="U967" s="11"/>
       <c r="V967" s="10"/>
     </row>
-    <row r="968" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:22" ns3:dyDescent="0.2">
       <c r="A968" s="61">
         <v>967</v>
       </c>
@@ -68360,7 +68363,7 @@
       <c r="U968" s="11"/>
       <c r="V968" s="10"/>
     </row>
-    <row r="969" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A969" s="61">
         <v>968</v>
       </c>
@@ -68416,7 +68419,7 @@
       <c r="U969" s="11"/>
       <c r="V969" s="10"/>
     </row>
-    <row r="970" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A970" s="61">
         <v>969</v>
       </c>
@@ -68474,7 +68477,7 @@
       <c r="U970" s="11"/>
       <c r="V970" s="10"/>
     </row>
-    <row r="971" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A971" s="61">
         <v>970</v>
       </c>
@@ -68532,7 +68535,7 @@
       <c r="U971" s="11"/>
       <c r="V971" s="10"/>
     </row>
-    <row r="972" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A972" s="61">
         <v>971</v>
       </c>
@@ -68588,7 +68591,7 @@
       <c r="U972" s="11"/>
       <c r="V972" s="10"/>
     </row>
-    <row r="973" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A973" s="61">
         <v>972</v>
       </c>
@@ -68644,7 +68647,7 @@
       <c r="U973" s="11"/>
       <c r="V973" s="10"/>
     </row>
-    <row r="974" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:22" ns3:dyDescent="0.2">
       <c r="A974" s="61">
         <v>973</v>
       </c>
@@ -68702,7 +68705,7 @@
       <c r="U974" s="11"/>
       <c r="V974" s="10"/>
     </row>
-    <row r="975" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:22" ns3:dyDescent="0.2">
       <c r="A975" s="58">
         <v>974</v>
       </c>
@@ -68760,7 +68763,7 @@
       <c r="U975" s="11"/>
       <c r="V975" s="10"/>
     </row>
-    <row r="976" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:22" ns3:dyDescent="0.2">
       <c r="A976" s="58">
         <v>975</v>
       </c>
@@ -68818,7 +68821,7 @@
       <c r="U976" s="11"/>
       <c r="V976" s="10"/>
     </row>
-    <row r="977" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:22" ns3:dyDescent="0.2">
       <c r="A977" s="61">
         <v>976</v>
       </c>
@@ -68876,7 +68879,7 @@
       <c r="U977" s="11"/>
       <c r="V977" s="10"/>
     </row>
-    <row r="978" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:22" ns3:dyDescent="0.2">
       <c r="A978" s="61">
         <v>977</v>
       </c>
@@ -68934,7 +68937,7 @@
       <c r="U978" s="11"/>
       <c r="V978" s="10"/>
     </row>
-    <row r="979" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:22" ns3:dyDescent="0.2">
       <c r="A979" s="61">
         <v>978</v>
       </c>
@@ -68994,7 +68997,7 @@
       <c r="U979" s="11"/>
       <c r="V979" s="10"/>
     </row>
-    <row r="980" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:22" ns3:dyDescent="0.2">
       <c r="A980" s="61">
         <v>979</v>
       </c>
@@ -69054,7 +69057,7 @@
       <c r="U980" s="11"/>
       <c r="V980" s="10"/>
     </row>
-    <row r="981" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:22" ns3:dyDescent="0.2">
       <c r="A981" s="61">
         <v>980</v>
       </c>
@@ -69112,7 +69115,7 @@
       <c r="U981" s="11"/>
       <c r="V981" s="10"/>
     </row>
-    <row r="982" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:22" ns3:dyDescent="0.2">
       <c r="A982" s="61">
         <v>981</v>
       </c>
@@ -69172,7 +69175,7 @@
       <c r="U982" s="11"/>
       <c r="V982" s="10"/>
     </row>
-    <row r="983" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:22" ns3:dyDescent="0.2">
       <c r="A983" s="61">
         <v>982</v>
       </c>
@@ -69232,7 +69235,7 @@
       <c r="U983" s="11"/>
       <c r="V983" s="10"/>
     </row>
-    <row r="984" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:22" ns3:dyDescent="0.2">
       <c r="A984" s="61">
         <v>983</v>
       </c>
@@ -69292,7 +69295,7 @@
       <c r="U984" s="11"/>
       <c r="V984" s="10"/>
     </row>
-    <row r="985" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:22" ns3:dyDescent="0.2">
       <c r="A985" s="61">
         <v>984</v>
       </c>
@@ -69346,7 +69349,7 @@
       <c r="U985" s="11"/>
       <c r="V985" s="10"/>
     </row>
-    <row r="986" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:22" ns3:dyDescent="0.2">
       <c r="A986" s="61">
         <v>985</v>
       </c>
@@ -69402,7 +69405,7 @@
       <c r="U986" s="11"/>
       <c r="V986" s="10"/>
     </row>
-    <row r="987" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:22" ns3:dyDescent="0.2">
       <c r="A987" s="61">
         <v>986</v>
       </c>
@@ -69458,7 +69461,7 @@
       <c r="U987" s="11"/>
       <c r="V987" s="10"/>
     </row>
-    <row r="988" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:22" ns3:dyDescent="0.2">
       <c r="A988" s="61">
         <v>987</v>
       </c>
@@ -69514,7 +69517,7 @@
       <c r="U988" s="11"/>
       <c r="V988" s="10"/>
     </row>
-    <row r="989" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:22" ns3:dyDescent="0.2">
       <c r="A989" s="61">
         <v>988</v>
       </c>
@@ -69570,7 +69573,7 @@
       <c r="U989" s="11"/>
       <c r="V989" s="10"/>
     </row>
-    <row r="990" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:22" ns3:dyDescent="0.2">
       <c r="A990" s="61">
         <v>989</v>
       </c>
@@ -69626,7 +69629,7 @@
       <c r="U990" s="11"/>
       <c r="V990" s="10"/>
     </row>
-    <row r="991" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:22" ns3:dyDescent="0.2">
       <c r="A991" s="61">
         <v>990</v>
       </c>
@@ -69682,7 +69685,7 @@
       <c r="U991" s="11"/>
       <c r="V991" s="10"/>
     </row>
-    <row r="992" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:22" ns3:dyDescent="0.2">
       <c r="A992" s="61">
         <v>991</v>
       </c>
@@ -69738,7 +69741,7 @@
       <c r="U992" s="11"/>
       <c r="V992" s="10"/>
     </row>
-    <row r="993" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:22" ns3:dyDescent="0.2">
       <c r="A993" s="61">
         <v>992</v>
       </c>
@@ -69794,7 +69797,7 @@
       <c r="U993" s="11"/>
       <c r="V993" s="10"/>
     </row>
-    <row r="994" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:22" ns3:dyDescent="0.2">
       <c r="A994" s="61">
         <v>993</v>
       </c>
@@ -69850,7 +69853,7 @@
       <c r="U994" s="11"/>
       <c r="V994" s="10"/>
     </row>
-    <row r="995" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:22" ns3:dyDescent="0.2">
       <c r="A995" s="61">
         <v>994</v>
       </c>
@@ -69906,7 +69909,7 @@
       <c r="U995" s="11"/>
       <c r="V995" s="10"/>
     </row>
-    <row r="996" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:22" ns3:dyDescent="0.2">
       <c r="A996" s="61">
         <v>995</v>
       </c>
@@ -69962,7 +69965,7 @@
       <c r="U996" s="11"/>
       <c r="V996" s="10"/>
     </row>
-    <row r="997" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:22" ns3:dyDescent="0.2">
       <c r="A997" s="61">
         <v>996</v>
       </c>
@@ -70020,7 +70023,7 @@
       <c r="U997" s="11"/>
       <c r="V997" s="10"/>
     </row>
-    <row r="998" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:22" ns3:dyDescent="0.2">
       <c r="A998" s="61">
         <v>997</v>
       </c>
@@ -70078,7 +70081,7 @@
       <c r="U998" s="11"/>
       <c r="V998" s="10"/>
     </row>
-    <row r="999" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:22" ns3:dyDescent="0.2">
       <c r="A999" s="61">
         <v>998</v>
       </c>
@@ -70136,7 +70139,7 @@
       <c r="U999" s="11"/>
       <c r="V999" s="10"/>
     </row>
-    <row r="1000" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1000" s="61">
         <v>999</v>
       </c>
@@ -70190,7 +70193,7 @@
       <c r="U1000" s="11"/>
       <c r="V1000" s="10"/>
     </row>
-    <row r="1001" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1001" s="61">
         <v>1000</v>
       </c>
@@ -70244,7 +70247,7 @@
       <c r="U1001" s="11"/>
       <c r="V1001" s="10"/>
     </row>
-    <row r="1002" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1002" s="61">
         <v>1001</v>
       </c>
@@ -70298,7 +70301,7 @@
       <c r="U1002" s="11"/>
       <c r="V1002" s="10"/>
     </row>
-    <row r="1003" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1003" s="61">
         <v>1002</v>
       </c>
@@ -70352,7 +70355,7 @@
       <c r="U1003" s="11"/>
       <c r="V1003" s="10"/>
     </row>
-    <row r="1004" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1004" s="61">
         <v>1003</v>
       </c>
@@ -70406,7 +70409,7 @@
       <c r="U1004" s="11"/>
       <c r="V1004" s="10"/>
     </row>
-    <row r="1005" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1005" s="61">
         <v>1004</v>
       </c>
@@ -70460,7 +70463,7 @@
       <c r="U1005" s="11"/>
       <c r="V1005" s="10"/>
     </row>
-    <row r="1006" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1006" s="61">
         <v>1005</v>
       </c>
@@ -70516,7 +70519,7 @@
       <c r="U1006" s="11"/>
       <c r="V1006" s="10"/>
     </row>
-    <row r="1007" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1007" s="61">
         <v>1006</v>
       </c>
@@ -70572,7 +70575,7 @@
       <c r="U1007" s="11"/>
       <c r="V1007" s="10"/>
     </row>
-    <row r="1008" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1008" s="61">
         <v>1007</v>
       </c>
@@ -70628,7 +70631,7 @@
       <c r="U1008" s="11"/>
       <c r="V1008" s="10"/>
     </row>
-    <row r="1009" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1009" s="61">
         <v>1008</v>
       </c>
@@ -70684,7 +70687,7 @@
       <c r="U1009" s="11"/>
       <c r="V1009" s="10"/>
     </row>
-    <row r="1010" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1010" s="61">
         <v>1009</v>
       </c>
@@ -70740,7 +70743,7 @@
       <c r="U1010" s="11"/>
       <c r="V1010" s="10"/>
     </row>
-    <row r="1011" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1011" s="61">
         <v>1010</v>
       </c>
@@ -70794,7 +70797,7 @@
       <c r="U1011" s="11"/>
       <c r="V1011" s="10"/>
     </row>
-    <row r="1012" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1012" s="61">
         <v>1011</v>
       </c>
@@ -70854,7 +70857,7 @@
       <c r="U1012" s="11"/>
       <c r="V1012" s="10"/>
     </row>
-    <row r="1013" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1013" s="61">
         <v>1012</v>
       </c>
@@ -70910,7 +70913,7 @@
       <c r="U1013" s="11"/>
       <c r="V1013" s="10"/>
     </row>
-    <row r="1014" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1014" s="61">
         <v>1013</v>
       </c>
@@ -70966,7 +70969,7 @@
       <c r="U1014" s="11"/>
       <c r="V1014" s="10"/>
     </row>
-    <row r="1015" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1015" s="61">
         <v>1014</v>
       </c>
@@ -71022,7 +71025,7 @@
       <c r="U1015" s="11"/>
       <c r="V1015" s="10"/>
     </row>
-    <row r="1016" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1016" s="61">
         <v>1015</v>
       </c>
@@ -71078,7 +71081,7 @@
       <c r="U1016" s="11"/>
       <c r="V1016" s="10"/>
     </row>
-    <row r="1017" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1017" s="61">
         <v>1016</v>
       </c>
@@ -71134,7 +71137,7 @@
       <c r="U1017" s="11"/>
       <c r="V1017" s="10"/>
     </row>
-    <row r="1018" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1018" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1018" s="61">
         <v>1017</v>
       </c>
@@ -71188,7 +71191,7 @@
       <c r="U1018" s="11"/>
       <c r="V1018" s="10"/>
     </row>
-    <row r="1019" spans="1:22" ht="16" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:22" ht="16" ns3:dyDescent="0.25">
       <c r="A1019" s="61">
         <v>1018</v>
       </c>
@@ -71246,7 +71249,7 @@
       <c r="U1019" s="11"/>
       <c r="V1019" s="10"/>
     </row>
-    <row r="1020" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1020" s="61">
         <v>1019</v>
       </c>
@@ -71304,7 +71307,7 @@
       <c r="U1020" s="11"/>
       <c r="V1020" s="10"/>
     </row>
-    <row r="1021" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1021" s="61">
         <v>1020</v>
       </c>
@@ -71358,7 +71361,7 @@
       <c r="U1021" s="11"/>
       <c r="V1021" s="10"/>
     </row>
-    <row r="1022" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1022" s="61">
         <v>1021</v>
       </c>
@@ -71412,7 +71415,7 @@
       <c r="U1022" s="11"/>
       <c r="V1022" s="10"/>
     </row>
-    <row r="1023" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1023" s="61">
         <v>1022</v>
       </c>
@@ -71466,7 +71469,7 @@
       <c r="U1023" s="11"/>
       <c r="V1023" s="10"/>
     </row>
-    <row r="1024" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1024" s="61">
         <v>1023</v>
       </c>
@@ -71520,7 +71523,7 @@
       <c r="U1024" s="11"/>
       <c r="V1024" s="10"/>
     </row>
-    <row r="1025" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:22" ht="16" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1025" s="61">
         <v>1024</v>
       </c>
@@ -71574,7 +71577,7 @@
       <c r="U1025" s="11"/>
       <c r="V1025" s="10"/>
     </row>
-    <row r="1026" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:22" ns3:dyDescent="0.2">
       <c r="A1026" s="61">
         <v>1025</v>
       </c>
@@ -71628,11 +71631,11 @@
       <c r="U1026" s="11"/>
       <c r="V1026" s="10"/>
     </row>
-    <row r="1027" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:22" ns3:dyDescent="0.2">
       <c r="Q1027" s="70"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X1026" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:X1026" ns2:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
